--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -18496,4 +18496,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03230F69-5C37-482A-9AF2-EA487C434149}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9B3E56-6981-4A8D-A07F-D09958A7E936}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{878B2073-6AC3-4E46-9BDE-C92993625DB4}"/>
 </file>
--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BCpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\2026\01.EPS\01.EI\01.메일_업무협의\260403_메일회신\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F6D865-6970-43AC-AAE4-3A52F19D49FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AAE271-F981-4E46-B7D1-BA251A5F72C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
-    <sheet name="NREL ATB 2024" sheetId="8" r:id="rId2"/>
-    <sheet name="Balance of System (NOT USED)" sheetId="5" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="10" r:id="rId4"/>
-    <sheet name="BCpUC-energy" sheetId="3" r:id="rId5"/>
-    <sheet name="BCpUC-power" sheetId="9" r:id="rId6"/>
-    <sheet name="BBoSCaSoFYC" sheetId="4" r:id="rId7"/>
+    <sheet name="KEEI_계산과정" sheetId="13" r:id="rId2"/>
+    <sheet name="NREL ATB 2024" sheetId="8" r:id="rId3"/>
+    <sheet name="Balance of System (NOT USED)" sheetId="5" r:id="rId4"/>
+    <sheet name="Calibration" sheetId="10" r:id="rId5"/>
+    <sheet name="BCpUC-energy" sheetId="3" r:id="rId6"/>
+    <sheet name="BCpUC-power" sheetId="9" r:id="rId7"/>
+    <sheet name="BBoSCaSoFYC" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="cpi_2020_to_2012">About!$A$50</definedName>
-    <definedName name="cpi_2022_to_2012">About!$A$52</definedName>
+    <definedName name="cpi_2020_to_2012">About!$A$59</definedName>
+    <definedName name="cpi_2022_to_2012">About!$A$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,6 +34,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="226">
   <si>
     <t>Year</t>
   </si>
@@ -51,9 +55,6 @@
     <t>Sources:</t>
   </si>
   <si>
-    <t>Battery cost projections per kWh</t>
-  </si>
-  <si>
     <t>Rocky Mountain Institute</t>
   </si>
   <si>
@@ -268,9 +269,6 @@
   </si>
   <si>
     <t>Base Year:</t>
-  </si>
-  <si>
-    <t>All values are given in 2021 U.S. dollars, see references at the bottom of this worksheet for dollar year conversions where source dollar years don't match 2021.</t>
   </si>
   <si>
     <t>Utility Scale Battery Storage</t>
@@ -298,9 +296,6 @@
     </r>
   </si>
   <si>
-    <t>Reference: Battery Storage cost values from W. Cole and A. Karmakar, “Cost Projections for Utility-scale Battery Storage: 2023 Update,” NREL/TP-6A40-85332. Golden, CO: National Renewable Energy Laboratory. https://www.nrel.gov/docs/fy23osti/85332.pdf. Note that values are converted to 2021$ for the ATB.</t>
-  </si>
-  <si>
     <t>Capital Cost ($/kWh)</t>
   </si>
   <si>
@@ -382,9 +377,6 @@
     <t>Future Projections</t>
   </si>
   <si>
-    <t xml:space="preserve">All values are given in 2021 U.S. dollars, using the Consumer Price Index (BLS, 2022) for dollar year conversions. </t>
-  </si>
-  <si>
     <t>For 15-year technical life (values in 2021$):</t>
   </si>
   <si>
@@ -463,9 +455,6 @@
     <t>Unit: Dmnl</t>
   </si>
   <si>
-    <t>Percent of First Year Total Costs</t>
-  </si>
-  <si>
     <t>Assumed duration:</t>
   </si>
   <si>
@@ -499,40 +488,304 @@
     <t>We determine this value via calibration against ATB data.</t>
   </si>
   <si>
-    <t>2022 to 2013 costs</t>
-  </si>
-  <si>
     <t>Raw Data (2022 $)</t>
   </si>
   <si>
     <t>Time (Year)</t>
   </si>
   <si>
-    <t>Battery Energy Cost per Unit Capacity : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Battery Power Cost per Unit Capacity : MostRecentRun</t>
+    <t>2021 (from 2023 ATB)</t>
+  </si>
+  <si>
+    <t>All values are given in 2022 U.S. dollars except 2021 data.</t>
+  </si>
+  <si>
+    <t>Reference: Battery Storage cost values from W. Cole and A. Karmakar, “Cost Projections for Utility-scale Battery Storage: 2023 Update,” NREL/TP-6A40-85332. Golden, CO: National Renewable Energy Laboratory. https://www.nrel.gov/docs/fy23osti/85332.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All values are given in 2022 U.S. dollars except for 2021 values from ATB 2023 </t>
+  </si>
+  <si>
+    <t>Battery Energy Cost per Unit Capacity : test</t>
+  </si>
+  <si>
+    <t>2022 to 2012 costs</t>
+  </si>
+  <si>
+    <t>Battery Power Cost per Unit Capacity : test</t>
+  </si>
+  <si>
+    <t>Battery cost projections per kWh(Trend)</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery cost projections per kWh(Value)</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>Li-ion (LFP)</t>
+  </si>
+  <si>
+    <t>Li-ion (NCM)</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>2025년</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2030년</t>
+  </si>
+  <si>
+    <t>A Study on the LCOS Outlook and the Establishment of the
+Optimal Mix for the Realization of efficient Carbon Neutrality(2/3)</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korea Energy Economics Institute</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.keei.re.kr/boardDownload.es?bid=0001&amp;list_no=127020&amp;seq=1</t>
+  </si>
+  <si>
+    <t>Page 97, Table 5-7</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025 to 2012 USD</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESS CAPEX 비용 환산 계산 과정 (KEEI 표 5-7 기반)</t>
+  </si>
+  <si>
+    <t>【STEP 0】 가정 및 기준값 (Assumptions)</t>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>기호</t>
+  </si>
+  <si>
+    <t>값</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>환율 (KRW/USD)</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>원/달러</t>
+  </si>
+  <si>
+    <t>한국은행 2025.9.26 기준 (1달러=1,412원)</t>
+  </si>
+  <si>
+    <t>CPI_adj</t>
+  </si>
+  <si>
+    <t>NREL ATB 기준 방전 시간</t>
+  </si>
+  <si>
+    <t>hr_ATB</t>
+  </si>
+  <si>
+    <t>시간</t>
+  </si>
+  <si>
+    <t>hr_KR</t>
+  </si>
+  <si>
+    <t>연도</t>
+  </si>
+  <si>
+    <t>방전(hr)</t>
+  </si>
+  <si>
+    <t>CAPEX Power</t>
+  </si>
+  <si>
+    <t>원/kW</t>
+  </si>
+  <si>
+    <t>CAPEX Energy</t>
+  </si>
+  <si>
+    <t>원/kWh</t>
+  </si>
+  <si>
+    <t>출처 / 비고</t>
+  </si>
+  <si>
+    <t>물가 보정계수 (2025→2012 USD)</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>한국 KEEI 표 방전 시간</t>
+  </si>
+  <si>
+    <t>【STEP 1】 원본 데이터 — 한국 CAPEX (원/kW, 원/kWh)   ※ 출처: KEEI 표 5-7, 2025년 9월 기준</t>
+  </si>
+  <si>
+    <t>계산식 (LFP 예시)</t>
+  </si>
+  <si>
+    <t>$/MW</t>
+  </si>
+  <si>
+    <t>About!A62 참조 (≈0.713)  |  2025 USD → 2012 USD 변환</t>
+  </si>
+  <si>
+    <t>NREL ATB 2024 대표 모델: 60MW/240MWh (4Hr Moderate)</t>
+  </si>
+  <si>
+    <t>KEEI 표 5-7 — 6시간 및 7시간 두 가지 조건</t>
+  </si>
+  <si>
+    <t>【STEP 2】 달러 환산 — 원/kW → $/MW, 원/kWh → $/MWh   환산식: 원값 × 1,000 ÷ FX(C5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  단위 환산 근거: 1 $/kW = 1,000 $/MW  |  원/kW × 1,000 ÷ 환율 = $/MW  |  원/kWh × 1,000 ÷ 환율 = $/MWh</t>
+  </si>
+  <si>
+    <t>E12 × 1,000 ÷ C5</t>
+  </si>
+  <si>
+    <t>위와 동일</t>
+  </si>
+  <si>
+    <t>$/MWh</t>
+  </si>
+  <si>
+    <t>E14 × 1,000 ÷ C5</t>
+  </si>
+  <si>
+    <t>E16 × 1,000 ÷ C5</t>
+  </si>
+  <si>
+    <t>E18 × 1,000 ÷ C5</t>
+  </si>
+  <si>
+    <t>【STEP 3】 실질가격 환산 — 2025 USD → 2012 USD   환산식: STEP 2 결과 × CPI 보정계수(C6 ≈ 0.713)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  보정 이유: NREL ATB 데이터는 2022 USD 기준이나 본 모델은 2012 USD 공통 기준 사용. 보정계수 = CPI(2012)/CPI(2025) = About!A62 ≈ 0.713</t>
+  </si>
+  <si>
+    <t>계산식</t>
+  </si>
+  <si>
+    <t>$/MW (2012$)</t>
+  </si>
+  <si>
+    <t>STEP2 결과 × C6</t>
+  </si>
+  <si>
+    <t>$/MWh (2012$)</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>【STEP 3-B】 Li-ion (LFP) 6시간 기준 — 선형보간/외삽으로 2020~2050년 비용 추정 (2012 USD)</t>
+  </si>
+  <si>
+    <t>CAPEX Power (LFP, 6hr)</t>
+  </si>
+  <si>
+    <t>CAPEX Energy (LFP, 6hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ⚠ 주의: 선형 외삽 특성상 에너지 비용이 2040년대 중반 이후 음수로 진입할 수 있음. 실제 모델 적용 시 하한값(0 또는 기술적 바닥가격) 설정 권장.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  기준: 2025년(E36, E38)·2030년(E40, E42). slope=(2030값-2025값)/5. 2020-2024: 2025 역외삽, 2025-2030: 내삽, 2031-2050: 2030 순외삽.</t>
+  </si>
+  <si>
+    <t>【STEP 4】 미국 NREL/LCOS vs 한국 KEEI — CAPEX 비교 (2025년 &amp; 2030년 기준)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  단위 통일: 미국 데이터($/MW, $/MWh, 2012$) vs 한국 데이터(원/kW, 원/kWh → $/MW, $/MWh 환산, 2025년 9월 기준 1달러=1,412원)</t>
+  </si>
+  <si>
+    <t>차이
+(KOR-USA)</t>
+  </si>
+  <si>
+    <t>차이율
+(%)</t>
+  </si>
+  <si>
+    <t>energy</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>power</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 (NREL)
+2021년</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국 (KEEI)
+2021년</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 (NREL)
+2024년</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국 (KEEI)
+2024년</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>NREL= 4hr</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>[참고] EPS US 모델</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0;#,##0"/>
-    <numFmt numFmtId="165" formatCode="###0;###0"/>
-    <numFmt numFmtId="166" formatCode="###0.00;###0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
+  <numFmts count="11">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="#,##0;#,##0"/>
+    <numFmt numFmtId="179" formatCode="###0;###0"/>
+    <numFmt numFmtId="180" formatCode="###0.00;###0.00"/>
+    <numFmt numFmtId="181" formatCode="0.000"/>
+    <numFmt numFmtId="182" formatCode="0.0%"/>
+    <numFmt numFmtId="183" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="188" formatCode="0.0000"/>
+    <numFmt numFmtId="189" formatCode="m&quot;월&quot;\ d&quot;일&quot;"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -540,7 +793,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -548,7 +801,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -556,14 +809,14 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -571,7 +824,7 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -579,21 +832,21 @@
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -662,14 +915,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -679,8 +932,71 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF7030A0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -765,8 +1081,62 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E6FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="77">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -1632,8 +2002,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF555555"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF555555"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF555555"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF555555"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF555555"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
@@ -1652,10 +2046,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1667,28 +2064,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1707,31 +2104,31 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1739,12 +2136,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1783,7 +2180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="5" fontId="10" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="10" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1795,7 +2192,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1838,8 +2235,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="10" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1852,7 +2249,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1956,27 +2353,81 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="5" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2024,60 +2475,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2087,18 +2484,114 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="15" borderId="78" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="16" borderId="78" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="15" borderId="78" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="15" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="23" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Currency" xfId="8" builtinId="4"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Percent" xfId="9" builtinId="5"/>
     <cellStyle name="Table title" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="백분율" xfId="9" builtinId="5"/>
+    <cellStyle name="쉼표 [0]" xfId="10" builtinId="6"/>
+    <cellStyle name="통화" xfId="8" builtinId="4"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2121,7 +2614,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2224,85 +2717,85 @@
                   <c:v>303546</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>275720</c:v>
+                  <c:v>274986</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>254008</c:v>
+                  <c:v>253296</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>237399</c:v>
+                  <c:v>236734</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>223663</c:v>
+                  <c:v>223030</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>212018</c:v>
+                  <c:v>211554</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>202332</c:v>
+                  <c:v>201954</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>194107</c:v>
+                  <c:v>193764</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>186872</c:v>
+                  <c:v>186541</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>180500</c:v>
+                  <c:v>180196</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>174745</c:v>
+                  <c:v>174552</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>169959</c:v>
+                  <c:v>169876</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>165780</c:v>
+                  <c:v>165776</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>162166</c:v>
+                  <c:v>162216</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>159002</c:v>
+                  <c:v>159077</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>156172</c:v>
+                  <c:v>156257</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>153632</c:v>
+                  <c:v>153722</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>151363</c:v>
+                  <c:v>151442</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>149361</c:v>
+                  <c:v>149428</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>147535</c:v>
+                  <c:v>147587</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>145853</c:v>
+                  <c:v>145898</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>144309</c:v>
+                  <c:v>144352</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>142883</c:v>
+                  <c:v>142921</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>141583</c:v>
+                  <c:v>141617</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>140367</c:v>
+                  <c:v>140396</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>139237</c:v>
+                  <c:v>139257</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>138175</c:v>
+                  <c:v>138188</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>137182</c:v>
+                  <c:v>137190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2594,6 +3087,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2601,7 +3095,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2639,7 +3132,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3112,6 +3605,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3119,7 +3613,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4347,6 +4840,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4608,317 +5105,2158 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="708" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2F3B8B63-BF4D-4957-AC1A-E892A8AB8F21}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;545432ba-5084-42ec-967c-bddb6af4d360&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="67.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="2" max="2" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="188" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="4">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="4">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1.0549999999999999</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="38">
+        <v>0.9143273584567535</v>
+      </c>
+      <c r="B57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="38">
+        <v>0.89805481563188172</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="38">
+        <v>0.88711067149387013</v>
+      </c>
+      <c r="B59" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="4">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="38">
+        <v>0.84730412960844359</v>
+      </c>
+      <c r="B60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60">
+        <f>cpi_2022_to_2012/A60</f>
+        <v>0.92590251319813455</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="38">
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="38">
+        <v>0.71310900044104586</v>
+      </c>
+      <c r="B62" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="38"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>1.0549999999999999</v>
-      </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="38">
-        <v>0.9143273584567535</v>
-      </c>
-      <c r="B48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="38">
-        <v>0.89805481563188172</v>
-      </c>
-      <c r="B49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="38">
-        <v>0.88711067149387013</v>
-      </c>
-      <c r="B50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="38">
-        <v>0.84730412960844359</v>
-      </c>
-      <c r="B51" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="38">
-        <v>0.78452102304761584</v>
-      </c>
-      <c r="B52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>135</v>
-      </c>
-      <c r="B55">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B29" r:id="rId3" xr:uid="{CA93FE29-A0A0-406A-B94C-DC5006AB819F}"/>
+    <hyperlink ref="B15" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B36" r:id="rId3" xr:uid="{CA93FE29-A0A0-406A-B94C-DC5006AB819F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA52F610-0BB7-4FA5-A954-7D9B28960546}">
+  <dimension ref="A1:AJ70"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="33" width="10.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="190" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="196" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="174"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="197" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="198" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="198" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="198" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="197" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="195" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="193">
+        <v>1412</v>
+      </c>
+      <c r="D5" s="192" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="191" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="195" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="194">
+        <f>About!A62</f>
+        <v>0.71310900044104586</v>
+      </c>
+      <c r="D6" s="192" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="191" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="195" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="192">
+        <v>4</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="191" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="195" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="192" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="204">
+        <v>46180</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="191" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="206" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="205"/>
+      <c r="F10" s="205"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="205"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="205"/>
+      <c r="L10" s="205"/>
+    </row>
+    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="198" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="198" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="198" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="198" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="198" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="198" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="198" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="199" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="199" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="199" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="199">
+        <v>6</v>
+      </c>
+      <c r="E12" s="200">
+        <v>245295</v>
+      </c>
+      <c r="F12" s="200">
+        <v>245295</v>
+      </c>
+      <c r="G12" s="200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="199"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199">
+        <v>7</v>
+      </c>
+      <c r="E13" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="G13" s="200">
+        <v>1164300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="201" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="201" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="201">
+        <v>6</v>
+      </c>
+      <c r="E14" s="200">
+        <v>369936</v>
+      </c>
+      <c r="F14" s="200">
+        <v>475633</v>
+      </c>
+      <c r="G14" s="200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="201"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201">
+        <v>7</v>
+      </c>
+      <c r="E15" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="200">
+        <v>201480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="199" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="199" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="199" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" s="199">
+        <v>6</v>
+      </c>
+      <c r="E16" s="200">
+        <v>213225</v>
+      </c>
+      <c r="F16" s="200">
+        <v>213225</v>
+      </c>
+      <c r="G16" s="200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="199"/>
+      <c r="B17" s="199"/>
+      <c r="C17" s="199"/>
+      <c r="D17" s="199">
+        <v>7</v>
+      </c>
+      <c r="E17" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="200">
+        <v>1164300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="201" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="201" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="201">
+        <v>6</v>
+      </c>
+      <c r="E18" s="200">
+        <v>284175</v>
+      </c>
+      <c r="F18" s="200">
+        <v>391064</v>
+      </c>
+      <c r="G18" s="200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="201"/>
+      <c r="B19" s="201"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="201">
+        <v>7</v>
+      </c>
+      <c r="E19" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="200" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="200">
+        <v>201480</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="196" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="174"/>
+      <c r="C21" s="174"/>
+      <c r="D21" s="174"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="174"/>
+      <c r="I21" s="174"/>
+      <c r="J21" s="174"/>
+      <c r="K21" s="174"/>
+      <c r="L21" s="174"/>
+    </row>
+    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="203" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="174"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="174"/>
+      <c r="E22" s="174"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="174"/>
+    </row>
+    <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="198" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="198" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="198" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" s="198" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="198" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="198" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="198" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="198" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="199" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="199" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="199" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="199">
+        <v>6</v>
+      </c>
+      <c r="E24" s="200">
+        <f>E12*1000/$C$5</f>
+        <v>173721.671388102</v>
+      </c>
+      <c r="F24" s="200">
+        <f>F12*1000/$C$5</f>
+        <v>173721.671388102</v>
+      </c>
+      <c r="G24" s="200">
+        <f>IFERROR(VALUE(G12)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="207" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="199"/>
+      <c r="B25" s="199"/>
+      <c r="C25" s="199"/>
+      <c r="D25" s="199">
+        <v>7</v>
+      </c>
+      <c r="E25" s="200">
+        <f>IFERROR(VALUE(E13)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="200">
+        <f>IFERROR(VALUE(F13)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="200">
+        <f>G13*1000/$C$5</f>
+        <v>824575.07082152972</v>
+      </c>
+      <c r="H25" s="207" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="201" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="201" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="201">
+        <v>6</v>
+      </c>
+      <c r="E26" s="202">
+        <f>E14*1000/$C$5</f>
+        <v>261994.33427762039</v>
+      </c>
+      <c r="F26" s="202">
+        <f>F14*1000/$C$5</f>
+        <v>336850.56657223793</v>
+      </c>
+      <c r="G26" s="202">
+        <f>IFERROR(VALUE(G14)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="208" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="201"/>
+      <c r="B27" s="201"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="201">
+        <v>7</v>
+      </c>
+      <c r="E27" s="202">
+        <f>IFERROR(VALUE(E15)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="202">
+        <f>IFERROR(VALUE(F15)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="202">
+        <f>G15*1000/$C$5</f>
+        <v>142691.21813031161</v>
+      </c>
+      <c r="H27" s="208" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="199" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="199" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="199" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="199">
+        <v>6</v>
+      </c>
+      <c r="E28" s="200">
+        <f>E16*1000/$C$5</f>
+        <v>151009.20679886686</v>
+      </c>
+      <c r="F28" s="200">
+        <f>F16*1000/$C$5</f>
+        <v>151009.20679886686</v>
+      </c>
+      <c r="G28" s="200">
+        <f>IFERROR(VALUE(G16)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="207" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="199"/>
+      <c r="B29" s="199"/>
+      <c r="C29" s="199"/>
+      <c r="D29" s="199">
+        <v>7</v>
+      </c>
+      <c r="E29" s="200">
+        <f>IFERROR(VALUE(E17)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="200">
+        <f>IFERROR(VALUE(F17)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="200">
+        <f>G17*1000/$C$5</f>
+        <v>824575.07082152972</v>
+      </c>
+      <c r="H29" s="207" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="201" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="201" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="201">
+        <v>6</v>
+      </c>
+      <c r="E30" s="202">
+        <f>E18*1000/$C$5</f>
+        <v>201257.0821529745</v>
+      </c>
+      <c r="F30" s="202">
+        <f>F18*1000/$C$5</f>
+        <v>276957.507082153</v>
+      </c>
+      <c r="G30" s="202">
+        <f>IFERROR(VALUE(G18)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="208" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="201"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="201">
+        <v>7</v>
+      </c>
+      <c r="E31" s="202">
+        <f>IFERROR(VALUE(E19)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="202">
+        <f>IFERROR(VALUE(F19)*1000/$C$5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="202">
+        <f>G19*1000/$C$5</f>
+        <v>142691.21813031161</v>
+      </c>
+      <c r="H31" s="208" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="196" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="174"/>
+      <c r="C33" s="174"/>
+      <c r="D33" s="174"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="174"/>
+      <c r="G33" s="174"/>
+      <c r="H33" s="174"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="174"/>
+      <c r="L33" s="174"/>
+    </row>
+    <row r="34" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="209" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="174"/>
+      <c r="C34" s="174"/>
+      <c r="D34" s="174"/>
+      <c r="E34" s="174"/>
+      <c r="F34" s="174"/>
+      <c r="G34" s="174"/>
+      <c r="H34" s="174"/>
+    </row>
+    <row r="35" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="198" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="198" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="198" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" s="198" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="198" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="198" t="s">
+        <v>153</v>
+      </c>
+      <c r="G35" s="198" t="s">
+        <v>154</v>
+      </c>
+      <c r="H35" s="198" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="199" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" s="199" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="199" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" s="199">
+        <v>6</v>
+      </c>
+      <c r="E36" s="200">
+        <f>E24*$C$6</f>
+        <v>123882.48743851724</v>
+      </c>
+      <c r="F36" s="200">
+        <f>F24*$C$6</f>
+        <v>123882.48743851724</v>
+      </c>
+      <c r="G36" s="200">
+        <f>IFERROR(G24*$C$6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="207" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="199"/>
+      <c r="B37" s="199"/>
+      <c r="C37" s="199"/>
+      <c r="D37" s="199">
+        <v>7</v>
+      </c>
+      <c r="E37" s="200"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200">
+        <f>G25*$C$6</f>
+        <v>588011.90454214567</v>
+      </c>
+      <c r="H37" s="207" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="201" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="201" t="s">
+        <v>207</v>
+      </c>
+      <c r="D38" s="201">
+        <v>6</v>
+      </c>
+      <c r="E38" s="202">
+        <f>E26*$C$6</f>
+        <v>186830.51783793111</v>
+      </c>
+      <c r="F38" s="202">
+        <f>F26*$C$6</f>
+        <v>240211.17082632857</v>
+      </c>
+      <c r="G38" s="202">
+        <f>IFERROR(G26*$C$6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="208" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="201"/>
+      <c r="B39" s="201"/>
+      <c r="C39" s="201"/>
+      <c r="D39" s="201">
+        <v>7</v>
+      </c>
+      <c r="E39" s="202"/>
+      <c r="F39" s="202"/>
+      <c r="G39" s="202">
+        <f>G27*$C$6</f>
+        <v>101754.39193262176</v>
+      </c>
+      <c r="H39" s="208" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="199" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" s="199" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" s="199" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" s="199">
+        <v>6</v>
+      </c>
+      <c r="E40" s="200">
+        <f>E28*$C$6</f>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="F40" s="200">
+        <f>F28*$C$6</f>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="G40" s="200">
+        <f>IFERROR(G28*$C$6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="207" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="199"/>
+      <c r="B41" s="199"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="199">
+        <v>7</v>
+      </c>
+      <c r="E41" s="200"/>
+      <c r="F41" s="200"/>
+      <c r="G41" s="200">
+        <f>G29*$C$6</f>
+        <v>588011.90454214567</v>
+      </c>
+      <c r="H41" s="207" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="201" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="201" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" s="201" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42" s="201">
+        <v>6</v>
+      </c>
+      <c r="E42" s="202">
+        <f>E30*$C$6</f>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="F42" s="202">
+        <f>F30*$C$6</f>
+        <v>197500.89103999801</v>
+      </c>
+      <c r="G42" s="202">
+        <f>IFERROR(G30*$C$6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="208" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="201"/>
+      <c r="B43" s="201"/>
+      <c r="C43" s="201"/>
+      <c r="D43" s="201">
+        <v>7</v>
+      </c>
+      <c r="E43" s="202"/>
+      <c r="F43" s="202"/>
+      <c r="G43" s="202">
+        <f>G31*$C$6</f>
+        <v>101754.39193262176</v>
+      </c>
+      <c r="H43" s="208" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="211"/>
+      <c r="B44" s="211"/>
+      <c r="C44" s="211"/>
+      <c r="D44" s="211"/>
+      <c r="E44" s="212"/>
+      <c r="F44" s="212"/>
+      <c r="G44" s="212"/>
+      <c r="H44" s="213"/>
+    </row>
+    <row r="45" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="196" t="s">
+        <v>209</v>
+      </c>
+      <c r="B45" s="174"/>
+      <c r="C45" s="174"/>
+      <c r="D45" s="174"/>
+      <c r="E45" s="174"/>
+      <c r="F45" s="174"/>
+      <c r="G45" s="174"/>
+      <c r="H45" s="174"/>
+      <c r="I45" s="174"/>
+      <c r="J45" s="174"/>
+      <c r="K45" s="174"/>
+      <c r="L45" s="174"/>
+      <c r="M45" s="174"/>
+      <c r="N45" s="174"/>
+      <c r="O45" s="174"/>
+      <c r="P45" s="174"/>
+      <c r="Q45" s="174"/>
+      <c r="R45" s="174"/>
+      <c r="S45" s="174"/>
+      <c r="T45" s="174"/>
+      <c r="U45" s="174"/>
+      <c r="V45" s="174"/>
+      <c r="W45" s="174"/>
+      <c r="X45" s="174"/>
+      <c r="Y45" s="174"/>
+      <c r="Z45" s="174"/>
+      <c r="AA45" s="174"/>
+      <c r="AB45" s="174"/>
+      <c r="AC45" s="174"/>
+      <c r="AD45" s="174"/>
+      <c r="AE45" s="174"/>
+      <c r="AF45" s="174"/>
+      <c r="AG45" s="174"/>
+    </row>
+    <row r="46" spans="1:33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="203" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" s="174"/>
+      <c r="C46" s="174"/>
+      <c r="D46" s="174"/>
+      <c r="E46" s="174"/>
+      <c r="F46" s="174"/>
+      <c r="G46" s="174"/>
+      <c r="H46" s="174"/>
+      <c r="I46" s="174"/>
+      <c r="J46" s="174"/>
+      <c r="K46" s="174"/>
+      <c r="L46" s="174"/>
+      <c r="M46" s="174"/>
+      <c r="N46" s="174"/>
+      <c r="O46" s="174"/>
+      <c r="P46" s="174"/>
+      <c r="Q46" s="174"/>
+      <c r="R46" s="174"/>
+      <c r="S46" s="174"/>
+      <c r="T46" s="174"/>
+      <c r="U46" s="174"/>
+      <c r="V46" s="174"/>
+      <c r="W46" s="174"/>
+      <c r="X46" s="174"/>
+      <c r="Y46" s="174"/>
+      <c r="Z46" s="174"/>
+      <c r="AA46" s="174"/>
+      <c r="AB46" s="174"/>
+      <c r="AC46" s="174"/>
+      <c r="AD46" s="174"/>
+      <c r="AE46" s="174"/>
+      <c r="AF46" s="174"/>
+      <c r="AG46" s="174"/>
+    </row>
+    <row r="47" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="198" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" s="198" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="218">
+        <v>2020</v>
+      </c>
+      <c r="D47" s="218">
+        <v>2021</v>
+      </c>
+      <c r="E47" s="218">
+        <v>2022</v>
+      </c>
+      <c r="F47" s="218">
+        <v>2023</v>
+      </c>
+      <c r="G47" s="218">
+        <v>2024</v>
+      </c>
+      <c r="H47" s="219">
+        <v>2025</v>
+      </c>
+      <c r="I47" s="218">
+        <v>2026</v>
+      </c>
+      <c r="J47" s="218">
+        <v>2027</v>
+      </c>
+      <c r="K47" s="218">
+        <v>2028</v>
+      </c>
+      <c r="L47" s="218">
+        <v>2029</v>
+      </c>
+      <c r="M47" s="219">
+        <v>2030</v>
+      </c>
+      <c r="N47" s="218">
+        <v>2031</v>
+      </c>
+      <c r="O47" s="218">
+        <v>2032</v>
+      </c>
+      <c r="P47" s="218">
+        <v>2033</v>
+      </c>
+      <c r="Q47" s="218">
+        <v>2034</v>
+      </c>
+      <c r="R47" s="218">
+        <v>2035</v>
+      </c>
+      <c r="S47" s="218">
+        <v>2036</v>
+      </c>
+      <c r="T47" s="218">
+        <v>2037</v>
+      </c>
+      <c r="U47" s="218">
+        <v>2038</v>
+      </c>
+      <c r="V47" s="218">
+        <v>2039</v>
+      </c>
+      <c r="W47" s="218">
+        <v>2040</v>
+      </c>
+      <c r="X47" s="218">
+        <v>2041</v>
+      </c>
+      <c r="Y47" s="218">
+        <v>2042</v>
+      </c>
+      <c r="Z47" s="218">
+        <v>2043</v>
+      </c>
+      <c r="AA47" s="218">
+        <v>2044</v>
+      </c>
+      <c r="AB47" s="218">
+        <v>2045</v>
+      </c>
+      <c r="AC47" s="218">
+        <v>2046</v>
+      </c>
+      <c r="AD47" s="218">
+        <v>2047</v>
+      </c>
+      <c r="AE47" s="218">
+        <v>2048</v>
+      </c>
+      <c r="AF47" s="218">
+        <v>2049</v>
+      </c>
+      <c r="AG47" s="218">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" s="214" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="217" t="s">
+        <v>210</v>
+      </c>
+      <c r="B48" s="216" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" s="220">
+        <f>E36+((E40-E36)/5)*(2020-2025)</f>
+        <v>140078.95035929937</v>
+      </c>
+      <c r="D48" s="220">
+        <f>E36+((E40-E36)/5)*(2021-2025)</f>
+        <v>136839.65777514293</v>
+      </c>
+      <c r="E48" s="220">
+        <f>E36+((E40-E36)/5)*(2022-2025)</f>
+        <v>133600.36519098651</v>
+      </c>
+      <c r="F48" s="220">
+        <f>E36+((E40-E36)/5)*(2023-2025)</f>
+        <v>130361.07260683009</v>
+      </c>
+      <c r="G48" s="220">
+        <f>E36+((E40-E36)/5)*(2024-2025)</f>
+        <v>127121.78002267367</v>
+      </c>
+      <c r="H48" s="221">
+        <f>E36</f>
+        <v>123882.48743851724</v>
+      </c>
+      <c r="I48" s="220">
+        <f>E36+((E40-E36)/5)*(2026-2025)</f>
+        <v>120643.19485436082</v>
+      </c>
+      <c r="J48" s="220">
+        <f>E36+((E40-E36)/5)*(2027-2025)</f>
+        <v>117403.9022702044</v>
+      </c>
+      <c r="K48" s="220">
+        <f>E36+((E40-E36)/5)*(2028-2025)</f>
+        <v>114164.60968604797</v>
+      </c>
+      <c r="L48" s="220">
+        <f>E36+((E40-E36)/5)*(2029-2025)</f>
+        <v>110925.31710189156</v>
+      </c>
+      <c r="M48" s="221">
+        <f>E40</f>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="N48" s="220">
+        <f>M48</f>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="O48" s="220">
+        <f t="shared" ref="O48:AG48" si="0">N48</f>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="P48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="Q48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="R48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="S48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="T48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="U48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="V48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="W48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="X48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="Y48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="Z48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AA48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AB48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AC48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AD48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AE48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AF48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+      <c r="AG48" s="220">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" s="215" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="195" t="s">
+        <v>211</v>
+      </c>
+      <c r="B49" s="222" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="223">
+        <f>E38+((E42-E38)/5)*(2020-2025)</f>
+        <v>230142.79899007312</v>
+      </c>
+      <c r="D49" s="223">
+        <f>E38+((E42-E38)/5)*(2021-2025)</f>
+        <v>221480.34275964473</v>
+      </c>
+      <c r="E49" s="223">
+        <f>E38+((E42-E38)/5)*(2022-2025)</f>
+        <v>212817.88652921631</v>
+      </c>
+      <c r="F49" s="223">
+        <f>E38+((E42-E38)/5)*(2023-2025)</f>
+        <v>204155.43029878792</v>
+      </c>
+      <c r="G49" s="223">
+        <f>E38+((E42-E38)/5)*(2024-2025)</f>
+        <v>195492.9740683595</v>
+      </c>
+      <c r="H49" s="224">
+        <f>E38</f>
+        <v>186830.51783793111</v>
+      </c>
+      <c r="I49" s="223">
+        <f>E38+((E42-E38)/5)*(2026-2025)</f>
+        <v>178168.06160750272</v>
+      </c>
+      <c r="J49" s="223">
+        <f>E38+((E42-E38)/5)*(2027-2025)</f>
+        <v>169505.6053770743</v>
+      </c>
+      <c r="K49" s="223">
+        <f>E38+((E42-E38)/5)*(2028-2025)</f>
+        <v>160843.14914664591</v>
+      </c>
+      <c r="L49" s="223">
+        <f>E38+((E42-E38)/5)*(2029-2025)</f>
+        <v>152180.69291621749</v>
+      </c>
+      <c r="M49" s="224">
+        <f>E42</f>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="N49" s="220">
+        <f>M49</f>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="O49" s="220">
+        <f t="shared" ref="O49:AG49" si="1">N49</f>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="P49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="Q49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="R49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="S49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="T49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="U49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="V49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="W49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="X49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="Y49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="Z49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AA49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AB49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AC49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AD49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AE49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AF49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AG49" s="220">
+        <f t="shared" si="1"/>
+        <v>143518.2366857891</v>
+      </c>
+      <c r="AH49"/>
+      <c r="AI49"/>
+      <c r="AJ49"/>
+    </row>
+    <row r="50" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="225" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="210"/>
+      <c r="C50" s="210"/>
+      <c r="D50" s="210"/>
+      <c r="E50" s="210"/>
+      <c r="F50" s="210"/>
+      <c r="G50" s="210"/>
+      <c r="H50" s="210"/>
+      <c r="I50" s="210"/>
+      <c r="J50" s="210"/>
+      <c r="K50" s="210"/>
+      <c r="L50" s="210"/>
+      <c r="M50" s="210"/>
+      <c r="N50" s="210"/>
+      <c r="O50" s="210"/>
+      <c r="P50" s="210"/>
+      <c r="Q50" s="210"/>
+      <c r="R50" s="210"/>
+      <c r="S50" s="210"/>
+      <c r="T50" s="210"/>
+      <c r="U50" s="210"/>
+      <c r="V50" s="210"/>
+      <c r="W50" s="210"/>
+      <c r="X50" s="210"/>
+      <c r="Y50" s="210"/>
+      <c r="Z50" s="210"/>
+      <c r="AA50" s="210"/>
+      <c r="AB50" s="210"/>
+      <c r="AC50" s="210"/>
+      <c r="AD50" s="210"/>
+      <c r="AE50" s="210"/>
+      <c r="AF50" s="210"/>
+      <c r="AG50" s="210"/>
+    </row>
+    <row r="51" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="196" t="s">
+        <v>214</v>
+      </c>
+      <c r="B52" s="174"/>
+      <c r="C52" s="174"/>
+      <c r="D52" s="174"/>
+      <c r="E52" s="174"/>
+      <c r="F52" s="174"/>
+      <c r="G52" s="174"/>
+      <c r="H52" s="174"/>
+      <c r="I52" s="174"/>
+      <c r="J52" s="174"/>
+      <c r="K52" s="174"/>
+      <c r="L52" s="174"/>
+    </row>
+    <row r="53" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="203" t="s">
+        <v>215</v>
+      </c>
+      <c r="B53" s="174"/>
+      <c r="C53" s="174"/>
+      <c r="D53" s="174"/>
+      <c r="E53" s="174"/>
+      <c r="F53" s="174"/>
+      <c r="G53" s="174"/>
+      <c r="H53" s="174"/>
+      <c r="I53" s="174"/>
+      <c r="J53" s="174"/>
+      <c r="K53" s="174"/>
+      <c r="L53" s="174"/>
+    </row>
+    <row r="54" spans="1:36" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="226" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" s="226" t="s">
+        <v>168</v>
+      </c>
+      <c r="C54" s="226" t="s">
+        <v>220</v>
+      </c>
+      <c r="D54" s="226" t="s">
+        <v>221</v>
+      </c>
+      <c r="E54" s="226" t="s">
+        <v>216</v>
+      </c>
+      <c r="F54" s="226" t="s">
+        <v>217</v>
+      </c>
+      <c r="G54" s="226" t="s">
+        <v>222</v>
+      </c>
+      <c r="H54" s="226" t="s">
+        <v>223</v>
+      </c>
+      <c r="I54" s="226" t="s">
+        <v>216</v>
+      </c>
+      <c r="J54" s="226" t="s">
+        <v>217</v>
+      </c>
+      <c r="K54" s="226" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" s="187">
+        <f>B62</f>
+        <v>253384.43615467878</v>
+      </c>
+      <c r="D55" s="187">
+        <f>D48</f>
+        <v>136839.65777514293</v>
+      </c>
+      <c r="E55" s="187">
+        <f>D55-C55</f>
+        <v>-116544.77837953586</v>
+      </c>
+      <c r="F55" s="227">
+        <f>E55/C55</f>
+        <v>-0.45995239545175132</v>
+      </c>
+      <c r="G55" s="187">
+        <f>E62</f>
+        <v>272119.91517411894</v>
+      </c>
+      <c r="H55" s="187">
+        <f>G48</f>
+        <v>127121.78002267367</v>
+      </c>
+      <c r="I55" s="187">
+        <f>H55-G55</f>
+        <v>-144998.13515144528</v>
+      </c>
+      <c r="J55" s="227">
+        <f>I55/G55</f>
+        <v>-0.53284646608340525</v>
+      </c>
+      <c r="K55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>211</v>
+      </c>
+      <c r="B56" t="s">
+        <v>198</v>
+      </c>
+      <c r="C56" s="187">
+        <f>B60</f>
+        <v>272875.18454364559</v>
+      </c>
+      <c r="D56" s="187">
+        <f>D49</f>
+        <v>221480.34275964473</v>
+      </c>
+      <c r="E56" s="187">
+        <f>D56-C56</f>
+        <v>-51394.841784000862</v>
+      </c>
+      <c r="F56" s="227">
+        <f>E56/C56</f>
+        <v>-0.18834560522589552</v>
+      </c>
+      <c r="G56" s="187">
+        <f>E60</f>
+        <v>279096.37947464635</v>
+      </c>
+      <c r="H56" s="187">
+        <f>G49</f>
+        <v>195492.9740683595</v>
+      </c>
+      <c r="I56" s="187">
+        <f>H56-G56</f>
+        <v>-83603.405406286853</v>
+      </c>
+      <c r="J56" s="227">
+        <f>I56/G56</f>
+        <v>-0.29955030432016599</v>
+      </c>
+      <c r="K56" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="187"/>
+      <c r="D57" s="187"/>
+      <c r="E57" s="187"/>
+      <c r="F57" s="227"/>
+      <c r="G57" s="187"/>
+      <c r="H57" s="187"/>
+      <c r="I57" s="187"/>
+      <c r="J57" s="227"/>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" s="188" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>218</v>
+      </c>
+      <c r="B59">
+        <v>2021</v>
+      </c>
+      <c r="C59">
+        <v>2022</v>
+      </c>
+      <c r="D59">
+        <v>2023</v>
+      </c>
+      <c r="E59">
+        <v>2024</v>
+      </c>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+      <c r="S59"/>
+      <c r="T59"/>
+      <c r="U59"/>
+      <c r="V59"/>
+      <c r="W59"/>
+      <c r="X59"/>
+      <c r="Y59"/>
+      <c r="Z59"/>
+      <c r="AA59"/>
+      <c r="AB59"/>
+      <c r="AC59"/>
+      <c r="AD59"/>
+      <c r="AE59"/>
+      <c r="AF59"/>
+      <c r="AG59"/>
+      <c r="AH59"/>
+      <c r="AI59"/>
+      <c r="AJ59"/>
+    </row>
+    <row r="60" spans="1:36" s="189" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="189" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="189">
+        <v>272875.18454364559</v>
+      </c>
+      <c r="C60" s="189">
+        <v>306691.70357876847</v>
+      </c>
+      <c r="D60" s="189">
+        <v>303546.34355618269</v>
+      </c>
+      <c r="E60" s="189">
+        <v>279096.37947464635</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" s="188" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61">
+        <v>2021</v>
+      </c>
+      <c r="C61">
+        <v>2022</v>
+      </c>
+      <c r="D61">
+        <v>2023</v>
+      </c>
+      <c r="E61">
+        <v>2024</v>
+      </c>
+      <c r="F61">
+        <v>2025</v>
+      </c>
+      <c r="G61">
+        <v>2026</v>
+      </c>
+      <c r="H61">
+        <v>2027</v>
+      </c>
+      <c r="I61">
+        <v>2028</v>
+      </c>
+      <c r="J61">
+        <v>2029</v>
+      </c>
+      <c r="K61">
+        <v>2030</v>
+      </c>
+      <c r="L61">
+        <v>2031</v>
+      </c>
+      <c r="M61">
+        <v>2032</v>
+      </c>
+      <c r="N61">
+        <v>2033</v>
+      </c>
+      <c r="O61">
+        <v>2034</v>
+      </c>
+      <c r="P61">
+        <v>2035</v>
+      </c>
+      <c r="Q61">
+        <v>2036</v>
+      </c>
+      <c r="R61">
+        <v>2037</v>
+      </c>
+      <c r="S61">
+        <v>2038</v>
+      </c>
+      <c r="T61">
+        <v>2039</v>
+      </c>
+      <c r="U61">
+        <v>2040</v>
+      </c>
+      <c r="V61">
+        <v>2041</v>
+      </c>
+      <c r="W61">
+        <v>2042</v>
+      </c>
+      <c r="X61">
+        <v>2043</v>
+      </c>
+      <c r="Y61">
+        <v>2044</v>
+      </c>
+      <c r="Z61">
+        <v>2045</v>
+      </c>
+      <c r="AA61">
+        <v>2046</v>
+      </c>
+      <c r="AB61">
+        <v>2047</v>
+      </c>
+      <c r="AC61">
+        <v>2048</v>
+      </c>
+      <c r="AD61">
+        <v>2049</v>
+      </c>
+      <c r="AE61">
+        <v>2050</v>
+      </c>
+      <c r="AF61"/>
+      <c r="AG61"/>
+    </row>
+    <row r="62" spans="1:36" s="189" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="189" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="189">
+        <v>253384.43615467878</v>
+      </c>
+      <c r="C62" s="189">
+        <v>284785.53121122846</v>
+      </c>
+      <c r="D62" s="189">
+        <v>281864.83588615071</v>
+      </c>
+      <c r="E62" s="189">
+        <v>272119.91517411894</v>
+      </c>
+      <c r="F62" s="189">
+        <v>244267.93200601047</v>
+      </c>
+      <c r="G62" s="189">
+        <v>245045.09148289612</v>
+      </c>
+      <c r="H62" s="189">
+        <v>245896.5501406297</v>
+      </c>
+      <c r="I62" s="189">
+        <v>246831.28958028281</v>
+      </c>
+      <c r="J62" s="189">
+        <v>247859.79983015926</v>
+      </c>
+      <c r="K62" s="189">
+        <v>248994.40989292334</v>
+      </c>
+      <c r="L62" s="189">
+        <v>247303.59777741029</v>
+      </c>
+      <c r="M62" s="189">
+        <v>245600.17607833183</v>
+      </c>
+      <c r="N62" s="189">
+        <v>243883.65354072856</v>
+      </c>
+      <c r="O62" s="189">
+        <v>242153.5130555816</v>
+      </c>
+      <c r="P62" s="189">
+        <v>240409.20993631281</v>
+      </c>
+      <c r="Q62" s="189">
+        <v>238650.17005554074</v>
+      </c>
+      <c r="R62" s="189">
+        <v>236875.78782870833</v>
+      </c>
+      <c r="S62" s="189">
+        <v>235085.42402968768</v>
+      </c>
+      <c r="T62" s="189">
+        <v>233278.40342179779</v>
+      </c>
+      <c r="U62" s="189">
+        <v>231454.01218578266</v>
+      </c>
+      <c r="V62" s="189">
+        <v>229611.49512414529</v>
+      </c>
+      <c r="W62" s="189">
+        <v>227750.05261882479</v>
+      </c>
+      <c r="X62" s="189">
+        <v>225868.83731644039</v>
+      </c>
+      <c r="Y62" s="189">
+        <v>223966.95051221756</v>
+      </c>
+      <c r="Z62" s="189">
+        <v>222043.43820014191</v>
+      </c>
+      <c r="AA62" s="189">
+        <v>220097.2867528405</v>
+      </c>
+      <c r="AB62" s="189">
+        <v>218127.41819005259</v>
+      </c>
+      <c r="AC62" s="189">
+        <v>216132.68498924136</v>
+      </c>
+      <c r="AD62" s="189">
+        <v>214111.864385811</v>
+      </c>
+      <c r="AE62" s="189">
+        <v>212063.65210338513</v>
+      </c>
+    </row>
+    <row r="63" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A45:AG45"/>
+    <mergeCell ref="A46:AG46"/>
+    <mergeCell ref="A50:AG50"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
+  <phoneticPr fontId="22" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734360E0-DC8F-4FFB-9748-D4950767514E}">
   <dimension ref="A1:DD222"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="4" max="4" width="36.5" customWidth="1"/>
+    <col min="5" max="5" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="12.5" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:108" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+    <row r="1" spans="1:108" s="40" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="165" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="M1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="M1" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2"/>
       <c r="B2"/>
       <c r="C2"/>
@@ -4931,7 +7269,7 @@
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
       <c r="L2" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M2" s="41"/>
       <c r="N2" s="41"/>
@@ -5030,7 +7368,7 @@
       <c r="DC2" s="41"/>
       <c r="DD2" s="41"/>
     </row>
-    <row r="3" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3"/>
@@ -5038,17 +7376,17 @@
       <c r="E3"/>
       <c r="F3"/>
       <c r="L3" s="43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="44"/>
-      <c r="L4" s="143" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L5" s="144"/>
+      <c r="L4" s="166" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="167"/>
     </row>
     <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H6" s="45"/>
@@ -5078,25 +7416,25 @@
     </row>
     <row r="7" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="161" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="145" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="145"/>
-      <c r="K7" s="145"/>
-      <c r="L7" s="145"/>
-      <c r="M7" s="145"/>
-      <c r="N7" s="145"/>
-      <c r="O7" s="145"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
@@ -5112,64 +7450,64 @@
     <row r="8" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="O8" s="52"/>
     </row>
-    <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9"/>
-      <c r="B9" s="146" t="s">
+      <c r="B9" s="168" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="169" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="147" t="s">
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="172">
+        <v>2022</v>
+      </c>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="174"/>
+      <c r="L9" s="174"/>
+    </row>
+    <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="168"/>
+      <c r="D10" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="J10" s="52"/>
+    </row>
+    <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="168"/>
+      <c r="D11" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="148"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="150">
-        <v>2021</v>
-      </c>
-      <c r="H9" s="151"/>
-      <c r="I9" s="151"/>
-      <c r="J9" s="151"/>
-      <c r="K9" s="152"/>
-      <c r="L9" s="152"/>
-    </row>
-    <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="146"/>
-      <c r="D10" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="52"/>
-    </row>
-    <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="146"/>
-      <c r="D11" s="153" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="154"/>
-      <c r="K11" s="154"/>
-      <c r="L11" s="154"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
       <c r="W11" s="54"/>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
       <c r="Z11" s="55"/>
       <c r="AA11" s="55"/>
     </row>
-    <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="146"/>
-      <c r="D12" s="155" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="157"/>
+    <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="168"/>
+      <c r="D12" s="177" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="178"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="178"/>
+      <c r="H12" s="178"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="178"/>
+      <c r="K12" s="178"/>
+      <c r="L12" s="179"/>
       <c r="M12" s="56"/>
       <c r="W12" s="54"/>
       <c r="X12" s="55"/>
@@ -5177,79 +7515,79 @@
       <c r="Z12" s="55"/>
       <c r="AA12" s="55"/>
     </row>
-    <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="146"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="159"/>
-      <c r="G13" s="159"/>
-      <c r="H13" s="159"/>
-      <c r="I13" s="159"/>
-      <c r="J13" s="159"/>
-      <c r="K13" s="159"/>
-      <c r="L13" s="160"/>
+    <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="168"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="182"/>
       <c r="W13" s="54"/>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
       <c r="Z13" s="55"/>
       <c r="AA13" s="55"/>
     </row>
-    <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="146"/>
-    </row>
-    <row r="15" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B15" s="146"/>
-      <c r="C15" s="161" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="161"/>
-      <c r="E15" s="161"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="161"/>
-      <c r="I15" s="161"/>
-      <c r="J15" s="161"/>
-      <c r="K15" s="161"/>
-      <c r="L15" s="161"/>
-      <c r="M15" s="161"/>
-      <c r="N15" s="161"/>
-      <c r="O15" s="161"/>
-      <c r="P15" s="161"/>
+    <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="168"/>
+    </row>
+    <row r="15" spans="1:108" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="168"/>
+      <c r="C15" s="183" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="183"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="183"/>
       <c r="Q15" s="57"/>
     </row>
-    <row r="16" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B16" s="146"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="161"/>
-      <c r="E16" s="161"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="161"/>
-      <c r="I16" s="161"/>
-      <c r="J16" s="161"/>
-      <c r="K16" s="161"/>
-      <c r="L16" s="161"/>
-      <c r="M16" s="161"/>
-      <c r="N16" s="161"/>
-      <c r="O16" s="161"/>
-      <c r="P16" s="161"/>
-    </row>
-    <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="146"/>
+    <row r="16" spans="1:108" x14ac:dyDescent="0.3">
+      <c r="B16" s="168"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="183"/>
+      <c r="P16" s="183"/>
+    </row>
+    <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="168"/>
       <c r="C17" s="58"/>
-      <c r="D17" s="168" t="s">
-        <v>80</v>
+      <c r="D17" s="158" t="s">
+        <v>77</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="146"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="168"/>
       <c r="C18" s="58"/>
-      <c r="D18" s="169"/>
-      <c r="F18" s="1">
-        <v>2021</v>
+      <c r="D18" s="159"/>
+      <c r="F18" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="G18" s="1">
         <v>2022</v>
@@ -5339,12 +7677,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="146"/>
+    <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="168"/>
       <c r="C19" s="58"/>
-      <c r="D19" s="169"/>
+      <c r="D19" s="159"/>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" s="59">
         <v>322.051049922</v>
@@ -5437,12 +7775,12 @@
         <v>129.15171555556242</v>
       </c>
     </row>
-    <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="146"/>
+    <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="168"/>
       <c r="C20" s="58"/>
-      <c r="D20" s="170"/>
+      <c r="D20" s="160"/>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F20" s="59">
         <v>322.051049922</v>
@@ -5535,12 +7873,12 @@
         <v>157.23705301149212</v>
       </c>
     </row>
-    <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="146"/>
+    <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="168"/>
       <c r="C21" s="58"/>
-      <c r="D21" s="170"/>
+      <c r="D21" s="160"/>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F21" s="59">
         <v>322.051049922</v>
@@ -5633,10 +7971,10 @@
         <v>274.95897351378562</v>
       </c>
     </row>
-    <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="146"/>
+    <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="168"/>
       <c r="C22" s="58"/>
-      <c r="D22" s="170"/>
+      <c r="D22" s="160"/>
       <c r="F22" s="60"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5668,21 +8006,21 @@
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
     </row>
-    <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="146"/>
+    <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="168"/>
       <c r="C23" s="58"/>
-      <c r="D23" s="170"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F23" s="60"/>
     </row>
-    <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="146"/>
+    <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="168"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="170"/>
-      <c r="F24" s="1">
-        <v>2021</v>
+      <c r="D24" s="160"/>
+      <c r="F24" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="G24" s="1">
         <v>2022</v>
@@ -5772,12 +8110,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="146"/>
+    <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="168"/>
       <c r="C25" s="58"/>
-      <c r="D25" s="170"/>
+      <c r="D25" s="160"/>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F25" s="59">
         <v>299.04780031199999</v>
@@ -5870,12 +8208,12 @@
         <v>118.54336408357527</v>
       </c>
     </row>
-    <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="146"/>
+    <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="168"/>
       <c r="C26" s="58"/>
-      <c r="D26" s="170"/>
+      <c r="D26" s="160"/>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F26" s="59">
         <v>299.04780031199999</v>
@@ -5968,12 +8306,12 @@
         <v>270.30971238933148</v>
       </c>
     </row>
-    <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="146"/>
+    <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="168"/>
       <c r="C27" s="58"/>
-      <c r="D27" s="170"/>
+      <c r="D27" s="160"/>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F27" s="59">
         <v>299.04780031199999</v>
@@ -6066,8 +8404,8 @@
         <v>291.72086922260991</v>
       </c>
     </row>
-    <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="146"/>
+    <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="168"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="G28" s="5"/>
@@ -6104,12 +8442,12 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="146"/>
+    <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="168"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
       <c r="E29" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
@@ -6146,8 +8484,8 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="146"/>
+    <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="168"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="1"/>
@@ -6186,26 +8524,26 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="146"/>
+    <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="168"/>
       <c r="C31" s="58"/>
-      <c r="D31" s="169" t="s">
+      <c r="D31" s="159" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="E31" s="61" t="s">
+      <c r="H31" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="62" t="s">
+      <c r="I31" s="63" t="s">
         <v>89</v>
-      </c>
-      <c r="G31" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" s="63" t="s">
-        <v>92</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="64"/>
@@ -6238,24 +8576,24 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="146"/>
+    <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="168"/>
       <c r="C32" s="58"/>
-      <c r="D32" s="169"/>
+      <c r="D32" s="159"/>
       <c r="E32" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="F32" s="67" t="s">
+      <c r="I32" s="68" t="s">
         <v>94</v>
-      </c>
-      <c r="G32" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="H32" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="I32" s="68" t="s">
-        <v>97</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="64"/>
@@ -6288,24 +8626,24 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="146"/>
+    <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="168"/>
       <c r="C33" s="58"/>
-      <c r="D33" s="169"/>
+      <c r="D33" s="159"/>
       <c r="E33" s="69" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F33" s="70" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G33" s="70" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H33" s="70" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I33" s="71" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="64"/>
@@ -6338,24 +8676,24 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="146"/>
+    <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="168"/>
       <c r="C34" s="58"/>
-      <c r="D34" s="169"/>
+      <c r="D34" s="159"/>
       <c r="E34" s="72" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F34" s="73" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G34" s="73" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H34" s="73" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I34" s="74" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="64"/>
@@ -6388,24 +8726,24 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="146"/>
+    <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="168"/>
       <c r="C35" s="58"/>
-      <c r="D35" s="169"/>
+      <c r="D35" s="159"/>
       <c r="E35" s="69" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F35" s="70" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G35" s="70" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H35" s="70" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I35" s="71" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="64"/>
@@ -6438,24 +8776,24 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="146"/>
+    <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="168"/>
       <c r="C36" s="58"/>
-      <c r="D36" s="169"/>
+      <c r="D36" s="159"/>
       <c r="E36" s="75" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G36" s="76" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H36" s="76" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I36" s="77" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="64"/>
@@ -6488,7 +8826,7 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="58"/>
       <c r="D37" s="58"/>
       <c r="E37" s="1"/>
@@ -6528,23 +8866,23 @@
       <c r="AM37" s="5"/>
     </row>
     <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="145" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" s="145"/>
-      <c r="E38" s="145"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="145"/>
-      <c r="H38" s="145"/>
-      <c r="I38" s="145"/>
-      <c r="J38" s="145"/>
-      <c r="K38" s="145"/>
-      <c r="L38" s="145"/>
-      <c r="M38" s="145"/>
-      <c r="N38" s="145"/>
-      <c r="O38" s="145"/>
-      <c r="P38" s="145"/>
-      <c r="Q38" s="145"/>
+      <c r="C38" s="161" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
+      <c r="P38" s="161"/>
+      <c r="Q38" s="161"/>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
       <c r="T38" s="50"/>
@@ -6574,19 +8912,19 @@
       <c r="AR38" s="78"/>
     </row>
     <row r="39" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:74" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D40" s="53" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="2:74" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="2:74" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="G42" s="1">
-        <v>2021</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="G42" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="H42" s="1">
         <v>2022</v>
@@ -6676,18 +9014,18 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="177" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="168" t="s">
-        <v>109</v>
+    <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="163" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="158" t="s">
+        <v>105</v>
       </c>
       <c r="E43" s="79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F43" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G43" s="81">
         <f>F19*2+F25</f>
@@ -6781,14 +9119,14 @@
         <v>376.84679519470012</v>
       </c>
     </row>
-    <row r="44" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B44" s="177"/>
-      <c r="D44" s="169"/>
+    <row r="44" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B44" s="163"/>
+      <c r="D44" s="159"/>
       <c r="E44" s="82" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F44" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G44" s="81">
         <f t="shared" ref="G44:G45" si="0">F20*2+F26</f>
@@ -6882,14 +9220,14 @@
         <v>584.78381841231567</v>
       </c>
     </row>
-    <row r="45" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B45" s="177"/>
-      <c r="D45" s="169"/>
+    <row r="45" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B45" s="163"/>
+      <c r="D45" s="159"/>
       <c r="E45" s="83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F45" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G45" s="81">
         <f t="shared" si="0"/>
@@ -6983,14 +9321,14 @@
         <v>841.63881625018121</v>
       </c>
     </row>
-    <row r="46" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B46" s="177"/>
-      <c r="D46" s="170"/>
+    <row r="46" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B46" s="163"/>
+      <c r="D46" s="160"/>
       <c r="E46" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F46" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G46" s="81">
         <f>F19*4+F25</f>
@@ -7117,14 +9455,14 @@
       <c r="BU46" s="5"/>
       <c r="BV46" s="5"/>
     </row>
-    <row r="47" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B47" s="177"/>
-      <c r="D47" s="170"/>
+    <row r="47" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B47" s="163"/>
+      <c r="D47" s="160"/>
       <c r="E47" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F47" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G47" s="81">
         <f>F20*4+F26</f>
@@ -7251,14 +9589,14 @@
       <c r="BU47" s="5"/>
       <c r="BV47" s="5"/>
     </row>
-    <row r="48" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B48" s="177"/>
-      <c r="D48" s="170"/>
+    <row r="48" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B48" s="163"/>
+      <c r="D48" s="160"/>
       <c r="E48" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F48" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G48" s="81">
         <f t="shared" ref="G48" si="1">F21*4+F27</f>
@@ -7385,14 +9723,14 @@
       <c r="BU48" s="5"/>
       <c r="BV48" s="5"/>
     </row>
-    <row r="49" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B49" s="177"/>
-      <c r="D49" s="170"/>
+    <row r="49" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B49" s="163"/>
+      <c r="D49" s="160"/>
       <c r="E49" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F49" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G49" s="81">
         <f t="shared" ref="G49:G51" si="2">F19*6+F25</f>
@@ -7519,14 +9857,14 @@
       <c r="BU49" s="5"/>
       <c r="BV49" s="5"/>
     </row>
-    <row r="50" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B50" s="177"/>
-      <c r="D50" s="170"/>
+    <row r="50" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B50" s="163"/>
+      <c r="D50" s="160"/>
       <c r="E50" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F50" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G50" s="81">
         <f t="shared" si="2"/>
@@ -7653,14 +9991,14 @@
       <c r="BU50" s="5"/>
       <c r="BV50" s="5"/>
     </row>
-    <row r="51" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B51" s="177"/>
-      <c r="D51" s="170"/>
+    <row r="51" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B51" s="163"/>
+      <c r="D51" s="160"/>
       <c r="E51" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F51" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G51" s="81">
         <f t="shared" si="2"/>
@@ -7787,14 +10125,14 @@
       <c r="BU51" s="5"/>
       <c r="BV51" s="5"/>
     </row>
-    <row r="52" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B52" s="177"/>
-      <c r="D52" s="170"/>
+    <row r="52" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B52" s="163"/>
+      <c r="D52" s="160"/>
       <c r="E52" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F52" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G52" s="81">
         <f t="shared" ref="G52:G54" si="3">F19*8+F25</f>
@@ -7921,14 +10259,14 @@
       <c r="BU52" s="5"/>
       <c r="BV52" s="5"/>
     </row>
-    <row r="53" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B53" s="177"/>
-      <c r="D53" s="170"/>
+    <row r="53" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B53" s="163"/>
+      <c r="D53" s="160"/>
       <c r="E53" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F53" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G53" s="81">
         <f t="shared" si="3"/>
@@ -8055,14 +10393,14 @@
       <c r="BU53" s="5"/>
       <c r="BV53" s="5"/>
     </row>
-    <row r="54" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B54" s="177"/>
-      <c r="D54" s="170"/>
+    <row r="54" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B54" s="163"/>
+      <c r="D54" s="160"/>
       <c r="E54" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F54" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G54" s="81">
         <f t="shared" si="3"/>
@@ -8189,14 +10527,14 @@
       <c r="BU54" s="5"/>
       <c r="BV54" s="5"/>
     </row>
-    <row r="55" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B55" s="177"/>
-      <c r="D55" s="170"/>
+    <row r="55" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B55" s="163"/>
+      <c r="D55" s="160"/>
       <c r="E55" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F55" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G55" s="81">
         <f t="shared" ref="G55:G57" si="4">F19*10+F25</f>
@@ -8323,14 +10661,14 @@
       <c r="BU55" s="5"/>
       <c r="BV55" s="5"/>
     </row>
-    <row r="56" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B56" s="177"/>
-      <c r="D56" s="170"/>
+    <row r="56" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B56" s="163"/>
+      <c r="D56" s="160"/>
       <c r="E56" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F56" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G56" s="81">
         <f t="shared" si="4"/>
@@ -8457,14 +10795,14 @@
       <c r="BU56" s="5"/>
       <c r="BV56" s="5"/>
     </row>
-    <row r="57" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B57" s="177"/>
-      <c r="D57" s="170"/>
+    <row r="57" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B57" s="163"/>
+      <c r="D57" s="160"/>
       <c r="E57" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F57" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G57" s="81">
         <f t="shared" si="4"/>
@@ -8591,8 +10929,8 @@
       <c r="BU57" s="5"/>
       <c r="BV57" s="5"/>
     </row>
-    <row r="58" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B58" s="177"/>
+    <row r="58" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B58" s="163"/>
       <c r="D58" s="58"/>
       <c r="E58" s="82"/>
       <c r="F58" s="82"/>
@@ -8660,8 +10998,8 @@
       <c r="BU58" s="5"/>
       <c r="BV58" s="5"/>
     </row>
-    <row r="59" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B59" s="177"/>
+    <row r="59" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B59" s="163"/>
       <c r="D59" s="58"/>
       <c r="E59" s="82"/>
       <c r="F59" s="82"/>
@@ -8729,8 +11067,8 @@
       <c r="BU59" s="5"/>
       <c r="BV59" s="5"/>
     </row>
-    <row r="60" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B60" s="177"/>
+    <row r="60" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B60" s="163"/>
       <c r="D60" s="58"/>
       <c r="E60" s="82"/>
       <c r="F60" s="82"/>
@@ -8798,13 +11136,13 @@
       <c r="BU60" s="5"/>
       <c r="BV60" s="5"/>
     </row>
-    <row r="61" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B61" s="177"/>
+    <row r="61" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B61" s="163"/>
       <c r="D61" s="84"/>
       <c r="E61" s="82"/>
       <c r="F61" s="82"/>
-      <c r="G61" s="1">
-        <v>2021</v>
+      <c r="G61" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="H61" s="1">
         <v>2022</v>
@@ -8894,16 +11232,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="62" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B62" s="177"/>
-      <c r="D62" s="168" t="s">
-        <v>110</v>
+    <row r="62" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B62" s="163"/>
+      <c r="D62" s="158" t="s">
+        <v>106</v>
       </c>
       <c r="E62" s="79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F62" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G62" s="81">
         <f t="shared" ref="G62:G70" si="5">0.025*G43</f>
@@ -8997,14 +11335,14 @@
         <v>9.4211698798675041</v>
       </c>
     </row>
-    <row r="63" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B63" s="177"/>
-      <c r="D63" s="169"/>
+    <row r="63" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B63" s="163"/>
+      <c r="D63" s="159"/>
       <c r="E63" s="82" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F63" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G63" s="81">
         <f t="shared" si="5"/>
@@ -9098,14 +11436,14 @@
         <v>14.619595460307892</v>
       </c>
     </row>
-    <row r="64" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B64" s="177"/>
-      <c r="D64" s="169"/>
+    <row r="64" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B64" s="163"/>
+      <c r="D64" s="159"/>
       <c r="E64" s="83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F64" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G64" s="81">
         <f t="shared" si="5"/>
@@ -9199,14 +11537,14 @@
         <v>21.04097040625453</v>
       </c>
     </row>
-    <row r="65" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B65" s="177"/>
-      <c r="D65" s="170"/>
+    <row r="65" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B65" s="163"/>
+      <c r="D65" s="160"/>
       <c r="E65" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F65" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G65" s="81">
         <f t="shared" si="5"/>
@@ -9300,14 +11638,14 @@
         <v>15.878755657645625</v>
       </c>
     </row>
-    <row r="66" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B66" s="177"/>
-      <c r="D66" s="170"/>
+    <row r="66" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B66" s="163"/>
+      <c r="D66" s="160"/>
       <c r="E66" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F66" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G66" s="81">
         <f t="shared" si="5"/>
@@ -9401,14 +11739,14 @@
         <v>22.4814481108825</v>
       </c>
     </row>
-    <row r="67" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B67" s="177"/>
-      <c r="D67" s="170"/>
+    <row r="67" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B67" s="163"/>
+      <c r="D67" s="160"/>
       <c r="E67" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F67" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G67" s="81">
         <f t="shared" si="5"/>
@@ -9502,14 +11840,14 @@
         <v>34.78891908194381</v>
       </c>
     </row>
-    <row r="68" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B68" s="177"/>
-      <c r="D68" s="170"/>
+    <row r="68" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B68" s="163"/>
+      <c r="D68" s="160"/>
       <c r="E68" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F68" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G68" s="81">
         <f t="shared" si="5"/>
@@ -9603,14 +11941,14 @@
         <v>22.336341435423748</v>
       </c>
     </row>
-    <row r="69" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B69" s="177"/>
-      <c r="D69" s="170"/>
+    <row r="69" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B69" s="163"/>
+      <c r="D69" s="160"/>
       <c r="E69" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F69" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G69" s="81">
         <f t="shared" si="5"/>
@@ -9704,14 +12042,14 @@
         <v>30.343300761457108</v>
       </c>
     </row>
-    <row r="70" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B70" s="177"/>
-      <c r="D70" s="170"/>
+    <row r="70" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B70" s="163"/>
+      <c r="D70" s="160"/>
       <c r="E70" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F70" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G70" s="81">
         <f t="shared" si="5"/>
@@ -9805,14 +12143,14 @@
         <v>48.536867757633097</v>
       </c>
     </row>
-    <row r="71" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B71" s="177"/>
-      <c r="D71" s="170"/>
+    <row r="71" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B71" s="163"/>
+      <c r="D71" s="160"/>
       <c r="E71" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F71" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G71" s="81">
         <f t="shared" ref="G71:G76" si="6">0.025*G52</f>
@@ -9939,14 +12277,14 @@
       <c r="BU71" s="5"/>
       <c r="BV71" s="5"/>
     </row>
-    <row r="72" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B72" s="177"/>
-      <c r="D72" s="170"/>
+    <row r="72" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B72" s="163"/>
+      <c r="D72" s="160"/>
       <c r="E72" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F72" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G72" s="81">
         <f t="shared" si="6"/>
@@ -10073,14 +12411,14 @@
       <c r="BU72" s="5"/>
       <c r="BV72" s="5"/>
     </row>
-    <row r="73" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B73" s="177"/>
-      <c r="D73" s="170"/>
+    <row r="73" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B73" s="163"/>
+      <c r="D73" s="160"/>
       <c r="E73" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F73" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G73" s="81">
         <f t="shared" si="6"/>
@@ -10207,14 +12545,14 @@
       <c r="BU73" s="5"/>
       <c r="BV73" s="5"/>
     </row>
-    <row r="74" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B74" s="177"/>
-      <c r="D74" s="170"/>
+    <row r="74" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B74" s="163"/>
+      <c r="D74" s="160"/>
       <c r="E74" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F74" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G74" s="81">
         <f t="shared" si="6"/>
@@ -10341,14 +12679,14 @@
       <c r="BU74" s="5"/>
       <c r="BV74" s="5"/>
     </row>
-    <row r="75" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B75" s="177"/>
-      <c r="D75" s="170"/>
+    <row r="75" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B75" s="163"/>
+      <c r="D75" s="160"/>
       <c r="E75" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F75" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G75" s="81">
         <f t="shared" si="6"/>
@@ -10475,14 +12813,14 @@
       <c r="BU75" s="5"/>
       <c r="BV75" s="5"/>
     </row>
-    <row r="76" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B76" s="177"/>
-      <c r="D76" s="170"/>
+    <row r="76" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B76" s="163"/>
+      <c r="D76" s="160"/>
       <c r="E76" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F76" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G76" s="81">
         <f t="shared" si="6"/>
@@ -10609,19 +12947,19 @@
       <c r="BU76" s="5"/>
       <c r="BV76" s="5"/>
     </row>
-    <row r="77" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B77" s="177"/>
+    <row r="77" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B77" s="163"/>
       <c r="D77" s="84"/>
       <c r="E77" s="82"/>
       <c r="F77" s="82"/>
     </row>
-    <row r="78" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B78" s="177"/>
+    <row r="78" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B78" s="163"/>
       <c r="D78" s="40"/>
       <c r="E78" s="85"/>
       <c r="F78" s="85"/>
-      <c r="G78" s="1">
-        <v>2021</v>
+      <c r="G78" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="H78" s="1">
         <v>2022</v>
@@ -10711,16 +13049,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="79" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B79" s="177"/>
-      <c r="D79" s="168" t="s">
-        <v>111</v>
+    <row r="79" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B79" s="163"/>
+      <c r="D79" s="158" t="s">
+        <v>107</v>
       </c>
       <c r="E79" s="79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F79" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G79" s="59">
         <v>0</v>
@@ -10814,14 +13152,14 @@
       </c>
       <c r="AO79" s="1"/>
     </row>
-    <row r="80" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B80" s="177"/>
-      <c r="D80" s="169"/>
+    <row r="80" spans="2:74" x14ac:dyDescent="0.3">
+      <c r="B80" s="163"/>
+      <c r="D80" s="159"/>
       <c r="E80" s="82" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F80" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G80" s="59">
         <v>0</v>
@@ -10915,14 +13253,14 @@
       </c>
       <c r="AO80" s="1"/>
     </row>
-    <row r="81" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B81" s="177"/>
-      <c r="D81" s="169"/>
+    <row r="81" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B81" s="163"/>
+      <c r="D81" s="159"/>
       <c r="E81" s="83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F81" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G81" s="59">
         <v>0</v>
@@ -11016,14 +13354,14 @@
       </c>
       <c r="AO81" s="1"/>
     </row>
-    <row r="82" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B82" s="178"/>
-      <c r="D82" s="170"/>
+    <row r="82" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B82" s="164"/>
+      <c r="D82" s="160"/>
       <c r="E82" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F82" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G82" s="59">
         <v>0</v>
@@ -11116,14 +13454,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B83" s="178"/>
-      <c r="D83" s="170"/>
+    <row r="83" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B83" s="164"/>
+      <c r="D83" s="160"/>
       <c r="E83" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F83" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G83" s="59">
         <v>0</v>
@@ -11216,14 +13554,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B84" s="178"/>
-      <c r="D84" s="170"/>
+    <row r="84" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B84" s="164"/>
+      <c r="D84" s="160"/>
       <c r="E84" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F84" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G84" s="59">
         <v>0</v>
@@ -11318,14 +13656,14 @@
       <c r="AK84" s="5"/>
       <c r="AL84" s="5"/>
     </row>
-    <row r="85" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B85" s="178"/>
-      <c r="D85" s="170"/>
+    <row r="85" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B85" s="164"/>
+      <c r="D85" s="160"/>
       <c r="E85" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F85" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G85" s="59">
         <v>0</v>
@@ -11420,14 +13758,14 @@
       <c r="AK85" s="5"/>
       <c r="AL85" s="5"/>
     </row>
-    <row r="86" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B86" s="178"/>
-      <c r="D86" s="170"/>
+    <row r="86" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B86" s="164"/>
+      <c r="D86" s="160"/>
       <c r="E86" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F86" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G86" s="59">
         <v>0</v>
@@ -11522,14 +13860,14 @@
       <c r="AK86" s="5"/>
       <c r="AL86" s="5"/>
     </row>
-    <row r="87" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B87" s="178"/>
-      <c r="D87" s="170"/>
+    <row r="87" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B87" s="164"/>
+      <c r="D87" s="160"/>
       <c r="E87" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F87" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G87" s="59">
         <v>0</v>
@@ -11624,14 +13962,14 @@
       <c r="AK87" s="5"/>
       <c r="AL87" s="5"/>
     </row>
-    <row r="88" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B88" s="178"/>
-      <c r="D88" s="170"/>
+    <row r="88" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B88" s="164"/>
+      <c r="D88" s="160"/>
       <c r="E88" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F88" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G88" s="59">
         <v>0</v>
@@ -11726,14 +14064,14 @@
       <c r="AK88" s="5"/>
       <c r="AL88" s="5"/>
     </row>
-    <row r="89" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B89" s="178"/>
-      <c r="D89" s="170"/>
+    <row r="89" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B89" s="164"/>
+      <c r="D89" s="160"/>
       <c r="E89" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F89" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G89" s="59">
         <v>0</v>
@@ -11828,14 +14166,14 @@
       <c r="AK89" s="5"/>
       <c r="AL89" s="5"/>
     </row>
-    <row r="90" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B90" s="178"/>
-      <c r="D90" s="170"/>
+    <row r="90" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B90" s="164"/>
+      <c r="D90" s="160"/>
       <c r="E90" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F90" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G90" s="59">
         <v>0</v>
@@ -11930,14 +14268,14 @@
       <c r="AK90" s="5"/>
       <c r="AL90" s="5"/>
     </row>
-    <row r="91" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B91" s="178"/>
-      <c r="D91" s="170"/>
+    <row r="91" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B91" s="164"/>
+      <c r="D91" s="160"/>
       <c r="E91" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F91" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G91" s="59">
         <v>0</v>
@@ -12032,14 +14370,14 @@
       <c r="AK91" s="5"/>
       <c r="AL91" s="5"/>
     </row>
-    <row r="92" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B92" s="178"/>
-      <c r="D92" s="170"/>
+    <row r="92" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B92" s="164"/>
+      <c r="D92" s="160"/>
       <c r="E92" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F92" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G92" s="59">
         <v>0</v>
@@ -12134,14 +14472,14 @@
       <c r="AK92" s="5"/>
       <c r="AL92" s="5"/>
     </row>
-    <row r="93" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B93" s="178"/>
-      <c r="D93" s="170"/>
+    <row r="93" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B93" s="164"/>
+      <c r="D93" s="160"/>
       <c r="E93" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F93" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G93" s="59">
         <v>0</v>
@@ -12236,13 +14574,13 @@
       <c r="AK93" s="5"/>
       <c r="AL93" s="5"/>
     </row>
-    <row r="94" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B94" s="178"/>
-    </row>
-    <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="178"/>
-      <c r="G95" s="1">
-        <v>2021</v>
+    <row r="94" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B94" s="164"/>
+    </row>
+    <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B95" s="164"/>
+      <c r="G95" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="H95" s="1">
         <v>2022</v>
@@ -12332,16 +14670,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="96" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B96" s="178"/>
-      <c r="D96" s="168" t="s">
-        <v>112</v>
+    <row r="96" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B96" s="164"/>
+      <c r="D96" s="158" t="s">
+        <v>108</v>
       </c>
       <c r="E96" s="79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F96" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G96" s="86">
         <v>0.85</v>
@@ -12434,14 +14772,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="97" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B97" s="178"/>
-      <c r="D97" s="169"/>
+    <row r="97" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B97" s="164"/>
+      <c r="D97" s="159"/>
       <c r="E97" s="82" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F97" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G97" s="86">
         <v>0.85</v>
@@ -12534,14 +14872,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="98" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B98" s="178"/>
-      <c r="D98" s="169"/>
+    <row r="98" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B98" s="164"/>
+      <c r="D98" s="159"/>
       <c r="E98" s="83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F98" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G98" s="86">
         <v>0.85</v>
@@ -12634,14 +14972,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="99" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B99" s="178"/>
-      <c r="D99" s="170"/>
+    <row r="99" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B99" s="164"/>
+      <c r="D99" s="160"/>
       <c r="E99" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F99" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G99" s="86">
         <v>0.85</v>
@@ -12734,14 +15072,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="100" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B100" s="178"/>
-      <c r="D100" s="170"/>
+    <row r="100" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B100" s="164"/>
+      <c r="D100" s="160"/>
       <c r="E100" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F100" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G100" s="86">
         <v>0.85</v>
@@ -12834,14 +15172,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="101" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B101" s="178"/>
-      <c r="D101" s="170"/>
+    <row r="101" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B101" s="164"/>
+      <c r="D101" s="160"/>
       <c r="E101" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F101" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G101" s="86">
         <v>0.85</v>
@@ -12934,14 +15272,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="102" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B102" s="178"/>
-      <c r="D102" s="170"/>
+    <row r="102" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B102" s="164"/>
+      <c r="D102" s="160"/>
       <c r="E102" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F102" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G102" s="86">
         <v>0.85</v>
@@ -13034,14 +15372,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="103" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B103" s="178"/>
-      <c r="D103" s="170"/>
+    <row r="103" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B103" s="164"/>
+      <c r="D103" s="160"/>
       <c r="E103" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F103" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G103" s="86">
         <v>0.85</v>
@@ -13134,14 +15472,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="104" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B104" s="178"/>
-      <c r="D104" s="170"/>
+    <row r="104" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B104" s="164"/>
+      <c r="D104" s="160"/>
       <c r="E104" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F104" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G104" s="86">
         <v>0.85</v>
@@ -13234,14 +15572,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="105" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B105" s="178"/>
-      <c r="D105" s="170"/>
+    <row r="105" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B105" s="164"/>
+      <c r="D105" s="160"/>
       <c r="E105" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F105" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G105" s="86">
         <v>0.85</v>
@@ -13334,14 +15672,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="106" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B106" s="178"/>
-      <c r="D106" s="170"/>
+    <row r="106" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B106" s="164"/>
+      <c r="D106" s="160"/>
       <c r="E106" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F106" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G106" s="86">
         <v>0.85</v>
@@ -13434,14 +15772,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="107" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B107" s="178"/>
-      <c r="D107" s="170"/>
+    <row r="107" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B107" s="164"/>
+      <c r="D107" s="160"/>
       <c r="E107" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F107" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G107" s="86">
         <v>0.85</v>
@@ -13534,14 +15872,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="108" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B108" s="178"/>
-      <c r="D108" s="170"/>
+    <row r="108" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B108" s="164"/>
+      <c r="D108" s="160"/>
       <c r="E108" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F108" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G108" s="86">
         <v>0.85</v>
@@ -13634,14 +15972,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="109" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B109" s="178"/>
-      <c r="D109" s="170"/>
+    <row r="109" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B109" s="164"/>
+      <c r="D109" s="160"/>
       <c r="E109" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F109" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G109" s="86">
         <v>0.85</v>
@@ -13734,14 +16072,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="110" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B110" s="178"/>
-      <c r="D110" s="170"/>
+    <row r="110" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B110" s="164"/>
+      <c r="D110" s="160"/>
       <c r="E110" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F110" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G110" s="86">
         <v>0.85</v>
@@ -13834,13 +16172,13 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="111" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B111" s="178"/>
-    </row>
-    <row r="112" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B112" s="178"/>
-      <c r="G112" s="1">
-        <v>2021</v>
+    <row r="111" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B111" s="164"/>
+    </row>
+    <row r="112" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B112" s="164"/>
+      <c r="G112" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="H112" s="1">
         <v>2022</v>
@@ -13930,16 +16268,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="113" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B113" s="178"/>
-      <c r="D113" s="168" t="s">
-        <v>113</v>
+    <row r="113" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B113" s="164"/>
+      <c r="D113" s="158" t="s">
+        <v>109</v>
       </c>
       <c r="E113" s="79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F113" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G113" s="86">
         <f>2/24</f>
@@ -14033,14 +16371,14 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="114" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B114" s="178"/>
-      <c r="D114" s="169"/>
+    <row r="114" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B114" s="164"/>
+      <c r="D114" s="159"/>
       <c r="E114" s="82" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F114" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G114" s="86">
         <f t="shared" ref="G114:G115" si="7">2/24</f>
@@ -14134,14 +16472,14 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="115" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B115" s="178"/>
-      <c r="D115" s="169"/>
+    <row r="115" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B115" s="164"/>
+      <c r="D115" s="159"/>
       <c r="E115" s="83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F115" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G115" s="86">
         <f t="shared" si="7"/>
@@ -14235,14 +16573,14 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="116" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B116" s="178"/>
-      <c r="D116" s="170"/>
+    <row r="116" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B116" s="164"/>
+      <c r="D116" s="160"/>
       <c r="E116" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F116" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G116" s="86">
         <f>4/24</f>
@@ -14336,14 +16674,14 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="117" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B117" s="178"/>
-      <c r="D117" s="170"/>
+    <row r="117" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B117" s="164"/>
+      <c r="D117" s="160"/>
       <c r="E117" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F117" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G117" s="86">
         <f t="shared" ref="G117:G118" si="8">4/24</f>
@@ -14437,14 +16775,14 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="118" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B118" s="178"/>
-      <c r="D118" s="170"/>
+    <row r="118" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B118" s="164"/>
+      <c r="D118" s="160"/>
       <c r="E118" s="79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F118" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G118" s="86">
         <f t="shared" si="8"/>
@@ -14538,14 +16876,14 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="119" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B119" s="178"/>
-      <c r="D119" s="170"/>
+    <row r="119" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B119" s="164"/>
+      <c r="D119" s="160"/>
       <c r="E119" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F119" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G119" s="86">
         <f>6/24</f>
@@ -14639,14 +16977,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="120" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B120" s="178"/>
-      <c r="D120" s="170"/>
+    <row r="120" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B120" s="164"/>
+      <c r="D120" s="160"/>
       <c r="E120" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F120" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G120" s="86">
         <f t="shared" ref="G120:G121" si="9">6/24</f>
@@ -14740,14 +17078,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="121" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B121" s="178"/>
-      <c r="D121" s="170"/>
+    <row r="121" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B121" s="164"/>
+      <c r="D121" s="160"/>
       <c r="E121" s="79" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F121" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G121" s="86">
         <f t="shared" si="9"/>
@@ -14841,14 +17179,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="122" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B122" s="178"/>
-      <c r="D122" s="170"/>
+    <row r="122" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B122" s="164"/>
+      <c r="D122" s="160"/>
       <c r="E122" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F122" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G122" s="86">
         <f>8/24</f>
@@ -14942,14 +17280,14 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="123" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B123" s="178"/>
-      <c r="D123" s="170"/>
+    <row r="123" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B123" s="164"/>
+      <c r="D123" s="160"/>
       <c r="E123" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F123" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G123" s="86">
         <f t="shared" ref="G123:G124" si="10">8/24</f>
@@ -15043,14 +17381,14 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="124" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B124" s="178"/>
-      <c r="D124" s="170"/>
+    <row r="124" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B124" s="164"/>
+      <c r="D124" s="160"/>
       <c r="E124" s="79" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F124" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G124" s="86">
         <f t="shared" si="10"/>
@@ -15144,14 +17482,14 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="125" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B125" s="178"/>
-      <c r="D125" s="170"/>
+    <row r="125" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B125" s="164"/>
+      <c r="D125" s="160"/>
       <c r="E125" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F125" s="80" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G125" s="86">
         <f>10/24</f>
@@ -15245,14 +17583,14 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="126" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B126" s="178"/>
-      <c r="D126" s="170"/>
+    <row r="126" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B126" s="164"/>
+      <c r="D126" s="160"/>
       <c r="E126" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F126" s="80" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G126" s="86">
         <f t="shared" ref="G126:G127" si="11">10/24</f>
@@ -15346,14 +17684,14 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="127" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B127" s="178"/>
-      <c r="D127" s="170"/>
+    <row r="127" spans="2:36" x14ac:dyDescent="0.3">
+      <c r="B127" s="164"/>
+      <c r="D127" s="160"/>
       <c r="E127" s="79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F127" s="80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G127" s="86">
         <f t="shared" si="11"/>
@@ -15447,27 +17785,27 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="128" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B128" s="87"/>
     </row>
-    <row r="129" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B129" s="171" t="s">
-        <v>114</v>
-      </c>
-      <c r="C129" s="145"/>
-      <c r="D129" s="145"/>
-      <c r="E129" s="145"/>
-      <c r="F129" s="145"/>
-      <c r="G129" s="145"/>
-      <c r="H129" s="145"/>
-      <c r="I129" s="145"/>
-      <c r="J129" s="145"/>
-      <c r="K129" s="145"/>
-      <c r="L129" s="145"/>
-      <c r="M129" s="145"/>
-      <c r="N129" s="145"/>
-      <c r="O129" s="145"/>
-      <c r="P129" s="145"/>
+    <row r="129" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B129" s="162" t="s">
+        <v>110</v>
+      </c>
+      <c r="C129" s="161"/>
+      <c r="D129" s="161"/>
+      <c r="E129" s="161"/>
+      <c r="F129" s="161"/>
+      <c r="G129" s="161"/>
+      <c r="H129" s="161"/>
+      <c r="I129" s="161"/>
+      <c r="J129" s="161"/>
+      <c r="K129" s="161"/>
+      <c r="L129" s="161"/>
+      <c r="M129" s="161"/>
+      <c r="N129" s="161"/>
+      <c r="O129" s="161"/>
+      <c r="P129" s="161"/>
       <c r="Q129" s="50"/>
       <c r="R129" s="50"/>
       <c r="S129" s="50"/>
@@ -15476,7 +17814,7 @@
       <c r="V129" s="50"/>
       <c r="W129" s="50"/>
     </row>
-    <row r="130" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B130" s="40"/>
       <c r="C130" s="40"/>
       <c r="D130" s="40"/>
@@ -15500,28 +17838,28 @@
       <c r="V130" s="40"/>
       <c r="W130" s="40"/>
     </row>
-    <row r="131" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B131" s="40"/>
-      <c r="C131" s="172" t="s">
-        <v>115</v>
-      </c>
-      <c r="D131" s="173"/>
-      <c r="E131" s="173"/>
-      <c r="F131" s="173"/>
-      <c r="G131" s="173"/>
-      <c r="H131" s="173"/>
-      <c r="I131" s="174" t="s">
-        <v>116</v>
-      </c>
-      <c r="J131" s="175"/>
-      <c r="K131" s="175"/>
-      <c r="L131" s="175"/>
-      <c r="M131" s="176"/>
+      <c r="C131" s="152" t="s">
+        <v>111</v>
+      </c>
+      <c r="D131" s="153"/>
+      <c r="E131" s="153"/>
+      <c r="F131" s="153"/>
+      <c r="G131" s="153"/>
+      <c r="H131" s="153"/>
+      <c r="I131" s="155" t="s">
+        <v>112</v>
+      </c>
+      <c r="J131" s="156"/>
+      <c r="K131" s="156"/>
+      <c r="L131" s="156"/>
+      <c r="M131" s="157"/>
       <c r="N131" s="89" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O131" s="90" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P131" s="91"/>
       <c r="Q131" s="91"/>
@@ -15532,36 +17870,36 @@
       <c r="V131" s="91"/>
       <c r="W131" s="92"/>
     </row>
-    <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="40"/>
-      <c r="C132" s="162" t="s">
-        <v>119</v>
-      </c>
-      <c r="D132" s="163"/>
-      <c r="E132" s="163"/>
-      <c r="F132" s="163"/>
-      <c r="G132" s="163"/>
-      <c r="H132" s="164"/>
+      <c r="C132" s="142" t="s">
+        <v>115</v>
+      </c>
+      <c r="D132" s="143"/>
+      <c r="E132" s="143"/>
+      <c r="F132" s="143"/>
+      <c r="G132" s="143"/>
+      <c r="H132" s="144"/>
       <c r="I132" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M132" s="96"/>
       <c r="N132" s="97"/>
       <c r="O132" s="98"/>
       <c r="W132" s="99"/>
     </row>
-    <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="40"/>
-      <c r="C133" s="162" t="s">
-        <v>120</v>
-      </c>
-      <c r="D133" s="163"/>
-      <c r="E133" s="163"/>
-      <c r="F133" s="163"/>
-      <c r="G133" s="163"/>
-      <c r="H133" s="164"/>
+      <c r="C133" s="142" t="s">
+        <v>116</v>
+      </c>
+      <c r="D133" s="143"/>
+      <c r="E133" s="143"/>
+      <c r="F133" s="143"/>
+      <c r="G133" s="143"/>
+      <c r="H133" s="144"/>
       <c r="I133" s="100" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J133" s="101"/>
       <c r="K133" s="101"/>
@@ -15570,7 +17908,7 @@
       <c r="N133" s="103"/>
       <c r="O133" s="103"/>
       <c r="P133" s="101" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="Q133" s="101"/>
       <c r="R133" s="101"/>
@@ -15580,23 +17918,23 @@
       <c r="V133" s="101"/>
       <c r="W133" s="104"/>
     </row>
-    <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="40"/>
-      <c r="C134" s="162" t="s">
-        <v>109</v>
-      </c>
-      <c r="D134" s="163"/>
-      <c r="E134" s="163"/>
-      <c r="F134" s="163"/>
-      <c r="G134" s="163"/>
-      <c r="H134" s="164"/>
-      <c r="I134" s="165" t="s">
-        <v>122</v>
-      </c>
-      <c r="J134" s="166"/>
-      <c r="K134" s="166"/>
-      <c r="L134" s="166"/>
-      <c r="M134" s="167"/>
+      <c r="C134" s="142" t="s">
+        <v>105</v>
+      </c>
+      <c r="D134" s="143"/>
+      <c r="E134" s="143"/>
+      <c r="F134" s="143"/>
+      <c r="G134" s="143"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="J134" s="149"/>
+      <c r="K134" s="149"/>
+      <c r="L134" s="149"/>
+      <c r="M134" s="150"/>
       <c r="N134" s="105"/>
       <c r="O134" s="105"/>
       <c r="P134" s="106"/>
@@ -15608,23 +17946,23 @@
       <c r="V134" s="106"/>
       <c r="W134" s="107"/>
     </row>
-    <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="40"/>
-      <c r="C135" s="162" t="s">
-        <v>123</v>
-      </c>
-      <c r="D135" s="163"/>
-      <c r="E135" s="163"/>
-      <c r="F135" s="163"/>
-      <c r="G135" s="163"/>
-      <c r="H135" s="164"/>
-      <c r="I135" s="165" t="s">
-        <v>124</v>
-      </c>
-      <c r="J135" s="166"/>
-      <c r="K135" s="166"/>
-      <c r="L135" s="166"/>
-      <c r="M135" s="167"/>
+      <c r="C135" s="142" t="s">
+        <v>119</v>
+      </c>
+      <c r="D135" s="143"/>
+      <c r="E135" s="143"/>
+      <c r="F135" s="143"/>
+      <c r="G135" s="143"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="148" t="s">
+        <v>120</v>
+      </c>
+      <c r="J135" s="149"/>
+      <c r="K135" s="149"/>
+      <c r="L135" s="149"/>
+      <c r="M135" s="150"/>
       <c r="N135" s="105"/>
       <c r="O135" s="105"/>
       <c r="P135" s="106"/>
@@ -15636,18 +17974,18 @@
       <c r="V135" s="106"/>
       <c r="W135" s="107"/>
     </row>
-    <row r="136" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B136" s="40"/>
-      <c r="C136" s="162" t="s">
-        <v>125</v>
-      </c>
-      <c r="D136" s="163"/>
-      <c r="E136" s="163"/>
-      <c r="F136" s="163"/>
-      <c r="G136" s="163"/>
-      <c r="H136" s="164"/>
+      <c r="C136" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="D136" s="143"/>
+      <c r="E136" s="143"/>
+      <c r="F136" s="143"/>
+      <c r="G136" s="143"/>
+      <c r="H136" s="144"/>
       <c r="I136" s="108" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J136" s="109"/>
       <c r="K136" s="109"/>
@@ -15664,18 +18002,18 @@
       <c r="V136" s="109"/>
       <c r="W136" s="111"/>
     </row>
-    <row r="137" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B137" s="40"/>
-      <c r="C137" s="179" t="s">
-        <v>126</v>
-      </c>
-      <c r="D137" s="180"/>
-      <c r="E137" s="180"/>
-      <c r="F137" s="180"/>
-      <c r="G137" s="180"/>
-      <c r="H137" s="181"/>
+      <c r="C137" s="145" t="s">
+        <v>122</v>
+      </c>
+      <c r="D137" s="146"/>
+      <c r="E137" s="146"/>
+      <c r="F137" s="146"/>
+      <c r="G137" s="146"/>
+      <c r="H137" s="147"/>
       <c r="I137" s="112" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J137" s="113"/>
       <c r="K137" s="113"/>
@@ -15692,14 +18030,14 @@
       <c r="V137" s="113"/>
       <c r="W137" s="115"/>
     </row>
-    <row r="138" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B138" s="40"/>
-      <c r="C138" s="182"/>
-      <c r="D138" s="182"/>
-      <c r="E138" s="182"/>
-      <c r="F138" s="182"/>
-      <c r="G138" s="182"/>
-      <c r="H138" s="182"/>
+      <c r="C138" s="151"/>
+      <c r="D138" s="151"/>
+      <c r="E138" s="151"/>
+      <c r="F138" s="151"/>
+      <c r="G138" s="151"/>
+      <c r="H138" s="151"/>
       <c r="I138" s="116"/>
       <c r="J138" s="116"/>
       <c r="K138" s="116"/>
@@ -15716,28 +18054,28 @@
       <c r="V138" s="117"/>
       <c r="W138" s="117"/>
     </row>
-    <row r="139" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B139" s="40"/>
-      <c r="C139" s="172" t="s">
-        <v>127</v>
-      </c>
-      <c r="D139" s="173"/>
-      <c r="E139" s="173"/>
-      <c r="F139" s="173"/>
-      <c r="G139" s="173"/>
-      <c r="H139" s="183"/>
-      <c r="I139" s="174" t="s">
-        <v>116</v>
-      </c>
-      <c r="J139" s="175"/>
-      <c r="K139" s="175"/>
-      <c r="L139" s="175"/>
-      <c r="M139" s="176"/>
+      <c r="C139" s="152" t="s">
+        <v>123</v>
+      </c>
+      <c r="D139" s="153"/>
+      <c r="E139" s="153"/>
+      <c r="F139" s="153"/>
+      <c r="G139" s="153"/>
+      <c r="H139" s="154"/>
+      <c r="I139" s="155" t="s">
+        <v>112</v>
+      </c>
+      <c r="J139" s="156"/>
+      <c r="K139" s="156"/>
+      <c r="L139" s="156"/>
+      <c r="M139" s="157"/>
       <c r="N139" s="89" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O139" s="89" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P139" s="118"/>
       <c r="Q139" s="119"/>
@@ -15748,18 +18086,18 @@
       <c r="V139" s="119"/>
       <c r="W139" s="120"/>
     </row>
-    <row r="140" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B140" s="40"/>
-      <c r="C140" s="162" t="s">
-        <v>120</v>
-      </c>
-      <c r="D140" s="163"/>
-      <c r="E140" s="163"/>
-      <c r="F140" s="163"/>
-      <c r="G140" s="163"/>
-      <c r="H140" s="164"/>
+      <c r="C140" s="142" t="s">
+        <v>116</v>
+      </c>
+      <c r="D140" s="143"/>
+      <c r="E140" s="143"/>
+      <c r="F140" s="143"/>
+      <c r="G140" s="143"/>
+      <c r="H140" s="144"/>
       <c r="I140" s="100" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J140" s="101"/>
       <c r="K140" s="101"/>
@@ -15768,7 +18106,7 @@
       <c r="N140" s="103"/>
       <c r="O140" s="103"/>
       <c r="P140" s="101" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="Q140" s="101"/>
       <c r="R140" s="101"/>
@@ -15778,10 +18116,10 @@
       <c r="V140" s="101"/>
       <c r="W140" s="104"/>
     </row>
-    <row r="141" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B141" s="40"/>
       <c r="C141" s="93" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D141" s="94"/>
       <c r="E141" s="94"/>
@@ -15789,7 +18127,7 @@
       <c r="G141" s="94"/>
       <c r="H141" s="95"/>
       <c r="I141" s="122" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J141" s="123"/>
       <c r="K141" s="123"/>
@@ -15806,9 +18144,9 @@
       <c r="V141" s="123"/>
       <c r="W141" s="126"/>
     </row>
-    <row r="142" spans="2:28" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:28" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C142" s="93" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D142" s="94"/>
       <c r="E142" s="94"/>
@@ -15816,7 +18154,7 @@
       <c r="G142" s="94"/>
       <c r="H142" s="95"/>
       <c r="I142" s="127" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J142" s="127"/>
       <c r="K142" s="127"/>
@@ -15824,7 +18162,7 @@
       <c r="M142" s="127"/>
       <c r="O142" s="128"/>
       <c r="P142" s="129" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q142" s="94"/>
       <c r="R142" s="95"/>
@@ -15839,18 +18177,18 @@
       <c r="AA142" s="94"/>
       <c r="AB142" s="95"/>
     </row>
-    <row r="143" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B143" s="40"/>
-      <c r="C143" s="162" t="s">
-        <v>123</v>
-      </c>
-      <c r="D143" s="163"/>
-      <c r="E143" s="163"/>
-      <c r="F143" s="163"/>
-      <c r="G143" s="163"/>
-      <c r="H143" s="164"/>
+      <c r="C143" s="142" t="s">
+        <v>119</v>
+      </c>
+      <c r="D143" s="143"/>
+      <c r="E143" s="143"/>
+      <c r="F143" s="143"/>
+      <c r="G143" s="143"/>
+      <c r="H143" s="144"/>
       <c r="I143" s="122" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J143" s="131"/>
       <c r="K143" s="131"/>
@@ -15867,18 +18205,18 @@
       <c r="V143" s="131"/>
       <c r="W143" s="134"/>
     </row>
-    <row r="144" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B144" s="40"/>
-      <c r="C144" s="162" t="s">
-        <v>125</v>
-      </c>
-      <c r="D144" s="163"/>
-      <c r="E144" s="163"/>
-      <c r="F144" s="163"/>
-      <c r="G144" s="163"/>
-      <c r="H144" s="164"/>
+      <c r="C144" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="D144" s="143"/>
+      <c r="E144" s="143"/>
+      <c r="F144" s="143"/>
+      <c r="G144" s="143"/>
+      <c r="H144" s="144"/>
       <c r="I144" s="122" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J144" s="109"/>
       <c r="K144" s="109"/>
@@ -15895,18 +18233,18 @@
       <c r="V144" s="109"/>
       <c r="W144" s="111"/>
     </row>
-    <row r="145" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B145" s="40"/>
-      <c r="C145" s="179" t="s">
-        <v>131</v>
-      </c>
-      <c r="D145" s="180"/>
-      <c r="E145" s="180"/>
-      <c r="F145" s="180"/>
-      <c r="G145" s="180"/>
-      <c r="H145" s="181"/>
+      <c r="C145" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="D145" s="146"/>
+      <c r="E145" s="146"/>
+      <c r="F145" s="146"/>
+      <c r="G145" s="146"/>
+      <c r="H145" s="147"/>
       <c r="I145" s="112" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J145" s="113"/>
       <c r="K145" s="113"/>
@@ -15923,250 +18261,249 @@
       <c r="V145" s="113"/>
       <c r="W145" s="115"/>
     </row>
-    <row r="146" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B146" s="87"/>
     </row>
-    <row r="147" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B147" s="87"/>
     </row>
-    <row r="148" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B148" s="87"/>
     </row>
-    <row r="149" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B149" s="87"/>
     </row>
-    <row r="150" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B150" s="87"/>
     </row>
-    <row r="151" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B151" s="87"/>
     </row>
-    <row r="152" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B152" s="87"/>
     </row>
-    <row r="153" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B153" s="87"/>
     </row>
-    <row r="154" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B154" s="87"/>
     </row>
-    <row r="155" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B155" s="87"/>
     </row>
-    <row r="156" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B156" s="87"/>
     </row>
-    <row r="157" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B157" s="87"/>
     </row>
-    <row r="158" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B158" s="87"/>
     </row>
-    <row r="159" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B159" s="87"/>
     </row>
-    <row r="160" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B160" s="87"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B161" s="87"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B162" s="87"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B163" s="87"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B164" s="87"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B165" s="87"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B166" s="87"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B167" s="87"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B168" s="87"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B169" s="87"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B170" s="87"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B171" s="87"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B172" s="87"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B173" s="87"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B174" s="87"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B175" s="87"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="87"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B177" s="87"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B178" s="87"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B179" s="87"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B180" s="87"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B181" s="87"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B182" s="87"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B183" s="87"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B184" s="87"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B185" s="87"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B186" s="87"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B187" s="87"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B188" s="87"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B189" s="87"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B190" s="87"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B191" s="87"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B192" s="87"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B193" s="87"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B194" s="87"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B195" s="87"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B196" s="87"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B197" s="87"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B198" s="87"/>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B199" s="87"/>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B200" s="87"/>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B201" s="87"/>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B202" s="87"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B203" s="87"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B204" s="87"/>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B205" s="87"/>
     </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B206" s="87"/>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B207" s="87"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B208" s="87"/>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B209" s="87"/>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B210" s="87"/>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B211" s="87"/>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B212" s="87"/>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B213" s="87"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B214" s="87"/>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B215" s="87"/>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B216" s="87"/>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B217" s="87"/>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B218" s="87"/>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B219" s="87"/>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B220" s="87"/>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B221" s="87"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B222" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C135:H135"/>
-    <mergeCell ref="I135:M135"/>
-    <mergeCell ref="C136:H136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="I139:M139"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="C7:Q7"/>
+    <mergeCell ref="B9:B36"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="C15:P16"/>
     <mergeCell ref="C134:H134"/>
     <mergeCell ref="I134:M134"/>
     <mergeCell ref="D17:D27"/>
@@ -16183,17 +18520,19 @@
     <mergeCell ref="D79:D93"/>
     <mergeCell ref="D96:D110"/>
     <mergeCell ref="D113:D127"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="C7:Q7"/>
-    <mergeCell ref="B9:B36"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D13:L13"/>
-    <mergeCell ref="C15:P16"/>
+    <mergeCell ref="I135:M135"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="I139:M139"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C135:H135"/>
   </mergeCells>
+  <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M1" r:id="rId1" display="https://atb.nrel.gov/electricity/2022/utility-scale_battery_storage" xr:uid="{7816EC9A-0454-4087-A6E1-F971C99AA20E}"/>
     <hyperlink ref="I134:M134" r:id="rId2" display="V. Ramasamy, D. Feldman, J. Desai, and R. Margolis. 2022. U.S. Solar Photovoltaic System and Energy Storage Cost Benchmark: Q1 2022. Golden, CO: National Renewable Energy Laboratory" xr:uid="{FBF86B4A-206F-4112-A570-8A7A00AB84EC}"/>
@@ -16206,18 +18545,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC34B27C-0BFA-4D35-874E-EA84BA74EBE0}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.5703125" customWidth="1"/>
-    <col min="2" max="14" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="14" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -16233,75 +18572,75 @@
       <c r="M1" s="33"/>
       <c r="N1" s="33"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="184" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="185"/>
       <c r="D2" s="186"/>
       <c r="E2" s="39"/>
       <c r="F2" s="184" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="185"/>
       <c r="H2" s="186"/>
       <c r="I2" s="184" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" s="185"/>
       <c r="K2" s="186"/>
       <c r="L2" s="184" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M2" s="185"/>
       <c r="N2" s="186"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="20"/>
       <c r="F3" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="21" t="s">
         <v>39</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>40</v>
       </c>
       <c r="J3" s="20" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="21" t="s">
         <v>39</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>40</v>
       </c>
       <c r="M3" s="20" t="s">
         <v>1</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="9">
         <v>50160000</v>
@@ -16344,9 +18683,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="9">
         <v>4200000</v>
@@ -16389,9 +18728,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="9">
         <v>3121131</v>
@@ -16434,9 +18773,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="9">
         <v>8602825</v>
@@ -16479,9 +18818,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9">
         <v>5479149</v>
@@ -16524,9 +18863,9 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="9">
         <v>2775545</v>
@@ -16569,9 +18908,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="9">
         <v>5293460</v>
@@ -16614,9 +18953,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="23">
         <v>79632110</v>
@@ -16659,9 +18998,9 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="7">
         <v>250000</v>
@@ -16701,9 +19040,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="9">
         <v>295289</v>
@@ -16743,9 +19082,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="9">
         <v>1802363</v>
@@ -16785,9 +19124,9 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="9">
         <v>2477135</v>
@@ -16827,9 +19166,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="9">
         <v>2477135</v>
@@ -16869,9 +19208,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="9">
         <v>4346702</v>
@@ -16911,9 +19250,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="28">
         <v>11648623</v>
@@ -16953,14 +19292,14 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>49</v>
       </c>
       <c r="D22" s="35">
         <f>SUM(D5:D9,D12:D17)</f>
@@ -16968,12 +19307,12 @@
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" s="36">
         <f>D10*SUM(D5:D7)/SUM(D4:D7)</f>
@@ -16981,12 +19320,12 @@
       </c>
       <c r="E23" s="36"/>
       <c r="F23" s="37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="35">
         <f>SUM(D22:D23)</f>
@@ -16994,12 +19333,12 @@
       </c>
       <c r="E24" s="35"/>
       <c r="F24" s="37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="5">
         <f>D24*10^6</f>
@@ -17007,25 +19346,25 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" s="5">
-        <f>D25*About!A48</f>
+        <f>D25*About!A57</f>
         <v>549760.10443936056</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -17035,22 +19374,23 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
   </mergeCells>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD9A83FF-6D12-451D-B709-5F68973469C6}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -17143,9 +19483,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B2">
         <v>272875</v>
@@ -17157,94 +19497,94 @@
         <v>303546</v>
       </c>
       <c r="E2">
-        <v>275720</v>
+        <v>274986</v>
       </c>
       <c r="F2">
-        <v>254008</v>
+        <v>253296</v>
       </c>
       <c r="G2">
-        <v>237399</v>
+        <v>236734</v>
       </c>
       <c r="H2">
-        <v>223663</v>
+        <v>223030</v>
       </c>
       <c r="I2">
-        <v>212018</v>
+        <v>211554</v>
       </c>
       <c r="J2">
-        <v>202332</v>
+        <v>201954</v>
       </c>
       <c r="K2">
-        <v>194107</v>
+        <v>193764</v>
       </c>
       <c r="L2">
-        <v>186872</v>
+        <v>186541</v>
       </c>
       <c r="M2">
-        <v>180500</v>
+        <v>180196</v>
       </c>
       <c r="N2">
-        <v>174745</v>
+        <v>174552</v>
       </c>
       <c r="O2">
-        <v>169959</v>
+        <v>169876</v>
       </c>
       <c r="P2">
-        <v>165780</v>
+        <v>165776</v>
       </c>
       <c r="Q2">
-        <v>162166</v>
+        <v>162216</v>
       </c>
       <c r="R2">
-        <v>159002</v>
+        <v>159077</v>
       </c>
       <c r="S2">
-        <v>156172</v>
+        <v>156257</v>
       </c>
       <c r="T2">
-        <v>153632</v>
+        <v>153722</v>
       </c>
       <c r="U2">
-        <v>151363</v>
+        <v>151442</v>
       </c>
       <c r="V2">
-        <v>149361</v>
+        <v>149428</v>
       </c>
       <c r="W2">
-        <v>147535</v>
+        <v>147587</v>
       </c>
       <c r="X2">
-        <v>145853</v>
+        <v>145898</v>
       </c>
       <c r="Y2">
-        <v>144309</v>
+        <v>144352</v>
       </c>
       <c r="Z2">
-        <v>142883</v>
+        <v>142921</v>
       </c>
       <c r="AA2">
-        <v>141583</v>
+        <v>141617</v>
       </c>
       <c r="AB2">
-        <v>140367</v>
+        <v>140396</v>
       </c>
       <c r="AC2">
-        <v>139237</v>
+        <v>139257</v>
       </c>
       <c r="AD2">
-        <v>138175</v>
+        <v>138188</v>
       </c>
       <c r="AE2">
-        <v>137182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <v>137190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="C3">
-        <f t="shared" ref="C3:AE3" si="0">C9*$B$12*1000</f>
+        <f>C9*$B$12*1000</f>
         <v>306878.94936720002</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:AE3" si="0">D9*$B$12*1000</f>
         <v>303731.66899460001</v>
       </c>
       <c r="E3">
@@ -17356,9 +19696,9 @@
         <v>123431.08661402132</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B5">
         <v>2021</v>
@@ -17451,9 +19791,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6">
         <v>253384</v>
@@ -17546,7 +19886,7 @@
         <v>212064</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="C7">
         <f t="shared" ref="C7:AE7" si="1">C10*$B$12*1000</f>
         <v>284959.40253119997</v>
@@ -17664,12 +20004,12 @@
         <v>212193.12422562522</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>390.92859792000002</v>
@@ -17759,12 +20099,12 @@
         <v>157.23705301149212</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>363.00560831999996</v>
@@ -17854,128 +20194,136 @@
         <v>270.30971238933148</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12">
         <v>0.78500000000000003</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF003399"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2021</v>
       </c>
       <c r="B2" s="5">
-        <f>'NREL ATB 2024'!F20*1000*About!A51</f>
-        <v>272875.18454364559</v>
+        <f>KEEI_계산과정!D49</f>
+        <v>221480.34275964473</v>
       </c>
       <c r="E2" s="5"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2022</v>
       </c>
       <c r="B3" s="5">
-        <f>'NREL ATB 2024'!G20*1000*cpi_2022_to_2012</f>
-        <v>306691.70357876847</v>
+        <f>KEEI_계산과정!E49</f>
+        <v>212817.88652921631</v>
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" s="5">
-        <f>'NREL ATB 2024'!H20*1000*cpi_2022_to_2012</f>
-        <v>303546.34355618269</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!F49</f>
+        <v>204155.43029878792</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2024</v>
       </c>
       <c r="B5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!G49</f>
+        <v>195492.9740683595</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2025</v>
       </c>
       <c r="B6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!H49</f>
+        <v>186830.51783793111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2026</v>
       </c>
       <c r="B7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!I49</f>
+        <v>178168.06160750272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2027</v>
       </c>
       <c r="B8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!J49</f>
+        <v>169505.6053770743</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2028</v>
       </c>
       <c r="B9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!K49</f>
+        <v>160843.14914664591</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2029</v>
       </c>
       <c r="B10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!L49</f>
+        <v>152180.69291621749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2030</v>
       </c>
       <c r="B11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!M49</f>
+        <v>143518.2366857891</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2031</v>
       </c>
@@ -17983,7 +20331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2032</v>
       </c>
@@ -17991,7 +20339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2033</v>
       </c>
@@ -17999,7 +20347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2034</v>
       </c>
@@ -18007,7 +20355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2035</v>
       </c>
@@ -18015,7 +20363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2036</v>
       </c>
@@ -18023,7 +20371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2037</v>
       </c>
@@ -18031,7 +20379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2038</v>
       </c>
@@ -18039,7 +20387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2039</v>
       </c>
@@ -18047,7 +20395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2040</v>
       </c>
@@ -18055,7 +20403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2041</v>
       </c>
@@ -18063,7 +20411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2042</v>
       </c>
@@ -18071,7 +20419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2043</v>
       </c>
@@ -18079,7 +20427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2044</v>
       </c>
@@ -18087,7 +20435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2045</v>
       </c>
@@ -18095,7 +20443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2046</v>
       </c>
@@ -18103,7 +20451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2047</v>
       </c>
@@ -18111,7 +20459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2048</v>
       </c>
@@ -18119,7 +20467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2049</v>
       </c>
@@ -18127,7 +20475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2050</v>
       </c>
@@ -18136,535 +20484,497 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87094533-1E2E-4CB1-BEF0-251B882C2D5B}">
   <sheetPr>
     <tabColor rgb="FF003399"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2021</v>
       </c>
       <c r="B2" s="5">
-        <f>'NREL ATB 2024'!F26*1000*About!A51</f>
-        <v>253384.43615467878</v>
+        <f>KEEI_계산과정!D48</f>
+        <v>136839.65777514293</v>
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2022</v>
       </c>
       <c r="B3" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A3,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>284785.53121122846</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!E48</f>
+        <v>133600.36519098651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A4,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>281864.83588615071</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!F48</f>
+        <v>130361.07260683009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2024</v>
       </c>
       <c r="B5" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A5,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>272119.91517411894</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!G48</f>
+        <v>127121.78002267367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2025</v>
       </c>
       <c r="B6" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A6,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>244267.93200601047</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!H48</f>
+        <v>123882.48743851724</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2026</v>
       </c>
       <c r="B7" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A7,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>245045.09148289612</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!I48</f>
+        <v>120643.19485436082</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2027</v>
       </c>
       <c r="B8" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A8,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>245896.5501406297</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!J48</f>
+        <v>117403.9022702044</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2028</v>
       </c>
       <c r="B9" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A9,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>246831.28958028281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!K48</f>
+        <v>114164.60968604797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2029</v>
       </c>
       <c r="B10" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A10,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>247859.79983015926</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!L48</f>
+        <v>110925.31710189156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2030</v>
       </c>
       <c r="B11" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A11,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>248994.40989292334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <f>KEEI_계산과정!M48</f>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2031</v>
       </c>
       <c r="B12" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A12,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>247303.59777741029</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <f>B11</f>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2032</v>
       </c>
       <c r="B13" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A13,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>245600.17607833183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" ref="B13:B31" si="0">B12</f>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2033</v>
       </c>
       <c r="B14" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A14,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>243883.65354072856</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2034</v>
       </c>
       <c r="B15" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A15,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>242153.5130555816</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2035</v>
       </c>
       <c r="B16" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A16,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>240409.20993631281</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2036</v>
       </c>
       <c r="B17" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A17,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>238650.17005554074</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2037</v>
       </c>
       <c r="B18" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A18,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>236875.78782870833</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2038</v>
       </c>
       <c r="B19" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A19,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>235085.42402968768</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2039</v>
       </c>
       <c r="B20" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A20,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>233278.40342179779</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2040</v>
       </c>
       <c r="B21" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A21,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>231454.01218578266</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2041</v>
       </c>
       <c r="B22" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A22,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>229611.49512414529</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2042</v>
       </c>
       <c r="B23" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A23,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>227750.05261882479</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2043</v>
       </c>
       <c r="B24" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A24,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>225868.83731644039</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2044</v>
       </c>
       <c r="B25" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A25,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>223966.95051221756</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2045</v>
       </c>
       <c r="B26" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A26,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>222043.43820014191</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2046</v>
       </c>
       <c r="B27" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A27,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>220097.2867528405</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2047</v>
       </c>
       <c r="B28" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A28,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>218127.41819005259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2048</v>
       </c>
       <c r="B29" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A29,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>216132.68498924136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2049</v>
       </c>
       <c r="B30" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A30,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>214111.864385811</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2050</v>
       </c>
       <c r="B31" s="5">
-        <f>INDEX('NREL ATB 2024'!$G$26:$AI$26,MATCH('BCpUC-power'!A31,'NREL ATB 2024'!$G$24:$AI$24,0))*1000*cpi_2022_to_2012</f>
-        <v>212063.65210338513</v>
+        <f t="shared" si="0"/>
+        <v>107686.02451773513</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2600C7A-0160-47B2-B089-93F8CBD71882}">
   <sheetPr>
     <tabColor rgb="FF003399"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="B2" s="36">
         <v>0.2</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
+      <c r="C2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="E2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="F2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="K2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="L2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="M2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="N2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="P2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="Q2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="R2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="S2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="T2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="U2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="V2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="W2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="X2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="Y2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="Z2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AA2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AB2" s="36">
+        <v>0.2</v>
+      </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
-    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03230F69-5C37-482A-9AF2-EA487C434149}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9B3E56-6981-4A8D-A07F-D09958A7E936}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{878B2073-6AC3-4E46-9BDE-C92993625DB4}"/>
 </file>
--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation-my.sharepoint.com/personal/maryfrancis_energyinnovation_org/Documents/South Korea/4.0.5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\elec\BCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{935069C4-DFE3-4F75-8831-FDBCBA4C7C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2958B585-FE57-483E-889A-B3CF2BDE2F44}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD84EB8-A062-4DE5-9603-10309A2960B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27975" yWindow="-360" windowWidth="23625" windowHeight="15345" tabRatio="839" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="839" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="14" r:id="rId1"/>
@@ -2138,7 +2138,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2536,83 +2536,32 @@
     <xf numFmtId="173" fontId="1" fillId="0" borderId="78" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="22" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2659,6 +2608,60 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2668,10 +2671,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5630,37 +5629,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="183" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1"/>
     <row r="3" spans="1:12" ht="24" customHeight="1">
-      <c r="A3" s="181" t="s">
+      <c r="A3" s="180" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="180"/>
-      <c r="C3" s="180"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="180"/>
-      <c r="H3" s="180"/>
-      <c r="I3" s="180"/>
-      <c r="J3" s="180"/>
-      <c r="K3" s="180"/>
-      <c r="L3" s="180"/>
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="181"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="181"/>
+      <c r="I3" s="181"/>
+      <c r="J3" s="181"/>
+      <c r="K3" s="181"/>
+      <c r="L3" s="181"/>
     </row>
     <row r="4" spans="1:12" ht="20.149999999999999" customHeight="1">
       <c r="A4" s="148" t="s">
@@ -5750,20 +5749,20 @@
     </row>
     <row r="9" spans="1:12" ht="20.149999999999999" customHeight="1"/>
     <row r="10" spans="1:12" ht="20.149999999999999" customHeight="1">
-      <c r="A10" s="181" t="s">
+      <c r="A10" s="180" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="183"/>
-      <c r="C10" s="183"/>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="183"/>
-      <c r="K10" s="183"/>
-      <c r="L10" s="183"/>
+      <c r="B10" s="184"/>
+      <c r="C10" s="184"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="184"/>
+      <c r="L10" s="184"/>
     </row>
     <row r="11" spans="1:12" ht="20.149999999999999" customHeight="1">
       <c r="A11" s="149" t="s">
@@ -5949,32 +5948,32 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="24" customHeight="1">
-      <c r="A21" s="181" t="s">
+      <c r="A21" s="180" t="s">
         <v>193</v>
       </c>
-      <c r="B21" s="180"/>
-      <c r="C21" s="180"/>
-      <c r="D21" s="180"/>
-      <c r="E21" s="180"/>
-      <c r="F21" s="180"/>
-      <c r="G21" s="180"/>
-      <c r="H21" s="180"/>
-      <c r="I21" s="180"/>
-      <c r="J21" s="180"/>
-      <c r="K21" s="180"/>
-      <c r="L21" s="180"/>
+      <c r="B21" s="181"/>
+      <c r="C21" s="181"/>
+      <c r="D21" s="181"/>
+      <c r="E21" s="181"/>
+      <c r="F21" s="181"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="181"/>
+      <c r="L21" s="181"/>
     </row>
     <row r="22" spans="1:12" ht="18" customHeight="1">
       <c r="A22" s="182" t="s">
         <v>194</v>
       </c>
-      <c r="B22" s="180"/>
-      <c r="C22" s="180"/>
-      <c r="D22" s="180"/>
-      <c r="E22" s="180"/>
-      <c r="F22" s="180"/>
-      <c r="G22" s="180"/>
-      <c r="H22" s="180"/>
+      <c r="B22" s="181"/>
+      <c r="C22" s="181"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="181"/>
     </row>
     <row r="23" spans="1:12" ht="20.149999999999999" customHeight="1">
       <c r="A23" s="149" t="s">
@@ -6212,32 +6211,32 @@
     </row>
     <row r="32" spans="1:12" ht="20.149999999999999" customHeight="1"/>
     <row r="33" spans="1:33" ht="20.149999999999999" customHeight="1">
-      <c r="A33" s="181" t="s">
+      <c r="A33" s="180" t="s">
         <v>201</v>
       </c>
-      <c r="B33" s="180"/>
-      <c r="C33" s="180"/>
-      <c r="D33" s="180"/>
-      <c r="E33" s="180"/>
-      <c r="F33" s="180"/>
-      <c r="G33" s="180"/>
-      <c r="H33" s="180"/>
-      <c r="I33" s="180"/>
-      <c r="J33" s="180"/>
-      <c r="K33" s="180"/>
-      <c r="L33" s="180"/>
+      <c r="B33" s="181"/>
+      <c r="C33" s="181"/>
+      <c r="D33" s="181"/>
+      <c r="E33" s="181"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="181"/>
+      <c r="L33" s="181"/>
     </row>
     <row r="34" spans="1:33" ht="18" customHeight="1">
-      <c r="A34" s="184" t="s">
+      <c r="A34" s="185" t="s">
         <v>202</v>
       </c>
-      <c r="B34" s="180"/>
-      <c r="C34" s="180"/>
-      <c r="D34" s="180"/>
-      <c r="E34" s="180"/>
-      <c r="F34" s="180"/>
-      <c r="G34" s="180"/>
-      <c r="H34" s="180"/>
+      <c r="B34" s="181"/>
+      <c r="C34" s="181"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
     </row>
     <row r="35" spans="1:33" ht="20.149999999999999" customHeight="1">
       <c r="A35" s="149" t="s">
@@ -6460,78 +6459,78 @@
       <c r="H44" s="159"/>
     </row>
     <row r="45" spans="1:33" ht="24" customHeight="1">
-      <c r="A45" s="181" t="s">
+      <c r="A45" s="180" t="s">
         <v>208</v>
       </c>
-      <c r="B45" s="180"/>
-      <c r="C45" s="180"/>
-      <c r="D45" s="180"/>
-      <c r="E45" s="180"/>
-      <c r="F45" s="180"/>
-      <c r="G45" s="180"/>
-      <c r="H45" s="180"/>
-      <c r="I45" s="180"/>
-      <c r="J45" s="180"/>
-      <c r="K45" s="180"/>
-      <c r="L45" s="180"/>
-      <c r="M45" s="180"/>
-      <c r="N45" s="180"/>
-      <c r="O45" s="180"/>
-      <c r="P45" s="180"/>
-      <c r="Q45" s="180"/>
-      <c r="R45" s="180"/>
-      <c r="S45" s="180"/>
-      <c r="T45" s="180"/>
-      <c r="U45" s="180"/>
-      <c r="V45" s="180"/>
-      <c r="W45" s="180"/>
-      <c r="X45" s="180"/>
-      <c r="Y45" s="180"/>
-      <c r="Z45" s="180"/>
-      <c r="AA45" s="180"/>
-      <c r="AB45" s="180"/>
-      <c r="AC45" s="180"/>
-      <c r="AD45" s="180"/>
-      <c r="AE45" s="180"/>
-      <c r="AF45" s="180"/>
-      <c r="AG45" s="180"/>
+      <c r="B45" s="181"/>
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="181"/>
+      <c r="F45" s="181"/>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="181"/>
+      <c r="J45" s="181"/>
+      <c r="K45" s="181"/>
+      <c r="L45" s="181"/>
+      <c r="M45" s="181"/>
+      <c r="N45" s="181"/>
+      <c r="O45" s="181"/>
+      <c r="P45" s="181"/>
+      <c r="Q45" s="181"/>
+      <c r="R45" s="181"/>
+      <c r="S45" s="181"/>
+      <c r="T45" s="181"/>
+      <c r="U45" s="181"/>
+      <c r="V45" s="181"/>
+      <c r="W45" s="181"/>
+      <c r="X45" s="181"/>
+      <c r="Y45" s="181"/>
+      <c r="Z45" s="181"/>
+      <c r="AA45" s="181"/>
+      <c r="AB45" s="181"/>
+      <c r="AC45" s="181"/>
+      <c r="AD45" s="181"/>
+      <c r="AE45" s="181"/>
+      <c r="AF45" s="181"/>
+      <c r="AG45" s="181"/>
     </row>
     <row r="46" spans="1:33" ht="20.149999999999999" customHeight="1">
       <c r="A46" s="182" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="180"/>
-      <c r="C46" s="180"/>
-      <c r="D46" s="180"/>
-      <c r="E46" s="180"/>
-      <c r="F46" s="180"/>
-      <c r="G46" s="180"/>
-      <c r="H46" s="180"/>
-      <c r="I46" s="180"/>
-      <c r="J46" s="180"/>
-      <c r="K46" s="180"/>
-      <c r="L46" s="180"/>
-      <c r="M46" s="180"/>
-      <c r="N46" s="180"/>
-      <c r="O46" s="180"/>
-      <c r="P46" s="180"/>
-      <c r="Q46" s="180"/>
-      <c r="R46" s="180"/>
-      <c r="S46" s="180"/>
-      <c r="T46" s="180"/>
-      <c r="U46" s="180"/>
-      <c r="V46" s="180"/>
-      <c r="W46" s="180"/>
-      <c r="X46" s="180"/>
-      <c r="Y46" s="180"/>
-      <c r="Z46" s="180"/>
-      <c r="AA46" s="180"/>
-      <c r="AB46" s="180"/>
-      <c r="AC46" s="180"/>
-      <c r="AD46" s="180"/>
-      <c r="AE46" s="180"/>
-      <c r="AF46" s="180"/>
-      <c r="AG46" s="180"/>
+      <c r="B46" s="181"/>
+      <c r="C46" s="181"/>
+      <c r="D46" s="181"/>
+      <c r="E46" s="181"/>
+      <c r="F46" s="181"/>
+      <c r="G46" s="181"/>
+      <c r="H46" s="181"/>
+      <c r="I46" s="181"/>
+      <c r="J46" s="181"/>
+      <c r="K46" s="181"/>
+      <c r="L46" s="181"/>
+      <c r="M46" s="181"/>
+      <c r="N46" s="181"/>
+      <c r="O46" s="181"/>
+      <c r="P46" s="181"/>
+      <c r="Q46" s="181"/>
+      <c r="R46" s="181"/>
+      <c r="S46" s="181"/>
+      <c r="T46" s="181"/>
+      <c r="U46" s="181"/>
+      <c r="V46" s="181"/>
+      <c r="W46" s="181"/>
+      <c r="X46" s="181"/>
+      <c r="Y46" s="181"/>
+      <c r="Z46" s="181"/>
+      <c r="AA46" s="181"/>
+      <c r="AB46" s="181"/>
+      <c r="AC46" s="181"/>
+      <c r="AD46" s="181"/>
+      <c r="AE46" s="181"/>
+      <c r="AF46" s="181"/>
+      <c r="AG46" s="181"/>
     </row>
     <row r="47" spans="1:33" ht="22" customHeight="1">
       <c r="A47" s="149" t="s">
@@ -6902,41 +6901,41 @@
       <c r="AJ49"/>
     </row>
     <row r="50" spans="1:36" ht="18" customHeight="1">
-      <c r="A50" s="185" t="s">
+      <c r="A50" s="186" t="s">
         <v>209</v>
       </c>
-      <c r="B50" s="186"/>
-      <c r="C50" s="186"/>
-      <c r="D50" s="186"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="186"/>
-      <c r="H50" s="186"/>
-      <c r="I50" s="186"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="186"/>
-      <c r="L50" s="186"/>
-      <c r="M50" s="186"/>
-      <c r="N50" s="186"/>
-      <c r="O50" s="186"/>
-      <c r="P50" s="186"/>
-      <c r="Q50" s="186"/>
-      <c r="R50" s="186"/>
-      <c r="S50" s="186"/>
-      <c r="T50" s="186"/>
-      <c r="U50" s="186"/>
-      <c r="V50" s="186"/>
-      <c r="W50" s="186"/>
-      <c r="X50" s="186"/>
-      <c r="Y50" s="186"/>
-      <c r="Z50" s="186"/>
-      <c r="AA50" s="186"/>
-      <c r="AB50" s="186"/>
-      <c r="AC50" s="186"/>
-      <c r="AD50" s="186"/>
-      <c r="AE50" s="186"/>
-      <c r="AF50" s="186"/>
-      <c r="AG50" s="186"/>
+      <c r="B50" s="187"/>
+      <c r="C50" s="187"/>
+      <c r="D50" s="187"/>
+      <c r="E50" s="187"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="187"/>
+      <c r="H50" s="187"/>
+      <c r="I50" s="187"/>
+      <c r="J50" s="187"/>
+      <c r="K50" s="187"/>
+      <c r="L50" s="187"/>
+      <c r="M50" s="187"/>
+      <c r="N50" s="187"/>
+      <c r="O50" s="187"/>
+      <c r="P50" s="187"/>
+      <c r="Q50" s="187"/>
+      <c r="R50" s="187"/>
+      <c r="S50" s="187"/>
+      <c r="T50" s="187"/>
+      <c r="U50" s="187"/>
+      <c r="V50" s="187"/>
+      <c r="W50" s="187"/>
+      <c r="X50" s="187"/>
+      <c r="Y50" s="187"/>
+      <c r="Z50" s="187"/>
+      <c r="AA50" s="187"/>
+      <c r="AB50" s="187"/>
+      <c r="AC50" s="187"/>
+      <c r="AD50" s="187"/>
+      <c r="AE50" s="187"/>
+      <c r="AF50" s="187"/>
+      <c r="AG50" s="187"/>
     </row>
     <row r="51" spans="1:36" ht="18" customHeight="1">
       <c r="A51" s="173" t="s">
@@ -6947,78 +6946,78 @@
       <c r="A52" s="173"/>
     </row>
     <row r="53" spans="1:36" ht="18" customHeight="1">
-      <c r="A53" s="181" t="s">
+      <c r="A53" s="180" t="s">
         <v>234</v>
       </c>
-      <c r="B53" s="180"/>
-      <c r="C53" s="180"/>
-      <c r="D53" s="180"/>
-      <c r="E53" s="180"/>
-      <c r="F53" s="180"/>
-      <c r="G53" s="180"/>
-      <c r="H53" s="180"/>
-      <c r="I53" s="180"/>
-      <c r="J53" s="180"/>
-      <c r="K53" s="180"/>
-      <c r="L53" s="180"/>
-      <c r="M53" s="180"/>
-      <c r="N53" s="180"/>
-      <c r="O53" s="180"/>
-      <c r="P53" s="180"/>
-      <c r="Q53" s="180"/>
-      <c r="R53" s="180"/>
-      <c r="S53" s="180"/>
-      <c r="T53" s="180"/>
-      <c r="U53" s="180"/>
-      <c r="V53" s="180"/>
-      <c r="W53" s="180"/>
-      <c r="X53" s="180"/>
-      <c r="Y53" s="180"/>
-      <c r="Z53" s="180"/>
-      <c r="AA53" s="180"/>
-      <c r="AB53" s="180"/>
-      <c r="AC53" s="180"/>
-      <c r="AD53" s="180"/>
-      <c r="AE53" s="180"/>
-      <c r="AF53" s="180"/>
-      <c r="AG53" s="180"/>
+      <c r="B53" s="181"/>
+      <c r="C53" s="181"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="181"/>
+      <c r="G53" s="181"/>
+      <c r="H53" s="181"/>
+      <c r="I53" s="181"/>
+      <c r="J53" s="181"/>
+      <c r="K53" s="181"/>
+      <c r="L53" s="181"/>
+      <c r="M53" s="181"/>
+      <c r="N53" s="181"/>
+      <c r="O53" s="181"/>
+      <c r="P53" s="181"/>
+      <c r="Q53" s="181"/>
+      <c r="R53" s="181"/>
+      <c r="S53" s="181"/>
+      <c r="T53" s="181"/>
+      <c r="U53" s="181"/>
+      <c r="V53" s="181"/>
+      <c r="W53" s="181"/>
+      <c r="X53" s="181"/>
+      <c r="Y53" s="181"/>
+      <c r="Z53" s="181"/>
+      <c r="AA53" s="181"/>
+      <c r="AB53" s="181"/>
+      <c r="AC53" s="181"/>
+      <c r="AD53" s="181"/>
+      <c r="AE53" s="181"/>
+      <c r="AF53" s="181"/>
+      <c r="AG53" s="181"/>
     </row>
     <row r="54" spans="1:36" ht="18" customHeight="1">
       <c r="A54" s="182" t="s">
         <v>235</v>
       </c>
-      <c r="B54" s="180"/>
-      <c r="C54" s="180"/>
-      <c r="D54" s="180"/>
-      <c r="E54" s="180"/>
-      <c r="F54" s="180"/>
-      <c r="G54" s="180"/>
-      <c r="H54" s="180"/>
-      <c r="I54" s="180"/>
-      <c r="J54" s="180"/>
-      <c r="K54" s="180"/>
-      <c r="L54" s="180"/>
-      <c r="M54" s="180"/>
-      <c r="N54" s="180"/>
-      <c r="O54" s="180"/>
-      <c r="P54" s="180"/>
-      <c r="Q54" s="180"/>
-      <c r="R54" s="180"/>
-      <c r="S54" s="180"/>
-      <c r="T54" s="180"/>
-      <c r="U54" s="180"/>
-      <c r="V54" s="180"/>
-      <c r="W54" s="180"/>
-      <c r="X54" s="180"/>
-      <c r="Y54" s="180"/>
-      <c r="Z54" s="180"/>
-      <c r="AA54" s="180"/>
-      <c r="AB54" s="180"/>
-      <c r="AC54" s="180"/>
-      <c r="AD54" s="180"/>
-      <c r="AE54" s="180"/>
-      <c r="AF54" s="180"/>
-      <c r="AG54" s="180"/>
+      <c r="B54" s="181"/>
+      <c r="C54" s="181"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="181"/>
+      <c r="F54" s="181"/>
+      <c r="G54" s="181"/>
+      <c r="H54" s="181"/>
+      <c r="I54" s="181"/>
+      <c r="J54" s="181"/>
+      <c r="K54" s="181"/>
+      <c r="L54" s="181"/>
+      <c r="M54" s="181"/>
+      <c r="N54" s="181"/>
+      <c r="O54" s="181"/>
+      <c r="P54" s="181"/>
+      <c r="Q54" s="181"/>
+      <c r="R54" s="181"/>
+      <c r="S54" s="181"/>
+      <c r="T54" s="181"/>
+      <c r="U54" s="181"/>
+      <c r="V54" s="181"/>
+      <c r="W54" s="181"/>
+      <c r="X54" s="181"/>
+      <c r="Y54" s="181"/>
+      <c r="Z54" s="181"/>
+      <c r="AA54" s="181"/>
+      <c r="AB54" s="181"/>
+      <c r="AC54" s="181"/>
+      <c r="AD54" s="181"/>
+      <c r="AE54" s="181"/>
+      <c r="AF54" s="181"/>
+      <c r="AG54" s="181"/>
     </row>
     <row r="55" spans="1:36" ht="22" customHeight="1">
       <c r="A55" s="149" t="s">
@@ -7421,36 +7420,36 @@
     </row>
     <row r="59" spans="1:36" ht="20.149999999999999" customHeight="1"/>
     <row r="60" spans="1:36" ht="24" customHeight="1">
-      <c r="A60" s="181" t="s">
+      <c r="A60" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="B60" s="180"/>
-      <c r="C60" s="180"/>
-      <c r="D60" s="180"/>
-      <c r="E60" s="180"/>
-      <c r="F60" s="180"/>
-      <c r="G60" s="180"/>
-      <c r="H60" s="180"/>
-      <c r="I60" s="180"/>
-      <c r="J60" s="180"/>
-      <c r="K60" s="180"/>
-      <c r="L60" s="180"/>
+      <c r="B60" s="181"/>
+      <c r="C60" s="181"/>
+      <c r="D60" s="181"/>
+      <c r="E60" s="181"/>
+      <c r="F60" s="181"/>
+      <c r="G60" s="181"/>
+      <c r="H60" s="181"/>
+      <c r="I60" s="181"/>
+      <c r="J60" s="181"/>
+      <c r="K60" s="181"/>
+      <c r="L60" s="181"/>
     </row>
     <row r="61" spans="1:36" ht="20.149999999999999" customHeight="1">
       <c r="A61" s="182" t="s">
         <v>211</v>
       </c>
-      <c r="B61" s="180"/>
-      <c r="C61" s="180"/>
-      <c r="D61" s="180"/>
-      <c r="E61" s="180"/>
-      <c r="F61" s="180"/>
-      <c r="G61" s="180"/>
-      <c r="H61" s="180"/>
-      <c r="I61" s="180"/>
-      <c r="J61" s="180"/>
-      <c r="K61" s="180"/>
-      <c r="L61" s="180"/>
+      <c r="B61" s="181"/>
+      <c r="C61" s="181"/>
+      <c r="D61" s="181"/>
+      <c r="E61" s="181"/>
+      <c r="F61" s="181"/>
+      <c r="G61" s="181"/>
+      <c r="H61" s="181"/>
+      <c r="I61" s="181"/>
+      <c r="J61" s="181"/>
+      <c r="K61" s="181"/>
+      <c r="L61" s="181"/>
     </row>
     <row r="62" spans="1:36" ht="38.15" customHeight="1">
       <c r="A62" s="171" t="s">
@@ -7857,19 +7856,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:108" s="39" customFormat="1" ht="18">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="188" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="188"/>
+      <c r="G1" s="188"/>
+      <c r="H1" s="188"/>
+      <c r="I1" s="188"/>
+      <c r="J1" s="188"/>
+      <c r="K1" s="188"/>
       <c r="M1" s="3" t="s">
         <v>67</v>
       </c>
@@ -7999,12 +7998,12 @@
     </row>
     <row r="4" spans="1:108" s="39" customFormat="1" ht="14.25" customHeight="1">
       <c r="D4" s="43"/>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="189" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:108" ht="14.9" customHeight="1">
-      <c r="L5" s="212"/>
+      <c r="L5" s="190"/>
     </row>
     <row r="6" spans="1:108" s="39" customFormat="1" ht="14.25" customHeight="1">
       <c r="H6" s="44"/>
@@ -8036,23 +8035,23 @@
       <c r="B7" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="206" t="s">
+      <c r="C7" s="191" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="206"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="206"/>
-      <c r="I7" s="206"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="206"/>
-      <c r="L7" s="206"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="206"/>
-      <c r="O7" s="206"/>
-      <c r="P7" s="206"/>
-      <c r="Q7" s="206"/>
+      <c r="D7" s="191"/>
+      <c r="E7" s="191"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="191"/>
+      <c r="I7" s="191"/>
+      <c r="J7" s="191"/>
+      <c r="K7" s="191"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="191"/>
+      <c r="N7" s="191"/>
+      <c r="O7" s="191"/>
+      <c r="P7" s="191"/>
+      <c r="Q7" s="191"/>
       <c r="R7" s="49"/>
       <c r="S7" s="49"/>
       <c r="T7" s="49"/>
@@ -8070,43 +8069,43 @@
     </row>
     <row r="9" spans="1:108" s="39" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
       <c r="A9"/>
-      <c r="B9" s="213" t="s">
+      <c r="B9" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="214" t="s">
+      <c r="D9" s="193" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="215"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="217">
+      <c r="E9" s="194"/>
+      <c r="F9" s="195"/>
+      <c r="G9" s="196">
         <v>2022</v>
       </c>
-      <c r="H9" s="218"/>
-      <c r="I9" s="218"/>
-      <c r="J9" s="218"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="180"/>
+      <c r="H9" s="197"/>
+      <c r="I9" s="197"/>
+      <c r="J9" s="197"/>
+      <c r="K9" s="181"/>
+      <c r="L9" s="181"/>
     </row>
     <row r="10" spans="1:108" s="39" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B10" s="213"/>
+      <c r="B10" s="192"/>
       <c r="D10" s="52" t="s">
         <v>144</v>
       </c>
       <c r="J10" s="51"/>
     </row>
     <row r="11" spans="1:108" s="39" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B11" s="213"/>
-      <c r="D11" s="219" t="s">
+      <c r="B11" s="192"/>
+      <c r="D11" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="220"/>
-      <c r="F11" s="220"/>
-      <c r="G11" s="220"/>
-      <c r="H11" s="220"/>
-      <c r="I11" s="220"/>
-      <c r="J11" s="220"/>
-      <c r="K11" s="220"/>
-      <c r="L11" s="220"/>
+      <c r="E11" s="199"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="199"/>
+      <c r="K11" s="199"/>
+      <c r="L11" s="199"/>
       <c r="W11" s="53"/>
       <c r="X11" s="54"/>
       <c r="Y11" s="54"/>
@@ -8114,18 +8113,18 @@
       <c r="AA11" s="54"/>
     </row>
     <row r="12" spans="1:108" s="39" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
-      <c r="B12" s="213"/>
-      <c r="D12" s="221" t="s">
+      <c r="B12" s="192"/>
+      <c r="D12" s="200" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="223"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="201"/>
+      <c r="G12" s="201"/>
+      <c r="H12" s="201"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="201"/>
+      <c r="K12" s="201"/>
+      <c r="L12" s="202"/>
       <c r="M12" s="55"/>
       <c r="W12" s="53"/>
       <c r="X12" s="54"/>
@@ -8134,16 +8133,16 @@
       <c r="AA12" s="54"/>
     </row>
     <row r="13" spans="1:108" s="39" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B13" s="213"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="225"/>
-      <c r="G13" s="225"/>
-      <c r="H13" s="225"/>
-      <c r="I13" s="225"/>
-      <c r="J13" s="225"/>
-      <c r="K13" s="225"/>
-      <c r="L13" s="226"/>
+      <c r="B13" s="192"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="204"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="204"/>
+      <c r="H13" s="204"/>
+      <c r="I13" s="204"/>
+      <c r="J13" s="204"/>
+      <c r="K13" s="204"/>
+      <c r="L13" s="205"/>
       <c r="W13" s="53"/>
       <c r="X13" s="54"/>
       <c r="Y13" s="54"/>
@@ -8151,49 +8150,49 @@
       <c r="AA13" s="54"/>
     </row>
     <row r="14" spans="1:108" ht="37.4" customHeight="1">
-      <c r="B14" s="213"/>
+      <c r="B14" s="192"/>
     </row>
     <row r="15" spans="1:108" ht="15" customHeight="1">
-      <c r="B15" s="213"/>
-      <c r="C15" s="227" t="s">
+      <c r="B15" s="192"/>
+      <c r="C15" s="206" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="227"/>
-      <c r="E15" s="227"/>
-      <c r="F15" s="227"/>
-      <c r="G15" s="227"/>
-      <c r="H15" s="227"/>
-      <c r="I15" s="227"/>
-      <c r="J15" s="227"/>
-      <c r="K15" s="227"/>
-      <c r="L15" s="227"/>
-      <c r="M15" s="227"/>
-      <c r="N15" s="227"/>
-      <c r="O15" s="227"/>
-      <c r="P15" s="227"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="206"/>
+      <c r="I15" s="206"/>
+      <c r="J15" s="206"/>
+      <c r="K15" s="206"/>
+      <c r="L15" s="206"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="206"/>
+      <c r="O15" s="206"/>
+      <c r="P15" s="206"/>
       <c r="Q15" s="56"/>
     </row>
     <row r="16" spans="1:108">
-      <c r="B16" s="213"/>
-      <c r="C16" s="227"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="227"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="227"/>
-      <c r="I16" s="227"/>
-      <c r="J16" s="227"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="227"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="227"/>
-      <c r="P16" s="227"/>
+      <c r="B16" s="192"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="206"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="206"/>
+      <c r="I16" s="206"/>
+      <c r="J16" s="206"/>
+      <c r="K16" s="206"/>
+      <c r="L16" s="206"/>
+      <c r="M16" s="206"/>
+      <c r="N16" s="206"/>
+      <c r="O16" s="206"/>
+      <c r="P16" s="206"/>
     </row>
     <row r="17" spans="2:39" ht="15" customHeight="1">
-      <c r="B17" s="213"/>
+      <c r="B17" s="192"/>
       <c r="C17" s="57"/>
-      <c r="D17" s="203" t="s">
+      <c r="D17" s="213" t="s">
         <v>77</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -8201,9 +8200,9 @@
       </c>
     </row>
     <row r="18" spans="2:39" ht="15" customHeight="1">
-      <c r="B18" s="213"/>
+      <c r="B18" s="192"/>
       <c r="C18" s="57"/>
-      <c r="D18" s="204"/>
+      <c r="D18" s="214"/>
       <c r="F18" s="1" t="s">
         <v>143</v>
       </c>
@@ -8296,9 +8295,9 @@
       </c>
     </row>
     <row r="19" spans="2:39" ht="15" customHeight="1">
-      <c r="B19" s="213"/>
+      <c r="B19" s="192"/>
       <c r="C19" s="57"/>
-      <c r="D19" s="204"/>
+      <c r="D19" s="214"/>
       <c r="E19" t="s">
         <v>79</v>
       </c>
@@ -8394,9 +8393,9 @@
       </c>
     </row>
     <row r="20" spans="2:39" ht="15" customHeight="1">
-      <c r="B20" s="213"/>
+      <c r="B20" s="192"/>
       <c r="C20" s="57"/>
-      <c r="D20" s="205"/>
+      <c r="D20" s="215"/>
       <c r="E20" t="s">
         <v>80</v>
       </c>
@@ -8492,9 +8491,9 @@
       </c>
     </row>
     <row r="21" spans="2:39" ht="15" customHeight="1">
-      <c r="B21" s="213"/>
+      <c r="B21" s="192"/>
       <c r="C21" s="57"/>
-      <c r="D21" s="205"/>
+      <c r="D21" s="215"/>
       <c r="E21" t="s">
         <v>81</v>
       </c>
@@ -8590,9 +8589,9 @@
       </c>
     </row>
     <row r="22" spans="2:39" ht="15" customHeight="1">
-      <c r="B22" s="213"/>
+      <c r="B22" s="192"/>
       <c r="C22" s="57"/>
-      <c r="D22" s="205"/>
+      <c r="D22" s="215"/>
       <c r="F22" s="59"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -8625,18 +8624,18 @@
       <c r="AI22" s="5"/>
     </row>
     <row r="23" spans="2:39" ht="15" customHeight="1">
-      <c r="B23" s="213"/>
+      <c r="B23" s="192"/>
       <c r="C23" s="57"/>
-      <c r="D23" s="205"/>
+      <c r="D23" s="215"/>
       <c r="E23" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F23" s="59"/>
     </row>
     <row r="24" spans="2:39" ht="15" customHeight="1">
-      <c r="B24" s="213"/>
+      <c r="B24" s="192"/>
       <c r="C24" s="57"/>
-      <c r="D24" s="205"/>
+      <c r="D24" s="215"/>
       <c r="F24" s="1" t="s">
         <v>143</v>
       </c>
@@ -8729,9 +8728,9 @@
       </c>
     </row>
     <row r="25" spans="2:39" ht="15" customHeight="1">
-      <c r="B25" s="213"/>
+      <c r="B25" s="192"/>
       <c r="C25" s="57"/>
-      <c r="D25" s="205"/>
+      <c r="D25" s="215"/>
       <c r="E25" t="s">
         <v>79</v>
       </c>
@@ -8827,9 +8826,9 @@
       </c>
     </row>
     <row r="26" spans="2:39" ht="15" customHeight="1">
-      <c r="B26" s="213"/>
+      <c r="B26" s="192"/>
       <c r="C26" s="57"/>
-      <c r="D26" s="205"/>
+      <c r="D26" s="215"/>
       <c r="E26" t="s">
         <v>80</v>
       </c>
@@ -8925,9 +8924,9 @@
       </c>
     </row>
     <row r="27" spans="2:39" ht="15" customHeight="1">
-      <c r="B27" s="213"/>
+      <c r="B27" s="192"/>
       <c r="C27" s="57"/>
-      <c r="D27" s="205"/>
+      <c r="D27" s="215"/>
       <c r="E27" t="s">
         <v>81</v>
       </c>
@@ -9023,7 +9022,7 @@
       </c>
     </row>
     <row r="28" spans="2:39" ht="15" customHeight="1">
-      <c r="B28" s="213"/>
+      <c r="B28" s="192"/>
       <c r="C28" s="57"/>
       <c r="D28" s="57"/>
       <c r="G28" s="5"/>
@@ -9061,7 +9060,7 @@
       <c r="AM28" s="5"/>
     </row>
     <row r="29" spans="2:39" ht="15" customHeight="1">
-      <c r="B29" s="213"/>
+      <c r="B29" s="192"/>
       <c r="C29" s="57"/>
       <c r="D29" s="57"/>
       <c r="E29" s="1" t="s">
@@ -9103,7 +9102,7 @@
       <c r="AM29" s="5"/>
     </row>
     <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1">
-      <c r="B30" s="213"/>
+      <c r="B30" s="192"/>
       <c r="C30" s="57"/>
       <c r="D30" s="57"/>
       <c r="E30" s="1"/>
@@ -9143,9 +9142,9 @@
       <c r="AM30" s="5"/>
     </row>
     <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1">
-      <c r="B31" s="213"/>
+      <c r="B31" s="192"/>
       <c r="C31" s="57"/>
-      <c r="D31" s="204" t="s">
+      <c r="D31" s="214" t="s">
         <v>84</v>
       </c>
       <c r="E31" s="60" t="s">
@@ -9195,9 +9194,9 @@
       <c r="AM31" s="5"/>
     </row>
     <row r="32" spans="2:39" ht="15" customHeight="1">
-      <c r="B32" s="213"/>
+      <c r="B32" s="192"/>
       <c r="C32" s="57"/>
-      <c r="D32" s="204"/>
+      <c r="D32" s="214"/>
       <c r="E32" s="65" t="s">
         <v>90</v>
       </c>
@@ -9245,9 +9244,9 @@
       <c r="AM32" s="5"/>
     </row>
     <row r="33" spans="2:74" ht="15" customHeight="1">
-      <c r="B33" s="213"/>
+      <c r="B33" s="192"/>
       <c r="C33" s="57"/>
-      <c r="D33" s="204"/>
+      <c r="D33" s="214"/>
       <c r="E33" s="68" t="s">
         <v>95</v>
       </c>
@@ -9295,9 +9294,9 @@
       <c r="AM33" s="5"/>
     </row>
     <row r="34" spans="2:74" ht="15" customHeight="1">
-      <c r="B34" s="213"/>
+      <c r="B34" s="192"/>
       <c r="C34" s="57"/>
-      <c r="D34" s="204"/>
+      <c r="D34" s="214"/>
       <c r="E34" s="71" t="s">
         <v>97</v>
       </c>
@@ -9345,9 +9344,9 @@
       <c r="AM34" s="5"/>
     </row>
     <row r="35" spans="2:74" ht="15" customHeight="1">
-      <c r="B35" s="213"/>
+      <c r="B35" s="192"/>
       <c r="C35" s="57"/>
-      <c r="D35" s="204"/>
+      <c r="D35" s="214"/>
       <c r="E35" s="68" t="s">
         <v>99</v>
       </c>
@@ -9395,9 +9394,9 @@
       <c r="AM35" s="5"/>
     </row>
     <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1">
-      <c r="B36" s="213"/>
+      <c r="B36" s="192"/>
       <c r="C36" s="57"/>
-      <c r="D36" s="204"/>
+      <c r="D36" s="214"/>
       <c r="E36" s="74" t="s">
         <v>101</v>
       </c>
@@ -9484,23 +9483,23 @@
       <c r="AM37" s="5"/>
     </row>
     <row r="38" spans="2:74" s="39" customFormat="1" ht="14.25" customHeight="1">
-      <c r="C38" s="206" t="s">
+      <c r="C38" s="191" t="s">
         <v>103</v>
       </c>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="206"/>
-      <c r="H38" s="206"/>
-      <c r="I38" s="206"/>
-      <c r="J38" s="206"/>
-      <c r="K38" s="206"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="206"/>
-      <c r="N38" s="206"/>
-      <c r="O38" s="206"/>
-      <c r="P38" s="206"/>
-      <c r="Q38" s="206"/>
+      <c r="D38" s="191"/>
+      <c r="E38" s="191"/>
+      <c r="F38" s="191"/>
+      <c r="G38" s="191"/>
+      <c r="H38" s="191"/>
+      <c r="I38" s="191"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="191"/>
+      <c r="L38" s="191"/>
+      <c r="M38" s="191"/>
+      <c r="N38" s="191"/>
+      <c r="O38" s="191"/>
+      <c r="P38" s="191"/>
+      <c r="Q38" s="191"/>
       <c r="R38" s="49"/>
       <c r="S38" s="49"/>
       <c r="T38" s="49"/>
@@ -9633,10 +9632,10 @@
       </c>
     </row>
     <row r="43" spans="2:74" ht="15" customHeight="1">
-      <c r="B43" s="208" t="s">
+      <c r="B43" s="222" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="203" t="s">
+      <c r="D43" s="213" t="s">
         <v>105</v>
       </c>
       <c r="E43" s="78" t="s">
@@ -9738,8 +9737,8 @@
       </c>
     </row>
     <row r="44" spans="2:74">
-      <c r="B44" s="208"/>
-      <c r="D44" s="204"/>
+      <c r="B44" s="222"/>
+      <c r="D44" s="214"/>
       <c r="E44" s="81" t="s">
         <v>90</v>
       </c>
@@ -9839,8 +9838,8 @@
       </c>
     </row>
     <row r="45" spans="2:74">
-      <c r="B45" s="208"/>
-      <c r="D45" s="204"/>
+      <c r="B45" s="222"/>
+      <c r="D45" s="214"/>
       <c r="E45" s="82" t="s">
         <v>90</v>
       </c>
@@ -9940,8 +9939,8 @@
       </c>
     </row>
     <row r="46" spans="2:74">
-      <c r="B46" s="208"/>
-      <c r="D46" s="205"/>
+      <c r="B46" s="222"/>
+      <c r="D46" s="215"/>
       <c r="E46" s="78" t="s">
         <v>95</v>
       </c>
@@ -10074,8 +10073,8 @@
       <c r="BV46" s="5"/>
     </row>
     <row r="47" spans="2:74">
-      <c r="B47" s="208"/>
-      <c r="D47" s="205"/>
+      <c r="B47" s="222"/>
+      <c r="D47" s="215"/>
       <c r="E47" s="78" t="s">
         <v>95</v>
       </c>
@@ -10208,8 +10207,8 @@
       <c r="BV47" s="5"/>
     </row>
     <row r="48" spans="2:74">
-      <c r="B48" s="208"/>
-      <c r="D48" s="205"/>
+      <c r="B48" s="222"/>
+      <c r="D48" s="215"/>
       <c r="E48" s="78" t="s">
         <v>95</v>
       </c>
@@ -10342,8 +10341,8 @@
       <c r="BV48" s="5"/>
     </row>
     <row r="49" spans="2:74">
-      <c r="B49" s="208"/>
-      <c r="D49" s="205"/>
+      <c r="B49" s="222"/>
+      <c r="D49" s="215"/>
       <c r="E49" s="78" t="s">
         <v>97</v>
       </c>
@@ -10476,8 +10475,8 @@
       <c r="BV49" s="5"/>
     </row>
     <row r="50" spans="2:74">
-      <c r="B50" s="208"/>
-      <c r="D50" s="205"/>
+      <c r="B50" s="222"/>
+      <c r="D50" s="215"/>
       <c r="E50" s="78" t="s">
         <v>97</v>
       </c>
@@ -10610,8 +10609,8 @@
       <c r="BV50" s="5"/>
     </row>
     <row r="51" spans="2:74">
-      <c r="B51" s="208"/>
-      <c r="D51" s="205"/>
+      <c r="B51" s="222"/>
+      <c r="D51" s="215"/>
       <c r="E51" s="78" t="s">
         <v>97</v>
       </c>
@@ -10744,8 +10743,8 @@
       <c r="BV51" s="5"/>
     </row>
     <row r="52" spans="2:74">
-      <c r="B52" s="208"/>
-      <c r="D52" s="205"/>
+      <c r="B52" s="222"/>
+      <c r="D52" s="215"/>
       <c r="E52" s="78" t="s">
         <v>99</v>
       </c>
@@ -10878,8 +10877,8 @@
       <c r="BV52" s="5"/>
     </row>
     <row r="53" spans="2:74">
-      <c r="B53" s="208"/>
-      <c r="D53" s="205"/>
+      <c r="B53" s="222"/>
+      <c r="D53" s="215"/>
       <c r="E53" s="78" t="s">
         <v>99</v>
       </c>
@@ -11012,8 +11011,8 @@
       <c r="BV53" s="5"/>
     </row>
     <row r="54" spans="2:74">
-      <c r="B54" s="208"/>
-      <c r="D54" s="205"/>
+      <c r="B54" s="222"/>
+      <c r="D54" s="215"/>
       <c r="E54" s="78" t="s">
         <v>99</v>
       </c>
@@ -11146,8 +11145,8 @@
       <c r="BV54" s="5"/>
     </row>
     <row r="55" spans="2:74">
-      <c r="B55" s="208"/>
-      <c r="D55" s="205"/>
+      <c r="B55" s="222"/>
+      <c r="D55" s="215"/>
       <c r="E55" s="78" t="s">
         <v>101</v>
       </c>
@@ -11280,8 +11279,8 @@
       <c r="BV55" s="5"/>
     </row>
     <row r="56" spans="2:74">
-      <c r="B56" s="208"/>
-      <c r="D56" s="205"/>
+      <c r="B56" s="222"/>
+      <c r="D56" s="215"/>
       <c r="E56" s="78" t="s">
         <v>101</v>
       </c>
@@ -11414,8 +11413,8 @@
       <c r="BV56" s="5"/>
     </row>
     <row r="57" spans="2:74">
-      <c r="B57" s="208"/>
-      <c r="D57" s="205"/>
+      <c r="B57" s="222"/>
+      <c r="D57" s="215"/>
       <c r="E57" s="78" t="s">
         <v>101</v>
       </c>
@@ -11548,7 +11547,7 @@
       <c r="BV57" s="5"/>
     </row>
     <row r="58" spans="2:74">
-      <c r="B58" s="208"/>
+      <c r="B58" s="222"/>
       <c r="D58" s="57"/>
       <c r="E58" s="81"/>
       <c r="F58" s="81"/>
@@ -11617,7 +11616,7 @@
       <c r="BV58" s="5"/>
     </row>
     <row r="59" spans="2:74">
-      <c r="B59" s="208"/>
+      <c r="B59" s="222"/>
       <c r="D59" s="57"/>
       <c r="E59" s="81"/>
       <c r="F59" s="81"/>
@@ -11686,7 +11685,7 @@
       <c r="BV59" s="5"/>
     </row>
     <row r="60" spans="2:74">
-      <c r="B60" s="208"/>
+      <c r="B60" s="222"/>
       <c r="D60" s="57"/>
       <c r="E60" s="81"/>
       <c r="F60" s="81"/>
@@ -11755,7 +11754,7 @@
       <c r="BV60" s="5"/>
     </row>
     <row r="61" spans="2:74">
-      <c r="B61" s="208"/>
+      <c r="B61" s="222"/>
       <c r="D61" s="83"/>
       <c r="E61" s="81"/>
       <c r="F61" s="81"/>
@@ -11851,8 +11850,8 @@
       </c>
     </row>
     <row r="62" spans="2:74">
-      <c r="B62" s="208"/>
-      <c r="D62" s="203" t="s">
+      <c r="B62" s="222"/>
+      <c r="D62" s="213" t="s">
         <v>106</v>
       </c>
       <c r="E62" s="78" t="s">
@@ -11954,8 +11953,8 @@
       </c>
     </row>
     <row r="63" spans="2:74">
-      <c r="B63" s="208"/>
-      <c r="D63" s="204"/>
+      <c r="B63" s="222"/>
+      <c r="D63" s="214"/>
       <c r="E63" s="81" t="s">
         <v>90</v>
       </c>
@@ -12055,8 +12054,8 @@
       </c>
     </row>
     <row r="64" spans="2:74">
-      <c r="B64" s="208"/>
-      <c r="D64" s="204"/>
+      <c r="B64" s="222"/>
+      <c r="D64" s="214"/>
       <c r="E64" s="82" t="s">
         <v>90</v>
       </c>
@@ -12156,8 +12155,8 @@
       </c>
     </row>
     <row r="65" spans="2:74">
-      <c r="B65" s="208"/>
-      <c r="D65" s="205"/>
+      <c r="B65" s="222"/>
+      <c r="D65" s="215"/>
       <c r="E65" s="78" t="s">
         <v>95</v>
       </c>
@@ -12257,8 +12256,8 @@
       </c>
     </row>
     <row r="66" spans="2:74">
-      <c r="B66" s="208"/>
-      <c r="D66" s="205"/>
+      <c r="B66" s="222"/>
+      <c r="D66" s="215"/>
       <c r="E66" s="78" t="s">
         <v>95</v>
       </c>
@@ -12358,8 +12357,8 @@
       </c>
     </row>
     <row r="67" spans="2:74">
-      <c r="B67" s="208"/>
-      <c r="D67" s="205"/>
+      <c r="B67" s="222"/>
+      <c r="D67" s="215"/>
       <c r="E67" s="78" t="s">
         <v>95</v>
       </c>
@@ -12459,8 +12458,8 @@
       </c>
     </row>
     <row r="68" spans="2:74">
-      <c r="B68" s="208"/>
-      <c r="D68" s="205"/>
+      <c r="B68" s="222"/>
+      <c r="D68" s="215"/>
       <c r="E68" s="78" t="s">
         <v>97</v>
       </c>
@@ -12560,8 +12559,8 @@
       </c>
     </row>
     <row r="69" spans="2:74">
-      <c r="B69" s="208"/>
-      <c r="D69" s="205"/>
+      <c r="B69" s="222"/>
+      <c r="D69" s="215"/>
       <c r="E69" s="78" t="s">
         <v>97</v>
       </c>
@@ -12661,8 +12660,8 @@
       </c>
     </row>
     <row r="70" spans="2:74">
-      <c r="B70" s="208"/>
-      <c r="D70" s="205"/>
+      <c r="B70" s="222"/>
+      <c r="D70" s="215"/>
       <c r="E70" s="78" t="s">
         <v>97</v>
       </c>
@@ -12762,8 +12761,8 @@
       </c>
     </row>
     <row r="71" spans="2:74">
-      <c r="B71" s="208"/>
-      <c r="D71" s="205"/>
+      <c r="B71" s="222"/>
+      <c r="D71" s="215"/>
       <c r="E71" s="78" t="s">
         <v>99</v>
       </c>
@@ -12896,8 +12895,8 @@
       <c r="BV71" s="5"/>
     </row>
     <row r="72" spans="2:74">
-      <c r="B72" s="208"/>
-      <c r="D72" s="205"/>
+      <c r="B72" s="222"/>
+      <c r="D72" s="215"/>
       <c r="E72" s="78" t="s">
         <v>99</v>
       </c>
@@ -13030,8 +13029,8 @@
       <c r="BV72" s="5"/>
     </row>
     <row r="73" spans="2:74">
-      <c r="B73" s="208"/>
-      <c r="D73" s="205"/>
+      <c r="B73" s="222"/>
+      <c r="D73" s="215"/>
       <c r="E73" s="78" t="s">
         <v>99</v>
       </c>
@@ -13164,8 +13163,8 @@
       <c r="BV73" s="5"/>
     </row>
     <row r="74" spans="2:74">
-      <c r="B74" s="208"/>
-      <c r="D74" s="205"/>
+      <c r="B74" s="222"/>
+      <c r="D74" s="215"/>
       <c r="E74" s="78" t="s">
         <v>101</v>
       </c>
@@ -13298,8 +13297,8 @@
       <c r="BV74" s="5"/>
     </row>
     <row r="75" spans="2:74">
-      <c r="B75" s="208"/>
-      <c r="D75" s="205"/>
+      <c r="B75" s="222"/>
+      <c r="D75" s="215"/>
       <c r="E75" s="78" t="s">
         <v>101</v>
       </c>
@@ -13432,8 +13431,8 @@
       <c r="BV75" s="5"/>
     </row>
     <row r="76" spans="2:74">
-      <c r="B76" s="208"/>
-      <c r="D76" s="205"/>
+      <c r="B76" s="222"/>
+      <c r="D76" s="215"/>
       <c r="E76" s="78" t="s">
         <v>101</v>
       </c>
@@ -13566,13 +13565,13 @@
       <c r="BV76" s="5"/>
     </row>
     <row r="77" spans="2:74">
-      <c r="B77" s="208"/>
+      <c r="B77" s="222"/>
       <c r="D77" s="83"/>
       <c r="E77" s="81"/>
       <c r="F77" s="81"/>
     </row>
     <row r="78" spans="2:74">
-      <c r="B78" s="208"/>
+      <c r="B78" s="222"/>
       <c r="D78" s="39"/>
       <c r="E78" s="84"/>
       <c r="F78" s="84"/>
@@ -13668,8 +13667,8 @@
       </c>
     </row>
     <row r="79" spans="2:74">
-      <c r="B79" s="208"/>
-      <c r="D79" s="203" t="s">
+      <c r="B79" s="222"/>
+      <c r="D79" s="213" t="s">
         <v>107</v>
       </c>
       <c r="E79" s="78" t="s">
@@ -13771,8 +13770,8 @@
       <c r="AO79" s="1"/>
     </row>
     <row r="80" spans="2:74">
-      <c r="B80" s="208"/>
-      <c r="D80" s="204"/>
+      <c r="B80" s="222"/>
+      <c r="D80" s="214"/>
       <c r="E80" s="81" t="s">
         <v>90</v>
       </c>
@@ -13872,8 +13871,8 @@
       <c r="AO80" s="1"/>
     </row>
     <row r="81" spans="2:41">
-      <c r="B81" s="208"/>
-      <c r="D81" s="204"/>
+      <c r="B81" s="222"/>
+      <c r="D81" s="214"/>
       <c r="E81" s="82" t="s">
         <v>90</v>
       </c>
@@ -13973,8 +13972,8 @@
       <c r="AO81" s="1"/>
     </row>
     <row r="82" spans="2:41">
-      <c r="B82" s="209"/>
-      <c r="D82" s="205"/>
+      <c r="B82" s="223"/>
+      <c r="D82" s="215"/>
       <c r="E82" s="78" t="s">
         <v>95</v>
       </c>
@@ -14073,8 +14072,8 @@
       </c>
     </row>
     <row r="83" spans="2:41">
-      <c r="B83" s="209"/>
-      <c r="D83" s="205"/>
+      <c r="B83" s="223"/>
+      <c r="D83" s="215"/>
       <c r="E83" s="78" t="s">
         <v>95</v>
       </c>
@@ -14173,8 +14172,8 @@
       </c>
     </row>
     <row r="84" spans="2:41">
-      <c r="B84" s="209"/>
-      <c r="D84" s="205"/>
+      <c r="B84" s="223"/>
+      <c r="D84" s="215"/>
       <c r="E84" s="78" t="s">
         <v>95</v>
       </c>
@@ -14275,8 +14274,8 @@
       <c r="AL84" s="5"/>
     </row>
     <row r="85" spans="2:41">
-      <c r="B85" s="209"/>
-      <c r="D85" s="205"/>
+      <c r="B85" s="223"/>
+      <c r="D85" s="215"/>
       <c r="E85" s="78" t="s">
         <v>97</v>
       </c>
@@ -14377,8 +14376,8 @@
       <c r="AL85" s="5"/>
     </row>
     <row r="86" spans="2:41">
-      <c r="B86" s="209"/>
-      <c r="D86" s="205"/>
+      <c r="B86" s="223"/>
+      <c r="D86" s="215"/>
       <c r="E86" s="78" t="s">
         <v>97</v>
       </c>
@@ -14479,8 +14478,8 @@
       <c r="AL86" s="5"/>
     </row>
     <row r="87" spans="2:41">
-      <c r="B87" s="209"/>
-      <c r="D87" s="205"/>
+      <c r="B87" s="223"/>
+      <c r="D87" s="215"/>
       <c r="E87" s="78" t="s">
         <v>97</v>
       </c>
@@ -14581,8 +14580,8 @@
       <c r="AL87" s="5"/>
     </row>
     <row r="88" spans="2:41">
-      <c r="B88" s="209"/>
-      <c r="D88" s="205"/>
+      <c r="B88" s="223"/>
+      <c r="D88" s="215"/>
       <c r="E88" s="78" t="s">
         <v>99</v>
       </c>
@@ -14683,8 +14682,8 @@
       <c r="AL88" s="5"/>
     </row>
     <row r="89" spans="2:41">
-      <c r="B89" s="209"/>
-      <c r="D89" s="205"/>
+      <c r="B89" s="223"/>
+      <c r="D89" s="215"/>
       <c r="E89" s="78" t="s">
         <v>99</v>
       </c>
@@ -14785,8 +14784,8 @@
       <c r="AL89" s="5"/>
     </row>
     <row r="90" spans="2:41">
-      <c r="B90" s="209"/>
-      <c r="D90" s="205"/>
+      <c r="B90" s="223"/>
+      <c r="D90" s="215"/>
       <c r="E90" s="78" t="s">
         <v>99</v>
       </c>
@@ -14887,8 +14886,8 @@
       <c r="AL90" s="5"/>
     </row>
     <row r="91" spans="2:41">
-      <c r="B91" s="209"/>
-      <c r="D91" s="205"/>
+      <c r="B91" s="223"/>
+      <c r="D91" s="215"/>
       <c r="E91" s="78" t="s">
         <v>101</v>
       </c>
@@ -14989,8 +14988,8 @@
       <c r="AL91" s="5"/>
     </row>
     <row r="92" spans="2:41">
-      <c r="B92" s="209"/>
-      <c r="D92" s="205"/>
+      <c r="B92" s="223"/>
+      <c r="D92" s="215"/>
       <c r="E92" s="78" t="s">
         <v>101</v>
       </c>
@@ -15091,8 +15090,8 @@
       <c r="AL92" s="5"/>
     </row>
     <row r="93" spans="2:41">
-      <c r="B93" s="209"/>
-      <c r="D93" s="205"/>
+      <c r="B93" s="223"/>
+      <c r="D93" s="215"/>
       <c r="E93" s="78" t="s">
         <v>101</v>
       </c>
@@ -15193,10 +15192,10 @@
       <c r="AL93" s="5"/>
     </row>
     <row r="94" spans="2:41">
-      <c r="B94" s="209"/>
+      <c r="B94" s="223"/>
     </row>
     <row r="95" spans="2:41" ht="15" customHeight="1">
-      <c r="B95" s="209"/>
+      <c r="B95" s="223"/>
       <c r="G95" s="1" t="s">
         <v>143</v>
       </c>
@@ -15289,8 +15288,8 @@
       </c>
     </row>
     <row r="96" spans="2:41">
-      <c r="B96" s="209"/>
-      <c r="D96" s="203" t="s">
+      <c r="B96" s="223"/>
+      <c r="D96" s="213" t="s">
         <v>108</v>
       </c>
       <c r="E96" s="78" t="s">
@@ -15391,8 +15390,8 @@
       </c>
     </row>
     <row r="97" spans="2:36">
-      <c r="B97" s="209"/>
-      <c r="D97" s="204"/>
+      <c r="B97" s="223"/>
+      <c r="D97" s="214"/>
       <c r="E97" s="81" t="s">
         <v>90</v>
       </c>
@@ -15491,8 +15490,8 @@
       </c>
     </row>
     <row r="98" spans="2:36">
-      <c r="B98" s="209"/>
-      <c r="D98" s="204"/>
+      <c r="B98" s="223"/>
+      <c r="D98" s="214"/>
       <c r="E98" s="82" t="s">
         <v>90</v>
       </c>
@@ -15591,8 +15590,8 @@
       </c>
     </row>
     <row r="99" spans="2:36">
-      <c r="B99" s="209"/>
-      <c r="D99" s="205"/>
+      <c r="B99" s="223"/>
+      <c r="D99" s="215"/>
       <c r="E99" s="78" t="s">
         <v>95</v>
       </c>
@@ -15691,8 +15690,8 @@
       </c>
     </row>
     <row r="100" spans="2:36">
-      <c r="B100" s="209"/>
-      <c r="D100" s="205"/>
+      <c r="B100" s="223"/>
+      <c r="D100" s="215"/>
       <c r="E100" s="78" t="s">
         <v>95</v>
       </c>
@@ -15791,8 +15790,8 @@
       </c>
     </row>
     <row r="101" spans="2:36">
-      <c r="B101" s="209"/>
-      <c r="D101" s="205"/>
+      <c r="B101" s="223"/>
+      <c r="D101" s="215"/>
       <c r="E101" s="78" t="s">
         <v>95</v>
       </c>
@@ -15891,8 +15890,8 @@
       </c>
     </row>
     <row r="102" spans="2:36">
-      <c r="B102" s="209"/>
-      <c r="D102" s="205"/>
+      <c r="B102" s="223"/>
+      <c r="D102" s="215"/>
       <c r="E102" s="78" t="s">
         <v>97</v>
       </c>
@@ -15991,8 +15990,8 @@
       </c>
     </row>
     <row r="103" spans="2:36">
-      <c r="B103" s="209"/>
-      <c r="D103" s="205"/>
+      <c r="B103" s="223"/>
+      <c r="D103" s="215"/>
       <c r="E103" s="78" t="s">
         <v>97</v>
       </c>
@@ -16091,8 +16090,8 @@
       </c>
     </row>
     <row r="104" spans="2:36">
-      <c r="B104" s="209"/>
-      <c r="D104" s="205"/>
+      <c r="B104" s="223"/>
+      <c r="D104" s="215"/>
       <c r="E104" s="78" t="s">
         <v>97</v>
       </c>
@@ -16191,8 +16190,8 @@
       </c>
     </row>
     <row r="105" spans="2:36">
-      <c r="B105" s="209"/>
-      <c r="D105" s="205"/>
+      <c r="B105" s="223"/>
+      <c r="D105" s="215"/>
       <c r="E105" s="78" t="s">
         <v>99</v>
       </c>
@@ -16291,8 +16290,8 @@
       </c>
     </row>
     <row r="106" spans="2:36">
-      <c r="B106" s="209"/>
-      <c r="D106" s="205"/>
+      <c r="B106" s="223"/>
+      <c r="D106" s="215"/>
       <c r="E106" s="78" t="s">
         <v>99</v>
       </c>
@@ -16391,8 +16390,8 @@
       </c>
     </row>
     <row r="107" spans="2:36">
-      <c r="B107" s="209"/>
-      <c r="D107" s="205"/>
+      <c r="B107" s="223"/>
+      <c r="D107" s="215"/>
       <c r="E107" s="78" t="s">
         <v>99</v>
       </c>
@@ -16491,8 +16490,8 @@
       </c>
     </row>
     <row r="108" spans="2:36">
-      <c r="B108" s="209"/>
-      <c r="D108" s="205"/>
+      <c r="B108" s="223"/>
+      <c r="D108" s="215"/>
       <c r="E108" s="78" t="s">
         <v>101</v>
       </c>
@@ -16591,8 +16590,8 @@
       </c>
     </row>
     <row r="109" spans="2:36">
-      <c r="B109" s="209"/>
-      <c r="D109" s="205"/>
+      <c r="B109" s="223"/>
+      <c r="D109" s="215"/>
       <c r="E109" s="78" t="s">
         <v>101</v>
       </c>
@@ -16691,8 +16690,8 @@
       </c>
     </row>
     <row r="110" spans="2:36">
-      <c r="B110" s="209"/>
-      <c r="D110" s="205"/>
+      <c r="B110" s="223"/>
+      <c r="D110" s="215"/>
       <c r="E110" s="78" t="s">
         <v>101</v>
       </c>
@@ -16791,10 +16790,10 @@
       </c>
     </row>
     <row r="111" spans="2:36">
-      <c r="B111" s="209"/>
+      <c r="B111" s="223"/>
     </row>
     <row r="112" spans="2:36">
-      <c r="B112" s="209"/>
+      <c r="B112" s="223"/>
       <c r="G112" s="1" t="s">
         <v>143</v>
       </c>
@@ -16887,8 +16886,8 @@
       </c>
     </row>
     <row r="113" spans="2:36">
-      <c r="B113" s="209"/>
-      <c r="D113" s="203" t="s">
+      <c r="B113" s="223"/>
+      <c r="D113" s="213" t="s">
         <v>109</v>
       </c>
       <c r="E113" s="78" t="s">
@@ -16990,8 +16989,8 @@
       </c>
     </row>
     <row r="114" spans="2:36">
-      <c r="B114" s="209"/>
-      <c r="D114" s="204"/>
+      <c r="B114" s="223"/>
+      <c r="D114" s="214"/>
       <c r="E114" s="81" t="s">
         <v>90</v>
       </c>
@@ -17091,8 +17090,8 @@
       </c>
     </row>
     <row r="115" spans="2:36">
-      <c r="B115" s="209"/>
-      <c r="D115" s="204"/>
+      <c r="B115" s="223"/>
+      <c r="D115" s="214"/>
       <c r="E115" s="82" t="s">
         <v>90</v>
       </c>
@@ -17192,8 +17191,8 @@
       </c>
     </row>
     <row r="116" spans="2:36">
-      <c r="B116" s="209"/>
-      <c r="D116" s="205"/>
+      <c r="B116" s="223"/>
+      <c r="D116" s="215"/>
       <c r="E116" s="78" t="s">
         <v>95</v>
       </c>
@@ -17293,8 +17292,8 @@
       </c>
     </row>
     <row r="117" spans="2:36">
-      <c r="B117" s="209"/>
-      <c r="D117" s="205"/>
+      <c r="B117" s="223"/>
+      <c r="D117" s="215"/>
       <c r="E117" s="78" t="s">
         <v>95</v>
       </c>
@@ -17394,8 +17393,8 @@
       </c>
     </row>
     <row r="118" spans="2:36">
-      <c r="B118" s="209"/>
-      <c r="D118" s="205"/>
+      <c r="B118" s="223"/>
+      <c r="D118" s="215"/>
       <c r="E118" s="78" t="s">
         <v>95</v>
       </c>
@@ -17495,8 +17494,8 @@
       </c>
     </row>
     <row r="119" spans="2:36">
-      <c r="B119" s="209"/>
-      <c r="D119" s="205"/>
+      <c r="B119" s="223"/>
+      <c r="D119" s="215"/>
       <c r="E119" s="78" t="s">
         <v>97</v>
       </c>
@@ -17596,8 +17595,8 @@
       </c>
     </row>
     <row r="120" spans="2:36">
-      <c r="B120" s="209"/>
-      <c r="D120" s="205"/>
+      <c r="B120" s="223"/>
+      <c r="D120" s="215"/>
       <c r="E120" s="78" t="s">
         <v>97</v>
       </c>
@@ -17697,8 +17696,8 @@
       </c>
     </row>
     <row r="121" spans="2:36">
-      <c r="B121" s="209"/>
-      <c r="D121" s="205"/>
+      <c r="B121" s="223"/>
+      <c r="D121" s="215"/>
       <c r="E121" s="78" t="s">
         <v>97</v>
       </c>
@@ -17798,8 +17797,8 @@
       </c>
     </row>
     <row r="122" spans="2:36">
-      <c r="B122" s="209"/>
-      <c r="D122" s="205"/>
+      <c r="B122" s="223"/>
+      <c r="D122" s="215"/>
       <c r="E122" s="78" t="s">
         <v>99</v>
       </c>
@@ -17899,8 +17898,8 @@
       </c>
     </row>
     <row r="123" spans="2:36">
-      <c r="B123" s="209"/>
-      <c r="D123" s="205"/>
+      <c r="B123" s="223"/>
+      <c r="D123" s="215"/>
       <c r="E123" s="78" t="s">
         <v>99</v>
       </c>
@@ -18000,8 +17999,8 @@
       </c>
     </row>
     <row r="124" spans="2:36">
-      <c r="B124" s="209"/>
-      <c r="D124" s="205"/>
+      <c r="B124" s="223"/>
+      <c r="D124" s="215"/>
       <c r="E124" s="78" t="s">
         <v>99</v>
       </c>
@@ -18101,8 +18100,8 @@
       </c>
     </row>
     <row r="125" spans="2:36">
-      <c r="B125" s="209"/>
-      <c r="D125" s="205"/>
+      <c r="B125" s="223"/>
+      <c r="D125" s="215"/>
       <c r="E125" s="78" t="s">
         <v>101</v>
       </c>
@@ -18202,8 +18201,8 @@
       </c>
     </row>
     <row r="126" spans="2:36">
-      <c r="B126" s="209"/>
-      <c r="D126" s="205"/>
+      <c r="B126" s="223"/>
+      <c r="D126" s="215"/>
       <c r="E126" s="78" t="s">
         <v>101</v>
       </c>
@@ -18303,8 +18302,8 @@
       </c>
     </row>
     <row r="127" spans="2:36">
-      <c r="B127" s="209"/>
-      <c r="D127" s="205"/>
+      <c r="B127" s="223"/>
+      <c r="D127" s="215"/>
       <c r="E127" s="78" t="s">
         <v>101</v>
       </c>
@@ -18407,23 +18406,23 @@
       <c r="B128" s="86"/>
     </row>
     <row r="129" spans="2:28">
-      <c r="B129" s="207" t="s">
+      <c r="B129" s="216" t="s">
         <v>110</v>
       </c>
-      <c r="C129" s="206"/>
-      <c r="D129" s="206"/>
-      <c r="E129" s="206"/>
-      <c r="F129" s="206"/>
-      <c r="G129" s="206"/>
-      <c r="H129" s="206"/>
-      <c r="I129" s="206"/>
-      <c r="J129" s="206"/>
-      <c r="K129" s="206"/>
-      <c r="L129" s="206"/>
-      <c r="M129" s="206"/>
-      <c r="N129" s="206"/>
-      <c r="O129" s="206"/>
-      <c r="P129" s="206"/>
+      <c r="C129" s="191"/>
+      <c r="D129" s="191"/>
+      <c r="E129" s="191"/>
+      <c r="F129" s="191"/>
+      <c r="G129" s="191"/>
+      <c r="H129" s="191"/>
+      <c r="I129" s="191"/>
+      <c r="J129" s="191"/>
+      <c r="K129" s="191"/>
+      <c r="L129" s="191"/>
+      <c r="M129" s="191"/>
+      <c r="N129" s="191"/>
+      <c r="O129" s="191"/>
+      <c r="P129" s="191"/>
       <c r="Q129" s="49"/>
       <c r="R129" s="49"/>
       <c r="S129" s="49"/>
@@ -18458,21 +18457,21 @@
     </row>
     <row r="131" spans="2:28">
       <c r="B131" s="39"/>
-      <c r="C131" s="197" t="s">
+      <c r="C131" s="217" t="s">
         <v>111</v>
       </c>
-      <c r="D131" s="198"/>
-      <c r="E131" s="198"/>
-      <c r="F131" s="198"/>
-      <c r="G131" s="198"/>
-      <c r="H131" s="198"/>
-      <c r="I131" s="200" t="s">
+      <c r="D131" s="218"/>
+      <c r="E131" s="218"/>
+      <c r="F131" s="218"/>
+      <c r="G131" s="218"/>
+      <c r="H131" s="218"/>
+      <c r="I131" s="219" t="s">
         <v>112</v>
       </c>
-      <c r="J131" s="201"/>
-      <c r="K131" s="201"/>
-      <c r="L131" s="201"/>
-      <c r="M131" s="202"/>
+      <c r="J131" s="220"/>
+      <c r="K131" s="220"/>
+      <c r="L131" s="220"/>
+      <c r="M131" s="221"/>
       <c r="N131" s="88" t="s">
         <v>113</v>
       </c>
@@ -18490,14 +18489,14 @@
     </row>
     <row r="132" spans="2:28" ht="14.9" customHeight="1">
       <c r="B132" s="39"/>
-      <c r="C132" s="187" t="s">
+      <c r="C132" s="207" t="s">
         <v>115</v>
       </c>
-      <c r="D132" s="188"/>
-      <c r="E132" s="188"/>
-      <c r="F132" s="188"/>
-      <c r="G132" s="188"/>
-      <c r="H132" s="189"/>
+      <c r="D132" s="208"/>
+      <c r="E132" s="208"/>
+      <c r="F132" s="208"/>
+      <c r="G132" s="208"/>
+      <c r="H132" s="209"/>
       <c r="I132" t="s">
         <v>92</v>
       </c>
@@ -18508,14 +18507,14 @@
     </row>
     <row r="133" spans="2:28" ht="14.9" customHeight="1">
       <c r="B133" s="39"/>
-      <c r="C133" s="187" t="s">
+      <c r="C133" s="207" t="s">
         <v>116</v>
       </c>
-      <c r="D133" s="188"/>
-      <c r="E133" s="188"/>
-      <c r="F133" s="188"/>
-      <c r="G133" s="188"/>
-      <c r="H133" s="189"/>
+      <c r="D133" s="208"/>
+      <c r="E133" s="208"/>
+      <c r="F133" s="208"/>
+      <c r="G133" s="208"/>
+      <c r="H133" s="209"/>
       <c r="I133" s="99" t="s">
         <v>92</v>
       </c>
@@ -18538,21 +18537,21 @@
     </row>
     <row r="134" spans="2:28" ht="45" customHeight="1">
       <c r="B134" s="39"/>
-      <c r="C134" s="187" t="s">
+      <c r="C134" s="207" t="s">
         <v>105</v>
       </c>
-      <c r="D134" s="188"/>
-      <c r="E134" s="188"/>
-      <c r="F134" s="188"/>
-      <c r="G134" s="188"/>
-      <c r="H134" s="189"/>
-      <c r="I134" s="193" t="s">
+      <c r="D134" s="208"/>
+      <c r="E134" s="208"/>
+      <c r="F134" s="208"/>
+      <c r="G134" s="208"/>
+      <c r="H134" s="209"/>
+      <c r="I134" s="210" t="s">
         <v>118</v>
       </c>
-      <c r="J134" s="194"/>
-      <c r="K134" s="194"/>
-      <c r="L134" s="194"/>
-      <c r="M134" s="195"/>
+      <c r="J134" s="211"/>
+      <c r="K134" s="211"/>
+      <c r="L134" s="211"/>
+      <c r="M134" s="212"/>
       <c r="N134" s="104"/>
       <c r="O134" s="104"/>
       <c r="P134" s="105"/>
@@ -18566,21 +18565,21 @@
     </row>
     <row r="135" spans="2:28" ht="46.5" customHeight="1">
       <c r="B135" s="39"/>
-      <c r="C135" s="187" t="s">
+      <c r="C135" s="207" t="s">
         <v>119</v>
       </c>
-      <c r="D135" s="188"/>
-      <c r="E135" s="188"/>
-      <c r="F135" s="188"/>
-      <c r="G135" s="188"/>
-      <c r="H135" s="189"/>
-      <c r="I135" s="193" t="s">
+      <c r="D135" s="208"/>
+      <c r="E135" s="208"/>
+      <c r="F135" s="208"/>
+      <c r="G135" s="208"/>
+      <c r="H135" s="209"/>
+      <c r="I135" s="210" t="s">
         <v>120</v>
       </c>
-      <c r="J135" s="194"/>
-      <c r="K135" s="194"/>
-      <c r="L135" s="194"/>
-      <c r="M135" s="195"/>
+      <c r="J135" s="211"/>
+      <c r="K135" s="211"/>
+      <c r="L135" s="211"/>
+      <c r="M135" s="212"/>
       <c r="N135" s="104"/>
       <c r="O135" s="104"/>
       <c r="P135" s="105"/>
@@ -18594,14 +18593,14 @@
     </row>
     <row r="136" spans="2:28">
       <c r="B136" s="39"/>
-      <c r="C136" s="187" t="s">
+      <c r="C136" s="207" t="s">
         <v>121</v>
       </c>
-      <c r="D136" s="188"/>
-      <c r="E136" s="188"/>
-      <c r="F136" s="188"/>
-      <c r="G136" s="188"/>
-      <c r="H136" s="189"/>
+      <c r="D136" s="208"/>
+      <c r="E136" s="208"/>
+      <c r="F136" s="208"/>
+      <c r="G136" s="208"/>
+      <c r="H136" s="209"/>
       <c r="I136" s="107" t="s">
         <v>92</v>
       </c>
@@ -18622,14 +18621,14 @@
     </row>
     <row r="137" spans="2:28" ht="15" thickBot="1">
       <c r="B137" s="39"/>
-      <c r="C137" s="190" t="s">
+      <c r="C137" s="224" t="s">
         <v>122</v>
       </c>
-      <c r="D137" s="191"/>
-      <c r="E137" s="191"/>
-      <c r="F137" s="191"/>
-      <c r="G137" s="191"/>
-      <c r="H137" s="192"/>
+      <c r="D137" s="225"/>
+      <c r="E137" s="225"/>
+      <c r="F137" s="225"/>
+      <c r="G137" s="225"/>
+      <c r="H137" s="226"/>
       <c r="I137" s="111" t="s">
         <v>92</v>
       </c>
@@ -18650,12 +18649,12 @@
     </row>
     <row r="138" spans="2:28" ht="15" thickBot="1">
       <c r="B138" s="39"/>
-      <c r="C138" s="196"/>
-      <c r="D138" s="196"/>
-      <c r="E138" s="196"/>
-      <c r="F138" s="196"/>
-      <c r="G138" s="196"/>
-      <c r="H138" s="196"/>
+      <c r="C138" s="227"/>
+      <c r="D138" s="227"/>
+      <c r="E138" s="227"/>
+      <c r="F138" s="227"/>
+      <c r="G138" s="227"/>
+      <c r="H138" s="227"/>
       <c r="I138" s="115"/>
       <c r="J138" s="115"/>
       <c r="K138" s="115"/>
@@ -18674,21 +18673,21 @@
     </row>
     <row r="139" spans="2:28">
       <c r="B139" s="39"/>
-      <c r="C139" s="197" t="s">
+      <c r="C139" s="217" t="s">
         <v>123</v>
       </c>
-      <c r="D139" s="198"/>
-      <c r="E139" s="198"/>
-      <c r="F139" s="198"/>
-      <c r="G139" s="198"/>
-      <c r="H139" s="199"/>
-      <c r="I139" s="200" t="s">
+      <c r="D139" s="218"/>
+      <c r="E139" s="218"/>
+      <c r="F139" s="218"/>
+      <c r="G139" s="218"/>
+      <c r="H139" s="228"/>
+      <c r="I139" s="219" t="s">
         <v>112</v>
       </c>
-      <c r="J139" s="201"/>
-      <c r="K139" s="201"/>
-      <c r="L139" s="201"/>
-      <c r="M139" s="202"/>
+      <c r="J139" s="220"/>
+      <c r="K139" s="220"/>
+      <c r="L139" s="220"/>
+      <c r="M139" s="221"/>
       <c r="N139" s="88" t="s">
         <v>113</v>
       </c>
@@ -18706,14 +18705,14 @@
     </row>
     <row r="140" spans="2:28">
       <c r="B140" s="39"/>
-      <c r="C140" s="187" t="s">
+      <c r="C140" s="207" t="s">
         <v>116</v>
       </c>
-      <c r="D140" s="188"/>
-      <c r="E140" s="188"/>
-      <c r="F140" s="188"/>
-      <c r="G140" s="188"/>
-      <c r="H140" s="189"/>
+      <c r="D140" s="208"/>
+      <c r="E140" s="208"/>
+      <c r="F140" s="208"/>
+      <c r="G140" s="208"/>
+      <c r="H140" s="209"/>
       <c r="I140" s="99" t="s">
         <v>92</v>
       </c>
@@ -18797,14 +18796,14 @@
     </row>
     <row r="143" spans="2:28">
       <c r="B143" s="39"/>
-      <c r="C143" s="187" t="s">
+      <c r="C143" s="207" t="s">
         <v>119</v>
       </c>
-      <c r="D143" s="188"/>
-      <c r="E143" s="188"/>
-      <c r="F143" s="188"/>
-      <c r="G143" s="188"/>
-      <c r="H143" s="189"/>
+      <c r="D143" s="208"/>
+      <c r="E143" s="208"/>
+      <c r="F143" s="208"/>
+      <c r="G143" s="208"/>
+      <c r="H143" s="209"/>
       <c r="I143" s="121" t="s">
         <v>124</v>
       </c>
@@ -18825,14 +18824,14 @@
     </row>
     <row r="144" spans="2:28">
       <c r="B144" s="39"/>
-      <c r="C144" s="187" t="s">
+      <c r="C144" s="207" t="s">
         <v>121</v>
       </c>
-      <c r="D144" s="188"/>
-      <c r="E144" s="188"/>
-      <c r="F144" s="188"/>
-      <c r="G144" s="188"/>
-      <c r="H144" s="189"/>
+      <c r="D144" s="208"/>
+      <c r="E144" s="208"/>
+      <c r="F144" s="208"/>
+      <c r="G144" s="208"/>
+      <c r="H144" s="209"/>
       <c r="I144" s="121" t="s">
         <v>124</v>
       </c>
@@ -18853,14 +18852,14 @@
     </row>
     <row r="145" spans="2:23" ht="15" thickBot="1">
       <c r="B145" s="39"/>
-      <c r="C145" s="190" t="s">
+      <c r="C145" s="224" t="s">
         <v>127</v>
       </c>
-      <c r="D145" s="191"/>
-      <c r="E145" s="191"/>
-      <c r="F145" s="191"/>
-      <c r="G145" s="191"/>
-      <c r="H145" s="192"/>
+      <c r="D145" s="225"/>
+      <c r="E145" s="225"/>
+      <c r="F145" s="225"/>
+      <c r="G145" s="225"/>
+      <c r="H145" s="226"/>
       <c r="I145" s="111" t="s">
         <v>92</v>
       </c>
@@ -19112,16 +19111,17 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="C7:Q7"/>
-    <mergeCell ref="B9:B36"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D13:L13"/>
-    <mergeCell ref="C15:P16"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="I135:M135"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="I139:M139"/>
     <mergeCell ref="C134:H134"/>
     <mergeCell ref="I134:M134"/>
     <mergeCell ref="D17:D27"/>
@@ -19138,17 +19138,16 @@
     <mergeCell ref="D79:D93"/>
     <mergeCell ref="D96:D110"/>
     <mergeCell ref="D113:D127"/>
-    <mergeCell ref="I135:M135"/>
-    <mergeCell ref="C136:H136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="I139:M139"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="C7:Q7"/>
+    <mergeCell ref="B9:B36"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="C15:P16"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
@@ -19192,27 +19191,27 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="14"/>
-      <c r="B2" s="228" t="s">
+      <c r="B2" s="229" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="229"/>
-      <c r="D2" s="230"/>
+      <c r="C2" s="230"/>
+      <c r="D2" s="231"/>
       <c r="E2" s="38"/>
-      <c r="F2" s="228" t="s">
+      <c r="F2" s="229" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="228" t="s">
+      <c r="G2" s="230"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="229"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="228" t="s">
+      <c r="J2" s="230"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="229" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="229"/>
-      <c r="N2" s="230"/>
+      <c r="M2" s="230"/>
+      <c r="N2" s="231"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="17" t="s">
@@ -20835,268 +20834,266 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" style="232" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" style="232" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="232"/>
-    <col min="4" max="4" width="9.90625" style="232" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="232"/>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="231" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="231" t="s">
+      <c r="A1" s="179" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="179" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="232">
+      <c r="A2">
         <v>2021</v>
       </c>
-      <c r="B2" s="232">
+      <c r="B2">
         <f>KEEI_계산과정!D56</f>
         <v>184566.95229970396</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="232">
+      <c r="A3">
         <v>2022</v>
       </c>
-      <c r="B3" s="232">
+      <c r="B3">
         <f>KEEI_계산과정!E56</f>
         <v>177348.23877434694</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="232">
+      <c r="A4">
         <v>2023</v>
       </c>
-      <c r="B4" s="232">
+      <c r="B4">
         <f>KEEI_계산과정!F56</f>
         <v>170129.52524898993</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="232">
+      <c r="A5">
         <v>2024</v>
       </c>
-      <c r="B5" s="232">
+      <c r="B5">
         <f>KEEI_계산과정!G56</f>
         <v>162910.81172363291</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="232">
+      <c r="A6">
         <v>2025</v>
       </c>
-      <c r="B6" s="232">
+      <c r="B6">
         <f>KEEI_계산과정!H56</f>
         <v>155692.09819827593</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="232">
+      <c r="A7">
         <v>2026</v>
       </c>
-      <c r="B7" s="232">
+      <c r="B7">
         <f>KEEI_계산과정!I56</f>
         <v>148473.38467291894</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="232">
+      <c r="A8">
         <v>2027</v>
       </c>
-      <c r="B8" s="232">
+      <c r="B8">
         <f>KEEI_계산과정!J56</f>
         <v>141254.67114756192</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="232">
+      <c r="A9">
         <v>2028</v>
       </c>
-      <c r="B9" s="232">
+      <c r="B9">
         <f>KEEI_계산과정!K56</f>
         <v>134035.95762220494</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="232">
+      <c r="A10">
         <v>2029</v>
       </c>
-      <c r="B10" s="232">
+      <c r="B10">
         <f>KEEI_계산과정!L56</f>
         <v>126817.24409684792</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="232">
+      <c r="A11">
         <v>2030</v>
       </c>
-      <c r="B11" s="232">
+      <c r="B11">
         <f>KEEI_계산과정!M56</f>
         <v>119598.53057149092</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="232">
+      <c r="A12">
         <v>2031</v>
       </c>
-      <c r="B12" s="232">
+      <c r="B12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="232">
+      <c r="A13">
         <v>2032</v>
       </c>
-      <c r="B13" s="232">
+      <c r="B13">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="232">
+      <c r="A14">
         <v>2033</v>
       </c>
-      <c r="B14" s="232">
+      <c r="B14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="232">
+      <c r="A15">
         <v>2034</v>
       </c>
-      <c r="B15" s="232">
+      <c r="B15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="232">
+      <c r="A16">
         <v>2035</v>
       </c>
-      <c r="B16" s="232">
+      <c r="B16">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="232">
+      <c r="A17">
         <v>2036</v>
       </c>
-      <c r="B17" s="232">
+      <c r="B17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="232">
+      <c r="A18">
         <v>2037</v>
       </c>
-      <c r="B18" s="232">
+      <c r="B18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="232">
+      <c r="A19">
         <v>2038</v>
       </c>
-      <c r="B19" s="232">
+      <c r="B19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="232">
+      <c r="A20">
         <v>2039</v>
       </c>
-      <c r="B20" s="232">
+      <c r="B20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="232">
+      <c r="A21">
         <v>2040</v>
       </c>
-      <c r="B21" s="232">
+      <c r="B21">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="232">
+      <c r="A22">
         <v>2041</v>
       </c>
-      <c r="B22" s="232">
+      <c r="B22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="232">
+      <c r="A23">
         <v>2042</v>
       </c>
-      <c r="B23" s="232">
+      <c r="B23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="232">
+      <c r="A24">
         <v>2043</v>
       </c>
-      <c r="B24" s="232">
+      <c r="B24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="232">
+      <c r="A25">
         <v>2044</v>
       </c>
-      <c r="B25" s="232">
+      <c r="B25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="232">
+      <c r="A26">
         <v>2045</v>
       </c>
-      <c r="B26" s="232">
+      <c r="B26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="232">
+      <c r="A27">
         <v>2046</v>
       </c>
-      <c r="B27" s="232">
+      <c r="B27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="232">
+      <c r="A28">
         <v>2047</v>
       </c>
-      <c r="B28" s="232">
+      <c r="B28">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="232">
+      <c r="A29">
         <v>2048</v>
       </c>
-      <c r="B29" s="232">
+      <c r="B29">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="232">
+      <c r="A30">
         <v>2049</v>
       </c>
-      <c r="B30" s="232">
+      <c r="B30">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="232">
+      <c r="A31">
         <v>2050</v>
       </c>
-      <c r="B31" s="232">
+      <c r="B31">
         <v>0</v>
       </c>
     </row>
@@ -21114,287 +21111,285 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" style="232" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" style="232" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="232"/>
-    <col min="4" max="4" width="9.90625" style="232" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="232"/>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="231" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="231" t="s">
+      <c r="A1" s="179" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="179" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="232">
+      <c r="A2">
         <v>2021</v>
       </c>
-      <c r="B2" s="232">
+      <c r="B2">
         <f>KEEI_계산과정!D48</f>
         <v>136839.65777514293</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="232">
+      <c r="A3">
         <v>2022</v>
       </c>
-      <c r="B3" s="232">
+      <c r="B3">
         <f>KEEI_계산과정!E48</f>
         <v>133600.36519098651</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="232">
+      <c r="A4">
         <v>2023</v>
       </c>
-      <c r="B4" s="232">
+      <c r="B4">
         <f>KEEI_계산과정!F48</f>
         <v>130361.07260683009</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="232">
+      <c r="A5">
         <v>2024</v>
       </c>
-      <c r="B5" s="232">
+      <c r="B5">
         <f>KEEI_계산과정!G48</f>
         <v>127121.78002267367</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="232">
+      <c r="A6">
         <v>2025</v>
       </c>
-      <c r="B6" s="232">
+      <c r="B6">
         <f>KEEI_계산과정!H48</f>
         <v>123882.48743851724</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="232">
+      <c r="A7">
         <v>2026</v>
       </c>
-      <c r="B7" s="232">
+      <c r="B7">
         <f>KEEI_계산과정!I48</f>
         <v>120643.19485436082</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="232">
+      <c r="A8">
         <v>2027</v>
       </c>
-      <c r="B8" s="232">
+      <c r="B8">
         <f>KEEI_계산과정!J48</f>
         <v>117403.9022702044</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="232">
+      <c r="A9">
         <v>2028</v>
       </c>
-      <c r="B9" s="232">
+      <c r="B9">
         <f>KEEI_계산과정!K48</f>
         <v>114164.60968604797</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="232">
+      <c r="A10">
         <v>2029</v>
       </c>
-      <c r="B10" s="232">
+      <c r="B10">
         <f>KEEI_계산과정!L48</f>
         <v>110925.31710189156</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="232">
+      <c r="A11">
         <v>2030</v>
       </c>
-      <c r="B11" s="232">
+      <c r="B11">
         <f>KEEI_계산과정!M48</f>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="232">
+      <c r="A12">
         <v>2031</v>
       </c>
-      <c r="B12" s="232">
+      <c r="B12">
         <f>B11</f>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="232">
+      <c r="A13">
         <v>2032</v>
       </c>
-      <c r="B13" s="232">
+      <c r="B13">
         <f t="shared" ref="B13:B31" si="0">B12</f>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="232">
+      <c r="A14">
         <v>2033</v>
       </c>
-      <c r="B14" s="232">
+      <c r="B14">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="232">
+      <c r="A15">
         <v>2034</v>
       </c>
-      <c r="B15" s="232">
+      <c r="B15">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="232">
+      <c r="A16">
         <v>2035</v>
       </c>
-      <c r="B16" s="232">
+      <c r="B16">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="232">
+      <c r="A17">
         <v>2036</v>
       </c>
-      <c r="B17" s="232">
+      <c r="B17">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="232">
+      <c r="A18">
         <v>2037</v>
       </c>
-      <c r="B18" s="232">
+      <c r="B18">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="232">
+      <c r="A19">
         <v>2038</v>
       </c>
-      <c r="B19" s="232">
+      <c r="B19">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="232">
+      <c r="A20">
         <v>2039</v>
       </c>
-      <c r="B20" s="232">
+      <c r="B20">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="232">
+      <c r="A21">
         <v>2040</v>
       </c>
-      <c r="B21" s="232">
+      <c r="B21">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="232">
+      <c r="A22">
         <v>2041</v>
       </c>
-      <c r="B22" s="232">
+      <c r="B22">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="232">
+      <c r="A23">
         <v>2042</v>
       </c>
-      <c r="B23" s="232">
+      <c r="B23">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="232">
+      <c r="A24">
         <v>2043</v>
       </c>
-      <c r="B24" s="232">
+      <c r="B24">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="232">
+      <c r="A25">
         <v>2044</v>
       </c>
-      <c r="B25" s="232">
+      <c r="B25">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="232">
+      <c r="A26">
         <v>2045</v>
       </c>
-      <c r="B26" s="232">
+      <c r="B26">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="232">
+      <c r="A27">
         <v>2046</v>
       </c>
-      <c r="B27" s="232">
+      <c r="B27">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="232">
+      <c r="A28">
         <v>2047</v>
       </c>
-      <c r="B28" s="232">
+      <c r="B28">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="232">
+      <c r="A29">
         <v>2048</v>
       </c>
-      <c r="B29" s="232">
+      <c r="B29">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="232">
+      <c r="A30">
         <v>2049</v>
       </c>
-      <c r="B30" s="232">
+      <c r="B30">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="232">
+      <c r="A31">
         <v>2050</v>
       </c>
-      <c r="B31" s="232">
+      <c r="B31">
         <f t="shared" si="0"/>
         <v>107686.02451773513</v>
       </c>
@@ -21410,182 +21405,206 @@
   <sheetPr>
     <tabColor rgb="FF003399"/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.90625" style="232" customWidth="1"/>
-    <col min="2" max="16384" width="8.7265625" style="232"/>
+    <col min="1" max="1" width="19.90625" customWidth="1"/>
+    <col min="2" max="6" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
-      <c r="A1" s="232" t="s">
+    <row r="1" spans="1:32">
+      <c r="A1" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="232">
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="C1" s="232">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="D1" s="232">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="E1" s="232">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="F1" s="232">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="G1" s="232">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="H1" s="232">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="I1" s="232">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="J1" s="232">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="K1" s="232">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="L1" s="232">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="M1" s="232">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="N1" s="232">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="O1" s="232">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="P1" s="232">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="Q1" s="232">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="R1" s="232">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="S1" s="232">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="T1" s="232">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="U1" s="232">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="V1" s="232">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="W1" s="232">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="X1" s="232">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="Y1" s="232">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="Z1" s="232">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AA1" s="232">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AB1" s="232">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
-      <c r="A2" s="232" t="s">
+    <row r="2" spans="1:32">
+      <c r="A2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="232">
+      <c r="B2">
         <v>0.2</v>
       </c>
-      <c r="C2" s="232">
+      <c r="C2">
         <v>0.2</v>
       </c>
-      <c r="D2" s="232">
+      <c r="D2">
         <v>0.2</v>
       </c>
-      <c r="E2" s="232">
+      <c r="E2">
         <v>0.2</v>
       </c>
-      <c r="F2" s="232">
+      <c r="F2">
         <v>0.2</v>
       </c>
-      <c r="G2" s="232">
+      <c r="G2">
         <v>0.2</v>
       </c>
-      <c r="H2" s="232">
+      <c r="H2">
         <v>0.2</v>
       </c>
-      <c r="I2" s="232">
+      <c r="I2">
         <v>0.2</v>
       </c>
-      <c r="J2" s="232">
+      <c r="J2">
         <v>0.2</v>
       </c>
-      <c r="K2" s="232">
+      <c r="K2">
         <v>0.2</v>
       </c>
-      <c r="L2" s="232">
+      <c r="L2">
         <v>0.2</v>
       </c>
-      <c r="M2" s="232">
+      <c r="M2">
         <v>0.2</v>
       </c>
-      <c r="N2" s="232">
+      <c r="N2">
         <v>0.2</v>
       </c>
-      <c r="O2" s="232">
+      <c r="O2">
         <v>0.2</v>
       </c>
-      <c r="P2" s="232">
+      <c r="P2">
         <v>0.2</v>
       </c>
-      <c r="Q2" s="232">
+      <c r="Q2">
         <v>0.2</v>
       </c>
-      <c r="R2" s="232">
+      <c r="R2">
         <v>0.2</v>
       </c>
-      <c r="S2" s="232">
+      <c r="S2">
         <v>0.2</v>
       </c>
-      <c r="T2" s="232">
+      <c r="T2">
         <v>0.2</v>
       </c>
-      <c r="U2" s="232">
+      <c r="U2">
         <v>0.2</v>
       </c>
-      <c r="V2" s="232">
+      <c r="V2">
         <v>0.2</v>
       </c>
-      <c r="W2" s="232">
+      <c r="W2">
         <v>0.2</v>
       </c>
-      <c r="X2" s="232">
+      <c r="X2">
         <v>0.2</v>
       </c>
-      <c r="Y2" s="232">
+      <c r="Y2">
         <v>0.2</v>
       </c>
-      <c r="Z2" s="232">
+      <c r="Z2">
         <v>0.2</v>
       </c>
-      <c r="AA2" s="232">
+      <c r="AA2">
         <v>0.2</v>
       </c>
-      <c r="AB2" s="232">
+      <c r="AB2">
+        <v>0.2</v>
+      </c>
+      <c r="AC2">
+        <v>0.2</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0.2</v>
+      </c>
+      <c r="AF2">
         <v>0.2</v>
       </c>
     </row>
